--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="385">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -956,6 +956,26 @@
   </si>
   <si>
     <t>022</t>
+  </si>
+  <si>
+    <t>* Select which teams or groups are in scope for the planned assessments
+* Select which capabilities/actions are in scope for each group's assessment
+* Select weights for each included action based on goals of the assessment and importance to the business
+* Set a preliminary target score for each included action to use for comparison
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>* Use objective (not subjective) scoring metrics for assessment evaluation
+* Document how metrics used in the assessment are calculated and state all assumptions
+* Use the same calculation assumptions and formulas across scopes if possible
+* List relevant documentation of process and policy as evidentiary support for each score
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>* Complete an initial assessment for different scopes of the business to establish a baseline
+* Plot scores over time to track maturity progress for priority scopes
+* Complete analysis on what contributed to or hindered progress across scopes or different areas of the assessment
+10*Ceil(x/3)</t>
   </si>
   <si>
     <t>* Define process for reviewing asking for credits from CSPs
@@ -1010,10 +1030,45 @@
 10*Ceil(x/4)</t>
   </si>
   <si>
+    <t>* Defined scope of each project to be estimated
+* Developed list of known inputs to the project
+* Have a process to determine what may be missing from the inputs or scope
+* Have a policy review to determine additional needs for inputs or scope
+* For each component of the estimate, list all assumptions
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Inventory possible commitment based discounts (RIs, Savings Plans, CUDs, etc.) available for deployed resources
+* Consider any private negotiated line item discounts vs public RI/CUD discounts
+* Set resource type standards to make use of spend commitments while maintaining needs of the business
+* Scenario plan commitment options versus potential changes in resources
+* Reference commit allocation strategy to calculate cost impact of shared scope vs private account commitments
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Use pricing lists or pricing calculators to estimate workload spend
+* Run workloads as trial experiments to get baseline spend
+* Estimate workload costs based on similar applications already deployed in your environment
+* Determine fixed costs vs formulas for variable costs due to growth of workloads
+* Factor in discounts and uptime metrics to determine accurate spend vs list
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>1. Calculate kg of carbon dioxide equivalents (kgCO2e), or similar, for new and ongoing workloads
+2. Compare carbon calculations with targets for new projects and overall consumption</t>
+  </si>
+  <si>
     <t>* Define and follow process for gathering deployment plans from teams
 * Determine timeline for each new project to adjust the forecast during that time
 * Determine how optimizations and lower run rate will impact the forecast on a rolling basis
 10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Refer teams to Documented Estimating Scope &amp; Policy and include these methods in trainings
+* Teams track baseline spend for resources they own, and share changes to baseline with leadership
+* Teams will share updates about their change in usage of shared resources and dependencies
+* Track team adoption of better estimates via KPIs around baseline or plan vs actuals
+10*Ceil(x/4)</t>
   </si>
   <si>
     <t>* Define cost drivers from finance/business
@@ -1126,6 +1181,15 @@
     <t>[{'Score': 0, 'Condition': 'Not monitored'}, {'Score': 2, 'Condition': 'Reported'}, {'Score': 5, 'Condition': 'Manual remediation'}, {'Score': 10, 'Condition': 'Automated remediation'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': '0 items completed'}, {'Score': 3, 'Condition': '1 item completed'}, {'Score': 5, 'Condition': '2 items completed'}, {'Score': 8, 'Condition': '3 items completed'}, {'Score': 10, 'Condition': '4 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': '1 item completed'}, {'Score': 5, 'Condition': '2 items completed'}, {'Score': 8, 'Condition': '3 items completed'}, {'Score': 10, 'Condition': '4 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 4, 'Condition': '1 item completed'}, {'Score': 7, 'Condition': '2 items completed'}, {'Score': 10, 'Condition': '3 items completed'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
   </si>
   <si>
@@ -1141,9 +1205,6 @@
     <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Done and clearly defined'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 4, 'Condition': '1 item completed'}, {'Score': 7, 'Condition': '2 items completed'}, {'Score': 10, 'Condition': '3 items completed'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'Does not exist'}, {'Score': 10, 'Condition': 'Exists'}]</t>
   </si>
   <si>
@@ -1162,15 +1223,15 @@
     <t>[{'Score': 0, 'Condition': 'No review of trends'}, {'Score': 3, 'Condition': 'Manual review of trends'}, {'Score': 6, 'Condition': 'Automated trend detection'}, {'Score': 10, 'Condition': 'Manual review and automated trend detection'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': '1 item completed'}, {'Score': 5, 'Condition': '2 items completed'}, {'Score': 8, 'Condition': '3 items completed'}, {'Score': 10, 'Condition': '4 items completed'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 1, 'Condition': 'Annual'}, {'Score': 2, 'Condition': 'Quarterly'}, {'Score': 5, 'Condition': 'Monthly'}, {'Score': 7, 'Condition': 'Bi-Weekly'}, {'Score': 8, 'Condition': 'Weekly'}, {'Score': 10, 'Condition': 'Daily'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'No alerting'}, {'Score': 10, 'Condition': 'Alerting exists'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': 'item 1 completed'}, {'Score': 10, 'Condition': 'item 2 completed'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 10, 'Condition': 'set goal thresholds for kpis and unit costs'}]</t>
   </si>
   <si>
@@ -1199,6 +1260,9 @@
   </si>
   <si>
     <t>0: Not monitored</t>
+  </si>
+  <si>
+    <t>0: 0 items completed</t>
   </si>
   <si>
     <t>0: No items completed</t>
@@ -2569,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H2">
         <f>E2*VALUE(LEFT(G2, FIND(":", G2)-1))</f>
@@ -2595,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H3">
         <f>E3*VALUE(LEFT(G3, FIND(":", G3)-1))</f>
@@ -2621,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H4">
         <f>E4*VALUE(LEFT(G4, FIND(":", G4)-1))</f>
@@ -2647,7 +2711,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="H5">
         <f>E5*VALUE(LEFT(G5, FIND(":", G5)-1))</f>
@@ -2673,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H6">
         <f>E6*VALUE(LEFT(G6, FIND(":", G6)-1))</f>
@@ -2698,10 +2762,13 @@
         <v>183</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>313</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="H7">
         <f>E7*VALUE(LEFT(G7, FIND(":", G7)-1))</f>
@@ -2724,10 +2791,13 @@
         <v>184</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="H8">
         <f>E8*VALUE(LEFT(G8, FIND(":", G8)-1))</f>
@@ -2750,10 +2820,13 @@
         <v>185</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>315</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="H9">
         <f>E9*VALUE(LEFT(G9, FIND(":", G9)-1))</f>
@@ -2779,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H10">
         <f>E10*VALUE(LEFT(G10, FIND(":", G10)-1))</f>
@@ -2805,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H11">
         <f>E11*VALUE(LEFT(G11, FIND(":", G11)-1))</f>
@@ -2833,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H12">
         <f>E12*VALUE(LEFT(G12, FIND(":", G12)-1))</f>
@@ -2859,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H13">
         <f>E13*VALUE(LEFT(G13, FIND(":", G13)-1))</f>
@@ -2885,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H14">
         <f>E14*VALUE(LEFT(G14, FIND(":", G14)-1))</f>
@@ -2911,10 +2984,10 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H15">
         <f>E15*VALUE(LEFT(G15, FIND(":", G15)-1))</f>
@@ -2940,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H16">
         <f>E16*VALUE(LEFT(G16, FIND(":", G16)-1))</f>
@@ -2968,7 +3041,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="H17">
         <f>E17*VALUE(LEFT(G17, FIND(":", G17)-1))</f>
@@ -2994,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H18">
         <f>E18*VALUE(LEFT(G18, FIND(":", G18)-1))</f>
@@ -3020,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H19">
         <f>E19*VALUE(LEFT(G19, FIND(":", G19)-1))</f>
@@ -3046,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H20">
         <f>E20*VALUE(LEFT(G20, FIND(":", G20)-1))</f>
@@ -3072,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H21">
         <f>E21*VALUE(LEFT(G21, FIND(":", G21)-1))</f>
@@ -3098,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H22">
         <f>E22*VALUE(LEFT(G22, FIND(":", G22)-1))</f>
@@ -3126,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H23">
         <f>E23*VALUE(LEFT(G23, FIND(":", G23)-1))</f>
@@ -3152,7 +3225,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="H24">
         <f>E24*VALUE(LEFT(G24, FIND(":", G24)-1))</f>
@@ -3178,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H25">
         <f>E25*VALUE(LEFT(G25, FIND(":", G25)-1))</f>
@@ -3204,10 +3277,10 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H26">
         <f>E26*VALUE(LEFT(G26, FIND(":", G26)-1))</f>
@@ -3233,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H27">
         <f>E27*VALUE(LEFT(G27, FIND(":", G27)-1))</f>
@@ -3261,7 +3334,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H28">
         <f>E28*VALUE(LEFT(G28, FIND(":", G28)-1))</f>
@@ -3287,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H29">
         <f>E29*VALUE(LEFT(G29, FIND(":", G29)-1))</f>
@@ -3313,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H30">
         <f>E30*VALUE(LEFT(G30, FIND(":", G30)-1))</f>
@@ -3339,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H31">
         <f>E31*VALUE(LEFT(G31, FIND(":", G31)-1))</f>
@@ -3365,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H32">
         <f>E32*VALUE(LEFT(G32, FIND(":", G32)-1))</f>
@@ -3391,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H33">
         <f>E33*VALUE(LEFT(G33, FIND(":", G33)-1))</f>
@@ -3419,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H34">
         <f>E34*VALUE(LEFT(G34, FIND(":", G34)-1))</f>
@@ -3445,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H35">
         <f>E35*VALUE(LEFT(G35, FIND(":", G35)-1))</f>
@@ -3471,7 +3544,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="H36">
         <f>E36*VALUE(LEFT(G36, FIND(":", G36)-1))</f>
@@ -3497,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H37">
         <f>E37*VALUE(LEFT(G37, FIND(":", G37)-1))</f>
@@ -3523,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H38">
         <f>E38*VALUE(LEFT(G38, FIND(":", G38)-1))</f>
@@ -3549,7 +3622,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="H39">
         <f>E39*VALUE(LEFT(G39, FIND(":", G39)-1))</f>
@@ -3577,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H40">
         <f>E40*VALUE(LEFT(G40, FIND(":", G40)-1))</f>
@@ -3603,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H41">
         <f>E41*VALUE(LEFT(G41, FIND(":", G41)-1))</f>
@@ -3629,10 +3702,10 @@
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H42">
         <f>E42*VALUE(LEFT(G42, FIND(":", G42)-1))</f>
@@ -3658,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H43">
         <f>E43*VALUE(LEFT(G43, FIND(":", G43)-1))</f>
@@ -3684,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H44">
         <f>E44*VALUE(LEFT(G44, FIND(":", G44)-1))</f>
@@ -3710,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H45">
         <f>E45*VALUE(LEFT(G45, FIND(":", G45)-1))</f>
@@ -3740,7 +3813,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H46">
         <f>E46*VALUE(LEFT(G46, FIND(":", G46)-1))</f>
@@ -3766,10 +3839,10 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H47">
         <f>E47*VALUE(LEFT(G47, FIND(":", G47)-1))</f>
@@ -3795,7 +3868,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="H48">
         <f>E48*VALUE(LEFT(G48, FIND(":", G48)-1))</f>
@@ -3821,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H49">
         <f>E49*VALUE(LEFT(G49, FIND(":", G49)-1))</f>
@@ -3847,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H50">
         <f>E50*VALUE(LEFT(G50, FIND(":", G50)-1))</f>
@@ -3873,7 +3946,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H51">
         <f>E51*VALUE(LEFT(G51, FIND(":", G51)-1))</f>
@@ -3901,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H52">
         <f>E52*VALUE(LEFT(G52, FIND(":", G52)-1))</f>
@@ -3927,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H53">
         <f>E53*VALUE(LEFT(G53, FIND(":", G53)-1))</f>
@@ -3953,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H54">
         <f>E54*VALUE(LEFT(G54, FIND(":", G54)-1))</f>
@@ -3979,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H55">
         <f>E55*VALUE(LEFT(G55, FIND(":", G55)-1))</f>
@@ -4005,7 +4078,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H56">
         <f>E56*VALUE(LEFT(G56, FIND(":", G56)-1))</f>
@@ -4031,7 +4104,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H57">
         <f>E57*VALUE(LEFT(G57, FIND(":", G57)-1))</f>
@@ -4059,7 +4132,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H58">
         <f>E58*VALUE(LEFT(G58, FIND(":", G58)-1))</f>
@@ -4085,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H59">
         <f>E59*VALUE(LEFT(G59, FIND(":", G59)-1))</f>
@@ -4111,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H60">
         <f>E60*VALUE(LEFT(G60, FIND(":", G60)-1))</f>
@@ -4137,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="H61">
         <f>E61*VALUE(LEFT(G61, FIND(":", G61)-1))</f>
@@ -4163,7 +4236,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H62">
         <f>E62*VALUE(LEFT(G62, FIND(":", G62)-1))</f>
@@ -4189,7 +4262,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H63">
         <f>E63*VALUE(LEFT(G63, FIND(":", G63)-1))</f>
@@ -4217,7 +4290,7 @@
         <v>1</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="H64">
         <f>E64*VALUE(LEFT(G64, FIND(":", G64)-1))</f>
@@ -4243,7 +4316,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="H65">
         <f>E65*VALUE(LEFT(G65, FIND(":", G65)-1))</f>
@@ -4269,7 +4342,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H66">
         <f>E66*VALUE(LEFT(G66, FIND(":", G66)-1))</f>
@@ -4295,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H67">
         <f>E67*VALUE(LEFT(G67, FIND(":", G67)-1))</f>
@@ -4321,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H68">
         <f>E68*VALUE(LEFT(G68, FIND(":", G68)-1))</f>
@@ -4347,10 +4420,10 @@
         <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H69">
         <f>E69*VALUE(LEFT(G69, FIND(":", G69)-1))</f>
@@ -4378,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H70">
         <f>E70*VALUE(LEFT(G70, FIND(":", G70)-1))</f>
@@ -4404,7 +4477,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="H71">
         <f>E71*VALUE(LEFT(G71, FIND(":", G71)-1))</f>
@@ -4430,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H72">
         <f>E72*VALUE(LEFT(G72, FIND(":", G72)-1))</f>
@@ -4456,7 +4529,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H73">
         <f>E73*VALUE(LEFT(G73, FIND(":", G73)-1))</f>
@@ -4482,7 +4555,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H74">
         <f>E74*VALUE(LEFT(G74, FIND(":", G74)-1))</f>
@@ -4508,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H75">
         <f>E75*VALUE(LEFT(G75, FIND(":", G75)-1))</f>
@@ -4538,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H76">
         <f>E76*VALUE(LEFT(G76, FIND(":", G76)-1))</f>
@@ -4564,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H77">
         <f>E77*VALUE(LEFT(G77, FIND(":", G77)-1))</f>
@@ -4590,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H78">
         <f>E78*VALUE(LEFT(G78, FIND(":", G78)-1))</f>
@@ -4616,7 +4689,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H79">
         <f>E79*VALUE(LEFT(G79, FIND(":", G79)-1))</f>
@@ -4642,7 +4715,7 @@
         <v>1</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="H80">
         <f>E80*VALUE(LEFT(G80, FIND(":", G80)-1))</f>
@@ -4668,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H81">
         <f>E81*VALUE(LEFT(G81, FIND(":", G81)-1))</f>
@@ -4696,7 +4769,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H82">
         <f>E82*VALUE(LEFT(G82, FIND(":", G82)-1))</f>
@@ -4722,7 +4795,7 @@
         <v>1</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H83">
         <f>E83*VALUE(LEFT(G83, FIND(":", G83)-1))</f>
@@ -4748,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H84">
         <f>E84*VALUE(LEFT(G84, FIND(":", G84)-1))</f>
@@ -4774,7 +4847,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H85">
         <f>E85*VALUE(LEFT(G85, FIND(":", G85)-1))</f>
@@ -4800,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H86">
         <f>E86*VALUE(LEFT(G86, FIND(":", G86)-1))</f>
@@ -4826,7 +4899,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H87">
         <f>E87*VALUE(LEFT(G87, FIND(":", G87)-1))</f>
@@ -4854,7 +4927,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H88">
         <f>E88*VALUE(LEFT(G88, FIND(":", G88)-1))</f>
@@ -4880,10 +4953,10 @@
         <v>1</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H89">
         <f>E89*VALUE(LEFT(G89, FIND(":", G89)-1))</f>
@@ -4909,7 +4982,7 @@
         <v>1</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H90">
         <f>E90*VALUE(LEFT(G90, FIND(":", G90)-1))</f>
@@ -4935,10 +5008,10 @@
         <v>1</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H91">
         <f>E91*VALUE(LEFT(G91, FIND(":", G91)-1))</f>
@@ -4964,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="H92">
         <f>E92*VALUE(LEFT(G92, FIND(":", G92)-1))</f>
@@ -4990,10 +5063,10 @@
         <v>1</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H93">
         <f>E93*VALUE(LEFT(G93, FIND(":", G93)-1))</f>
@@ -5018,10 +5091,13 @@
         <v>270</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="H94">
         <f>E94*VALUE(LEFT(G94, FIND(":", G94)-1))</f>
@@ -5044,10 +5120,13 @@
         <v>271</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="H95">
         <f>E95*VALUE(LEFT(G95, FIND(":", G95)-1))</f>
@@ -5070,10 +5149,13 @@
         <v>272</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>326</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="H96">
         <f>E96*VALUE(LEFT(G96, FIND(":", G96)-1))</f>
@@ -5096,10 +5178,13 @@
         <v>273</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>327</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="H97">
         <f>E97*VALUE(LEFT(G97, FIND(":", G97)-1))</f>
@@ -5125,10 +5210,10 @@
         <v>1</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H98">
         <f>E98*VALUE(LEFT(G98, FIND(":", G98)-1))</f>
@@ -5154,7 +5239,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H99">
         <f>E99*VALUE(LEFT(G99, FIND(":", G99)-1))</f>
@@ -5177,10 +5262,13 @@
         <v>276</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="H100">
         <f>E100*VALUE(LEFT(G100, FIND(":", G100)-1))</f>
@@ -5208,10 +5296,10 @@
         <v>1</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H101">
         <f>E101*VALUE(LEFT(G101, FIND(":", G101)-1))</f>
@@ -5237,7 +5325,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H102">
         <f>E102*VALUE(LEFT(G102, FIND(":", G102)-1))</f>
@@ -5263,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H103">
         <f>E103*VALUE(LEFT(G103, FIND(":", G103)-1))</f>
@@ -5289,7 +5377,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H104">
         <f>E104*VALUE(LEFT(G104, FIND(":", G104)-1))</f>
@@ -5315,7 +5403,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H105">
         <f>E105*VALUE(LEFT(G105, FIND(":", G105)-1))</f>
@@ -5341,7 +5429,7 @@
         <v>1</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H106">
         <f>E106*VALUE(LEFT(G106, FIND(":", G106)-1))</f>
@@ -5371,10 +5459,10 @@
         <v>1</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H107">
         <f>E107*VALUE(LEFT(G107, FIND(":", G107)-1))</f>
@@ -5400,10 +5488,10 @@
         <v>1</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H108">
         <f>E108*VALUE(LEFT(G108, FIND(":", G108)-1))</f>
@@ -5429,10 +5517,10 @@
         <v>1</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H109">
         <f>E109*VALUE(LEFT(G109, FIND(":", G109)-1))</f>
@@ -5458,10 +5546,10 @@
         <v>1</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H110">
         <f>E110*VALUE(LEFT(G110, FIND(":", G110)-1))</f>
@@ -5487,10 +5575,10 @@
         <v>1</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H111">
         <f>E111*VALUE(LEFT(G111, FIND(":", G111)-1))</f>
@@ -5516,10 +5604,10 @@
         <v>1</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H112">
         <f>E112*VALUE(LEFT(G112, FIND(":", G112)-1))</f>
@@ -5545,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H113">
         <f>E113*VALUE(LEFT(G113, FIND(":", G113)-1))</f>
@@ -5573,10 +5661,10 @@
         <v>1</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H114">
         <f>E114*VALUE(LEFT(G114, FIND(":", G114)-1))</f>
@@ -5602,10 +5690,10 @@
         <v>1</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H115">
         <f>E115*VALUE(LEFT(G115, FIND(":", G115)-1))</f>
@@ -5631,7 +5719,7 @@
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="H116">
         <f>E116*VALUE(LEFT(G116, FIND(":", G116)-1))</f>
@@ -5657,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H117">
         <f>E117*VALUE(LEFT(G117, FIND(":", G117)-1))</f>
@@ -5683,7 +5771,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H118">
         <f>E118*VALUE(LEFT(G118, FIND(":", G118)-1))</f>
@@ -5709,10 +5797,10 @@
         <v>1</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H119">
         <f>E119*VALUE(LEFT(G119, FIND(":", G119)-1))</f>
@@ -5738,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H120">
         <f>E120*VALUE(LEFT(G120, FIND(":", G120)-1))</f>
@@ -5766,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H121">
         <f>E121*VALUE(LEFT(G121, FIND(":", G121)-1))</f>
@@ -5792,7 +5880,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H122">
         <f>E122*VALUE(LEFT(G122, FIND(":", G122)-1))</f>
@@ -5818,7 +5906,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H123">
         <f>E123*VALUE(LEFT(G123, FIND(":", G123)-1))</f>
@@ -5844,7 +5932,7 @@
         <v>1</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="H124">
         <f>E124*VALUE(LEFT(G124, FIND(":", G124)-1))</f>
@@ -5870,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H125">
         <f>E125*VALUE(LEFT(G125, FIND(":", G125)-1))</f>
@@ -5896,10 +5984,10 @@
         <v>1</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H126">
         <f>E126*VALUE(LEFT(G126, FIND(":", G126)-1))</f>
@@ -5925,10 +6013,10 @@
         <v>1</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H127">
         <f>E127*VALUE(LEFT(G127, FIND(":", G127)-1))</f>
@@ -5954,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H128">
         <f>E128*VALUE(LEFT(G128, FIND(":", G128)-1))</f>
@@ -5980,7 +6068,7 @@
         <v>1</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="H129">
         <f>E129*VALUE(LEFT(G129, FIND(":", G129)-1))</f>
@@ -6008,7 +6096,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H130">
         <f>E130*VALUE(LEFT(G130, FIND(":", G130)-1))</f>
@@ -6034,10 +6122,10 @@
         <v>1</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H131">
         <f>E131*VALUE(LEFT(G131, FIND(":", G131)-1))</f>
@@ -6063,10 +6151,10 @@
         <v>1</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H132">
         <f>E132*VALUE(LEFT(G132, FIND(":", G132)-1))</f>
@@ -6092,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H133">
         <f>E133*VALUE(LEFT(G133, FIND(":", G133)-1))</f>
@@ -6118,7 +6206,7 @@
         <v>1</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="H134">
         <f>E134*VALUE(LEFT(G134, FIND(":", G134)-1))</f>
@@ -6144,7 +6232,7 @@
         <v>0</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H135">
         <f>E135*VALUE(LEFT(G135, FIND(":", G135)-1))</f>
@@ -6170,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H136">
         <f>E136*VALUE(LEFT(G136, FIND(":", G136)-1))</f>
@@ -6229,13 +6317,13 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: 0 items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G9">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G10">
       <formula1>"0: None"</formula1>
@@ -6490,16 +6578,16 @@
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G94">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G95">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G96">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G97">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G98">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
@@ -6508,7 +6596,7 @@
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G100">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G101">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="390">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -976,6 +976,18 @@
 * Plot scores over time to track maturity progress for priority scopes
 * Complete analysis on what contributed to or hindered progress across scopes or different areas of the assessment
 10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>1. Invite subject matter experts (SMEs) and leadership to determine which gaps to address first
+2. Determine owners for addressing each of the prioritized gaps
+3. Owners will work with relevant teams to scope out how to meet the target score for each gap
+4. Work is then scheduled in a roadmap with deadlines that can be tracked at the leadership level</t>
+  </si>
+  <si>
+    <t>* Schedule a cadence to report progress outcomes to key stakeholders.
+* Create reporting to show progress on key outcomes across all maturity initiatives.
+* After successful outcomes are achieved, move on to the next prioritized item in the roadmap.
+* Periodically reevaluate the gap analysis and priority list based on lessons learned and new business goals.</t>
   </si>
   <si>
     <t>* Define process for reviewing asking for credits from CSPs
@@ -1190,6 +1202,9 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 4, 'Condition': '1 item completed'}, {'Score': 7, 'Condition': '2 items completed'}, {'Score': 10, 'Condition': '3 items completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1, and 2 completed'}, {'Score': 8, 'Condition': 'items 1, 2, and 3 completed'}, {'Score': 10, 'Condition': 'items 1, 2, 3, and 4 completed'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
   </si>
   <si>
@@ -1232,7 +1247,7 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': 'item 1 completed'}, {'Score': 10, 'Condition': 'item 2 completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 10, 'Condition': 'set goal thresholds for kpis and unit costs'}]</t>
+    <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 10, 'Condition': 'communicates wins in KPI thresholds and unit costs'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': '0%'}, {'Score': 1, 'Condition': '10%'}, {'Score': 2, 'Condition': '20%'}, {'Score': 3, 'Condition': '30%'}, {'Score': 4, 'Condition': '40%'}, {'Score': 5, 'Condition': '50%'}, {'Score': 6, 'Condition': '60%'}, {'Score': 7, 'Condition': '70%'}, {'Score': 8, 'Condition': '80% '}, {'Score': 9, 'Condition': '90%'}, {'Score': 10, 'Condition': 'Near 100%'}]</t>
@@ -1244,7 +1259,7 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 5, 'Condition': '3 items completed'}, {'Score': 7, 'Condition': '4 items completed'}, {'Score': 9, 'Condition': '5 items completed'}, {'Score': 10, 'Condition': '6 items completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'No alerting in workflow tools'}, {'Score': 1, 'Condition': 'Alerting in at least one tool'}, {'Score': 3, 'Condition': 'Alerting in some tooling [20%]'}, {'Score': 6, 'Condition': 'Alerting in most tooling [60%]'}, {'Score': 10, 'Condition': 'Alerting in all workflow tools [100%]'}]</t>
+    <t>[{'Score': 0, 'Condition': 'No alerting to any owners'}, {'Score': 1, 'Condition': 'Alerting in at least one owner'}, {'Score': 3, 'Condition': 'Alerting to some owners [&gt;20%]'}, {'Score': 6, 'Condition': 'Alerting to most owners [&gt;60%]'}, {'Score': 10, 'Condition': 'Alerting to all owners [100%]'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 3, 'Condition': '2 items completed'}, {'Score': 4, 'Condition': '3 items completed'}, {'Score': 5, 'Condition': '4 items completed'}, {'Score': 7, 'Condition': '5 items completed'}, {'Score': 8, 'Condition': '6 items completed'}, {'Score': 9, 'Condition': '7 items completed'}, {'Score': 10, 'Condition': '8 items completed'}]</t>
@@ -1256,6 +1271,9 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 items completed'}, {'Score': 3, 'Condition': '2 items completed'}, {'Score': 5, 'Condition': '3 items completed'}, {'Score': 6, 'Condition': '4 items completed'}, {'Score': 8, 'Condition': '5 items completed'}, {'Score': 9, 'Condition': '6 items completed'}, {'Score': 10, 'Condition': '7 items completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No alerting in workflow tools'}, {'Score': 1, 'Condition': 'Alerting in at least one tool'}, {'Score': 3, 'Condition': 'Alerting in some tooling [&gt;20%]'}, {'Score': 6, 'Condition': 'Alerting in most tooling [&gt;60%]'}, {'Score': 10, 'Condition': 'Alerting in all workflow tools [100%]'}]</t>
+  </si>
+  <si>
     <t>0: None</t>
   </si>
   <si>
@@ -1292,10 +1310,13 @@
     <t>0: No alerting</t>
   </si>
   <si>
+    <t>0: No alerting to any owners</t>
+  </si>
+  <si>
+    <t>0: Never</t>
+  </si>
+  <si>
     <t>0: No alerting in workflow tools</t>
-  </si>
-  <si>
-    <t>0: Never</t>
   </si>
 </sst>
 </file>
@@ -2633,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H2">
         <f>E2*VALUE(LEFT(G2, FIND(":", G2)-1))</f>
@@ -2659,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H3">
         <f>E3*VALUE(LEFT(G3, FIND(":", G3)-1))</f>
@@ -2685,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H4">
         <f>E4*VALUE(LEFT(G4, FIND(":", G4)-1))</f>
@@ -2711,7 +2732,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="H5">
         <f>E5*VALUE(LEFT(G5, FIND(":", G5)-1))</f>
@@ -2737,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H6">
         <f>E6*VALUE(LEFT(G6, FIND(":", G6)-1))</f>
@@ -2768,7 +2789,7 @@
         <v>313</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="H7">
         <f>E7*VALUE(LEFT(G7, FIND(":", G7)-1))</f>
@@ -2797,7 +2818,7 @@
         <v>314</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H8">
         <f>E8*VALUE(LEFT(G8, FIND(":", G8)-1))</f>
@@ -2826,7 +2847,7 @@
         <v>315</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H9">
         <f>E9*VALUE(LEFT(G9, FIND(":", G9)-1))</f>
@@ -2849,10 +2870,13 @@
         <v>186</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="H10">
         <f>E10*VALUE(LEFT(G10, FIND(":", G10)-1))</f>
@@ -2877,8 +2901,11 @@
       <c r="E11">
         <v>0</v>
       </c>
+      <c r="F11" s="1" t="s">
+        <v>317</v>
+      </c>
       <c r="G11" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="H11">
         <f>E11*VALUE(LEFT(G11, FIND(":", G11)-1))</f>
@@ -2906,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H12">
         <f>E12*VALUE(LEFT(G12, FIND(":", G12)-1))</f>
@@ -2932,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H13">
         <f>E13*VALUE(LEFT(G13, FIND(":", G13)-1))</f>
@@ -2958,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H14">
         <f>E14*VALUE(LEFT(G14, FIND(":", G14)-1))</f>
@@ -2984,10 +3011,10 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H15">
         <f>E15*VALUE(LEFT(G15, FIND(":", G15)-1))</f>
@@ -3013,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H16">
         <f>E16*VALUE(LEFT(G16, FIND(":", G16)-1))</f>
@@ -3041,7 +3068,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H17">
         <f>E17*VALUE(LEFT(G17, FIND(":", G17)-1))</f>
@@ -3067,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H18">
         <f>E18*VALUE(LEFT(G18, FIND(":", G18)-1))</f>
@@ -3093,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H19">
         <f>E19*VALUE(LEFT(G19, FIND(":", G19)-1))</f>
@@ -3119,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H20">
         <f>E20*VALUE(LEFT(G20, FIND(":", G20)-1))</f>
@@ -3145,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H21">
         <f>E21*VALUE(LEFT(G21, FIND(":", G21)-1))</f>
@@ -3171,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H22">
         <f>E22*VALUE(LEFT(G22, FIND(":", G22)-1))</f>
@@ -3199,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H23">
         <f>E23*VALUE(LEFT(G23, FIND(":", G23)-1))</f>
@@ -3225,7 +3252,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="H24">
         <f>E24*VALUE(LEFT(G24, FIND(":", G24)-1))</f>
@@ -3251,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H25">
         <f>E25*VALUE(LEFT(G25, FIND(":", G25)-1))</f>
@@ -3277,10 +3304,10 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H26">
         <f>E26*VALUE(LEFT(G26, FIND(":", G26)-1))</f>
@@ -3306,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H27">
         <f>E27*VALUE(LEFT(G27, FIND(":", G27)-1))</f>
@@ -3334,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H28">
         <f>E28*VALUE(LEFT(G28, FIND(":", G28)-1))</f>
@@ -3360,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H29">
         <f>E29*VALUE(LEFT(G29, FIND(":", G29)-1))</f>
@@ -3386,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H30">
         <f>E30*VALUE(LEFT(G30, FIND(":", G30)-1))</f>
@@ -3412,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H31">
         <f>E31*VALUE(LEFT(G31, FIND(":", G31)-1))</f>
@@ -3438,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H32">
         <f>E32*VALUE(LEFT(G32, FIND(":", G32)-1))</f>
@@ -3464,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H33">
         <f>E33*VALUE(LEFT(G33, FIND(":", G33)-1))</f>
@@ -3492,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H34">
         <f>E34*VALUE(LEFT(G34, FIND(":", G34)-1))</f>
@@ -3518,7 +3545,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H35">
         <f>E35*VALUE(LEFT(G35, FIND(":", G35)-1))</f>
@@ -3544,7 +3571,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H36">
         <f>E36*VALUE(LEFT(G36, FIND(":", G36)-1))</f>
@@ -3570,7 +3597,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H37">
         <f>E37*VALUE(LEFT(G37, FIND(":", G37)-1))</f>
@@ -3596,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H38">
         <f>E38*VALUE(LEFT(G38, FIND(":", G38)-1))</f>
@@ -3622,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H39">
         <f>E39*VALUE(LEFT(G39, FIND(":", G39)-1))</f>
@@ -3650,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H40">
         <f>E40*VALUE(LEFT(G40, FIND(":", G40)-1))</f>
@@ -3676,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H41">
         <f>E41*VALUE(LEFT(G41, FIND(":", G41)-1))</f>
@@ -3702,10 +3729,10 @@
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H42">
         <f>E42*VALUE(LEFT(G42, FIND(":", G42)-1))</f>
@@ -3731,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H43">
         <f>E43*VALUE(LEFT(G43, FIND(":", G43)-1))</f>
@@ -3757,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H44">
         <f>E44*VALUE(LEFT(G44, FIND(":", G44)-1))</f>
@@ -3783,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H45">
         <f>E45*VALUE(LEFT(G45, FIND(":", G45)-1))</f>
@@ -3813,7 +3840,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H46">
         <f>E46*VALUE(LEFT(G46, FIND(":", G46)-1))</f>
@@ -3839,10 +3866,10 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H47">
         <f>E47*VALUE(LEFT(G47, FIND(":", G47)-1))</f>
@@ -3868,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="H48">
         <f>E48*VALUE(LEFT(G48, FIND(":", G48)-1))</f>
@@ -3894,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H49">
         <f>E49*VALUE(LEFT(G49, FIND(":", G49)-1))</f>
@@ -3920,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H50">
         <f>E50*VALUE(LEFT(G50, FIND(":", G50)-1))</f>
@@ -3946,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H51">
         <f>E51*VALUE(LEFT(G51, FIND(":", G51)-1))</f>
@@ -3974,7 +4001,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H52">
         <f>E52*VALUE(LEFT(G52, FIND(":", G52)-1))</f>
@@ -4000,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H53">
         <f>E53*VALUE(LEFT(G53, FIND(":", G53)-1))</f>
@@ -4026,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H54">
         <f>E54*VALUE(LEFT(G54, FIND(":", G54)-1))</f>
@@ -4052,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H55">
         <f>E55*VALUE(LEFT(G55, FIND(":", G55)-1))</f>
@@ -4078,7 +4105,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H56">
         <f>E56*VALUE(LEFT(G56, FIND(":", G56)-1))</f>
@@ -4104,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H57">
         <f>E57*VALUE(LEFT(G57, FIND(":", G57)-1))</f>
@@ -4132,7 +4159,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H58">
         <f>E58*VALUE(LEFT(G58, FIND(":", G58)-1))</f>
@@ -4158,7 +4185,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H59">
         <f>E59*VALUE(LEFT(G59, FIND(":", G59)-1))</f>
@@ -4184,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H60">
         <f>E60*VALUE(LEFT(G60, FIND(":", G60)-1))</f>
@@ -4210,7 +4237,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H61">
         <f>E61*VALUE(LEFT(G61, FIND(":", G61)-1))</f>
@@ -4236,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H62">
         <f>E62*VALUE(LEFT(G62, FIND(":", G62)-1))</f>
@@ -4262,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H63">
         <f>E63*VALUE(LEFT(G63, FIND(":", G63)-1))</f>
@@ -4290,7 +4317,7 @@
         <v>1</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H64">
         <f>E64*VALUE(LEFT(G64, FIND(":", G64)-1))</f>
@@ -4316,7 +4343,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H65">
         <f>E65*VALUE(LEFT(G65, FIND(":", G65)-1))</f>
@@ -4342,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H66">
         <f>E66*VALUE(LEFT(G66, FIND(":", G66)-1))</f>
@@ -4368,7 +4395,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H67">
         <f>E67*VALUE(LEFT(G67, FIND(":", G67)-1))</f>
@@ -4394,7 +4421,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H68">
         <f>E68*VALUE(LEFT(G68, FIND(":", G68)-1))</f>
@@ -4420,10 +4447,10 @@
         <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H69">
         <f>E69*VALUE(LEFT(G69, FIND(":", G69)-1))</f>
@@ -4451,7 +4478,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H70">
         <f>E70*VALUE(LEFT(G70, FIND(":", G70)-1))</f>
@@ -4477,7 +4504,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="H71">
         <f>E71*VALUE(LEFT(G71, FIND(":", G71)-1))</f>
@@ -4503,7 +4530,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H72">
         <f>E72*VALUE(LEFT(G72, FIND(":", G72)-1))</f>
@@ -4529,7 +4556,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H73">
         <f>E73*VALUE(LEFT(G73, FIND(":", G73)-1))</f>
@@ -4555,7 +4582,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H74">
         <f>E74*VALUE(LEFT(G74, FIND(":", G74)-1))</f>
@@ -4581,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H75">
         <f>E75*VALUE(LEFT(G75, FIND(":", G75)-1))</f>
@@ -4611,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H76">
         <f>E76*VALUE(LEFT(G76, FIND(":", G76)-1))</f>
@@ -4637,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H77">
         <f>E77*VALUE(LEFT(G77, FIND(":", G77)-1))</f>
@@ -4663,7 +4690,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H78">
         <f>E78*VALUE(LEFT(G78, FIND(":", G78)-1))</f>
@@ -4689,7 +4716,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H79">
         <f>E79*VALUE(LEFT(G79, FIND(":", G79)-1))</f>
@@ -4715,7 +4742,7 @@
         <v>1</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H80">
         <f>E80*VALUE(LEFT(G80, FIND(":", G80)-1))</f>
@@ -4741,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H81">
         <f>E81*VALUE(LEFT(G81, FIND(":", G81)-1))</f>
@@ -4769,7 +4796,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H82">
         <f>E82*VALUE(LEFT(G82, FIND(":", G82)-1))</f>
@@ -4795,7 +4822,7 @@
         <v>1</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H83">
         <f>E83*VALUE(LEFT(G83, FIND(":", G83)-1))</f>
@@ -4821,7 +4848,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H84">
         <f>E84*VALUE(LEFT(G84, FIND(":", G84)-1))</f>
@@ -4847,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H85">
         <f>E85*VALUE(LEFT(G85, FIND(":", G85)-1))</f>
@@ -4873,7 +4900,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H86">
         <f>E86*VALUE(LEFT(G86, FIND(":", G86)-1))</f>
@@ -4899,7 +4926,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H87">
         <f>E87*VALUE(LEFT(G87, FIND(":", G87)-1))</f>
@@ -4927,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H88">
         <f>E88*VALUE(LEFT(G88, FIND(":", G88)-1))</f>
@@ -4953,10 +4980,10 @@
         <v>1</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H89">
         <f>E89*VALUE(LEFT(G89, FIND(":", G89)-1))</f>
@@ -4982,7 +5009,7 @@
         <v>1</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H90">
         <f>E90*VALUE(LEFT(G90, FIND(":", G90)-1))</f>
@@ -5008,10 +5035,10 @@
         <v>1</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H91">
         <f>E91*VALUE(LEFT(G91, FIND(":", G91)-1))</f>
@@ -5037,7 +5064,7 @@
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H92">
         <f>E92*VALUE(LEFT(G92, FIND(":", G92)-1))</f>
@@ -5063,10 +5090,10 @@
         <v>1</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H93">
         <f>E93*VALUE(LEFT(G93, FIND(":", G93)-1))</f>
@@ -5094,10 +5121,10 @@
         <v>1</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H94">
         <f>E94*VALUE(LEFT(G94, FIND(":", G94)-1))</f>
@@ -5123,10 +5150,10 @@
         <v>1</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H95">
         <f>E95*VALUE(LEFT(G95, FIND(":", G95)-1))</f>
@@ -5152,10 +5179,10 @@
         <v>1</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H96">
         <f>E96*VALUE(LEFT(G96, FIND(":", G96)-1))</f>
@@ -5181,10 +5208,10 @@
         <v>1</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H97">
         <f>E97*VALUE(LEFT(G97, FIND(":", G97)-1))</f>
@@ -5210,10 +5237,10 @@
         <v>1</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H98">
         <f>E98*VALUE(LEFT(G98, FIND(":", G98)-1))</f>
@@ -5239,7 +5266,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H99">
         <f>E99*VALUE(LEFT(G99, FIND(":", G99)-1))</f>
@@ -5265,10 +5292,10 @@
         <v>1</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H100">
         <f>E100*VALUE(LEFT(G100, FIND(":", G100)-1))</f>
@@ -5296,10 +5323,10 @@
         <v>1</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H101">
         <f>E101*VALUE(LEFT(G101, FIND(":", G101)-1))</f>
@@ -5325,7 +5352,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H102">
         <f>E102*VALUE(LEFT(G102, FIND(":", G102)-1))</f>
@@ -5351,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H103">
         <f>E103*VALUE(LEFT(G103, FIND(":", G103)-1))</f>
@@ -5377,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H104">
         <f>E104*VALUE(LEFT(G104, FIND(":", G104)-1))</f>
@@ -5403,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H105">
         <f>E105*VALUE(LEFT(G105, FIND(":", G105)-1))</f>
@@ -5429,7 +5456,7 @@
         <v>1</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H106">
         <f>E106*VALUE(LEFT(G106, FIND(":", G106)-1))</f>
@@ -5459,10 +5486,10 @@
         <v>1</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H107">
         <f>E107*VALUE(LEFT(G107, FIND(":", G107)-1))</f>
@@ -5488,10 +5515,10 @@
         <v>1</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H108">
         <f>E108*VALUE(LEFT(G108, FIND(":", G108)-1))</f>
@@ -5517,10 +5544,10 @@
         <v>1</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H109">
         <f>E109*VALUE(LEFT(G109, FIND(":", G109)-1))</f>
@@ -5546,10 +5573,10 @@
         <v>1</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H110">
         <f>E110*VALUE(LEFT(G110, FIND(":", G110)-1))</f>
@@ -5575,10 +5602,10 @@
         <v>1</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H111">
         <f>E111*VALUE(LEFT(G111, FIND(":", G111)-1))</f>
@@ -5604,10 +5631,10 @@
         <v>1</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H112">
         <f>E112*VALUE(LEFT(G112, FIND(":", G112)-1))</f>
@@ -5633,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H113">
         <f>E113*VALUE(LEFT(G113, FIND(":", G113)-1))</f>
@@ -5661,10 +5688,10 @@
         <v>1</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H114">
         <f>E114*VALUE(LEFT(G114, FIND(":", G114)-1))</f>
@@ -5690,10 +5717,10 @@
         <v>1</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H115">
         <f>E115*VALUE(LEFT(G115, FIND(":", G115)-1))</f>
@@ -5719,7 +5746,7 @@
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="H116">
         <f>E116*VALUE(LEFT(G116, FIND(":", G116)-1))</f>
@@ -5745,7 +5772,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H117">
         <f>E117*VALUE(LEFT(G117, FIND(":", G117)-1))</f>
@@ -5771,7 +5798,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H118">
         <f>E118*VALUE(LEFT(G118, FIND(":", G118)-1))</f>
@@ -5797,10 +5824,10 @@
         <v>1</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H119">
         <f>E119*VALUE(LEFT(G119, FIND(":", G119)-1))</f>
@@ -5826,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H120">
         <f>E120*VALUE(LEFT(G120, FIND(":", G120)-1))</f>
@@ -5854,7 +5881,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H121">
         <f>E121*VALUE(LEFT(G121, FIND(":", G121)-1))</f>
@@ -5880,7 +5907,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H122">
         <f>E122*VALUE(LEFT(G122, FIND(":", G122)-1))</f>
@@ -5906,7 +5933,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H123">
         <f>E123*VALUE(LEFT(G123, FIND(":", G123)-1))</f>
@@ -5932,7 +5959,7 @@
         <v>1</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="H124">
         <f>E124*VALUE(LEFT(G124, FIND(":", G124)-1))</f>
@@ -5958,7 +5985,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H125">
         <f>E125*VALUE(LEFT(G125, FIND(":", G125)-1))</f>
@@ -5984,10 +6011,10 @@
         <v>1</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H126">
         <f>E126*VALUE(LEFT(G126, FIND(":", G126)-1))</f>
@@ -6013,10 +6040,10 @@
         <v>1</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H127">
         <f>E127*VALUE(LEFT(G127, FIND(":", G127)-1))</f>
@@ -6042,7 +6069,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H128">
         <f>E128*VALUE(LEFT(G128, FIND(":", G128)-1))</f>
@@ -6068,7 +6095,7 @@
         <v>1</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="H129">
         <f>E129*VALUE(LEFT(G129, FIND(":", G129)-1))</f>
@@ -6096,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H130">
         <f>E130*VALUE(LEFT(G130, FIND(":", G130)-1))</f>
@@ -6122,10 +6149,10 @@
         <v>1</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H131">
         <f>E131*VALUE(LEFT(G131, FIND(":", G131)-1))</f>
@@ -6151,10 +6178,10 @@
         <v>1</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H132">
         <f>E132*VALUE(LEFT(G132, FIND(":", G132)-1))</f>
@@ -6180,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H133">
         <f>E133*VALUE(LEFT(G133, FIND(":", G133)-1))</f>
@@ -6206,7 +6233,7 @@
         <v>1</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H134">
         <f>E134*VALUE(LEFT(G134, FIND(":", G134)-1))</f>
@@ -6232,7 +6259,7 @@
         <v>0</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H135">
         <f>E135*VALUE(LEFT(G135, FIND(":", G135)-1))</f>
@@ -6258,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H136">
         <f>E136*VALUE(LEFT(G136, FIND(":", G136)-1))</f>
@@ -6326,10 +6353,10 @@
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G10">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,3: item 1 completed,5: items 1, and 2 completed,8: items 1, 2, and 3 completed,10: items 1, 2, 3, and 4 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G12">
       <formula1>"0: None"</formula1>
@@ -6614,7 +6641,7 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G106">
-      <formula1>"0: None,10: set goal thresholds for kpis and unit costs"</formula1>
+      <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G107">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
@@ -6644,7 +6671,7 @@
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G116">
-      <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [20%],6: Alerting in most tooling [60%],10: Alerting in all workflow tools [100%]"</formula1>
+      <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G117">
       <formula1>"0: None"</formula1>
@@ -6698,7 +6725,7 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G134">
-      <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [20%],6: Alerting in most tooling [60%],10: Alerting in all workflow tools [100%]"</formula1>
+      <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G135">
       <formula1>"0: None"</formula1>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="396">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -121,6 +121,9 @@
     <t>serial number</t>
   </si>
   <si>
+    <t>version</t>
+  </si>
+  <si>
     <t>weights</t>
   </si>
   <si>
@@ -956,6 +959,21 @@
   </si>
   <si>
     <t>022</t>
+  </si>
+  <si>
+    <t>0.7.0</t>
+  </si>
+  <si>
+    <t>1.7.0</t>
+  </si>
+  <si>
+    <t>0.8.0</t>
+  </si>
+  <si>
+    <t>0.5.0</t>
+  </si>
+  <si>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>* Select which teams or groups are in scope for the planned assessments
@@ -2590,30 +2608,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J136"/>
+  <dimension ref="A1:K136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="63" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="40.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.42578125" hidden="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.28515625" hidden="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="0" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.42578125" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.28515625" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>33</v>
@@ -2636,8 +2655,11 @@
       <c r="J1" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -2645,1185 +2667,1293 @@
         <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E2">
+        <v>179</v>
+      </c>
+      <c r="E2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F2" s="1">
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H2">
         <f>E2*VALUE(LEFT(G2, FIND(":", G2)-1))</f>
         <v>0</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>6</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E3">
+        <v>180</v>
+      </c>
+      <c r="E3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H3">
         <f>E3*VALUE(LEFT(G3, FIND(":", G3)-1))</f>
         <v>0</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E4">
+        <v>181</v>
+      </c>
+      <c r="E4" t="s">
+        <v>314</v>
+      </c>
+      <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H4">
         <f>E4*VALUE(LEFT(G4, FIND(":", G4)-1))</f>
         <v>0</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>6</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5">
+        <v>182</v>
+      </c>
+      <c r="E5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F5" s="1">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H5">
         <f>E5*VALUE(LEFT(G5, FIND(":", G5)-1))</f>
         <v>0</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>6</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E6">
+        <v>183</v>
+      </c>
+      <c r="E6" t="s">
+        <v>314</v>
+      </c>
+      <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H6">
         <f>E6*VALUE(LEFT(G6, FIND(":", G6)-1))</f>
         <v>0</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>6</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E7">
+        <v>184</v>
+      </c>
+      <c r="E7" t="s">
+        <v>316</v>
+      </c>
+      <c r="F7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="H7">
         <f>E7*VALUE(LEFT(G7, FIND(":", G7)-1))</f>
         <v>0</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>6</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E8">
+        <v>185</v>
+      </c>
+      <c r="E8" t="s">
+        <v>316</v>
+      </c>
+      <c r="F8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H8">
         <f>E8*VALUE(LEFT(G8, FIND(":", G8)-1))</f>
         <v>0</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>6</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9">
+        <v>186</v>
+      </c>
+      <c r="E9" t="s">
+        <v>316</v>
+      </c>
+      <c r="F9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H9">
         <f>E9*VALUE(LEFT(G9, FIND(":", G9)-1))</f>
         <v>0</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>6</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10">
+        <v>187</v>
+      </c>
+      <c r="E10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H10">
         <f>E10*VALUE(LEFT(G10, FIND(":", G10)-1))</f>
         <v>0</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>6</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>317</v>
+        <v>188</v>
+      </c>
+      <c r="E11" t="s">
+        <v>314</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H11">
         <f>E11*VALUE(LEFT(G11, FIND(":", G11)-1))</f>
         <v>0</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>6</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E12">
+        <v>189</v>
+      </c>
+      <c r="E12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H12">
         <f>E12*VALUE(LEFT(G12, FIND(":", G12)-1))</f>
         <v>0</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>6</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:11">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E13">
+        <v>190</v>
+      </c>
+      <c r="E13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H13">
         <f>E13*VALUE(LEFT(G13, FIND(":", G13)-1))</f>
         <v>0</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>6</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:11">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E14">
+        <v>191</v>
+      </c>
+      <c r="E14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H14">
         <f>E14*VALUE(LEFT(G14, FIND(":", G14)-1))</f>
         <v>0</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>6</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:11">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E15">
+        <v>192</v>
+      </c>
+      <c r="E15" t="s">
+        <v>315</v>
+      </c>
+      <c r="F15" s="1">
         <v>1</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="G15" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H15">
         <f>E15*VALUE(LEFT(G15, FIND(":", G15)-1))</f>
         <v>0</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>6</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:11">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E16">
+        <v>193</v>
+      </c>
+      <c r="E16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H16">
         <f>E16*VALUE(LEFT(G16, FIND(":", G16)-1))</f>
         <v>0</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>6</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:11">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E17">
+        <v>194</v>
+      </c>
+      <c r="E17" t="s">
+        <v>315</v>
+      </c>
+      <c r="F17" s="1">
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="H17">
         <f>E17*VALUE(LEFT(G17, FIND(":", G17)-1))</f>
         <v>0</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>6</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:11">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E18">
+        <v>195</v>
+      </c>
+      <c r="E18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H18">
         <f>E18*VALUE(LEFT(G18, FIND(":", G18)-1))</f>
         <v>0</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>6</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:11">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E19">
+        <v>196</v>
+      </c>
+      <c r="E19" t="s">
+        <v>314</v>
+      </c>
+      <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H19">
         <f>E19*VALUE(LEFT(G19, FIND(":", G19)-1))</f>
         <v>0</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>6</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:11">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="E20">
+        <v>197</v>
+      </c>
+      <c r="E20" t="s">
+        <v>314</v>
+      </c>
+      <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H20">
         <f>E20*VALUE(LEFT(G20, FIND(":", G20)-1))</f>
         <v>0</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>6</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:11">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E21">
+        <v>198</v>
+      </c>
+      <c r="E21" t="s">
+        <v>314</v>
+      </c>
+      <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H21">
         <f>E21*VALUE(LEFT(G21, FIND(":", G21)-1))</f>
         <v>0</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>6</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:11">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E22">
+        <v>199</v>
+      </c>
+      <c r="E22" t="s">
+        <v>314</v>
+      </c>
+      <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H22">
         <f>E22*VALUE(LEFT(G22, FIND(":", G22)-1))</f>
         <v>0</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>6</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:11">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E23">
+        <v>200</v>
+      </c>
+      <c r="E23" t="s">
+        <v>314</v>
+      </c>
+      <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H23">
         <f>E23*VALUE(LEFT(G23, FIND(":", G23)-1))</f>
         <v>0</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>6</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E24">
+        <v>201</v>
+      </c>
+      <c r="E24" t="s">
+        <v>315</v>
+      </c>
+      <c r="F24" s="1">
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="H24">
         <f>E24*VALUE(LEFT(G24, FIND(":", G24)-1))</f>
         <v>0</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>6</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:11">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E25">
+        <v>202</v>
+      </c>
+      <c r="E25" t="s">
+        <v>314</v>
+      </c>
+      <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H25">
         <f>E25*VALUE(LEFT(G25, FIND(":", G25)-1))</f>
         <v>0</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>6</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:11">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E26">
+        <v>203</v>
+      </c>
+      <c r="E26" t="s">
+        <v>315</v>
+      </c>
+      <c r="F26" s="1">
         <v>1</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="G26" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H26">
         <f>E26*VALUE(LEFT(G26, FIND(":", G26)-1))</f>
         <v>0</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>6</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:11">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E27">
+        <v>204</v>
+      </c>
+      <c r="E27" t="s">
+        <v>314</v>
+      </c>
+      <c r="F27" s="1">
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H27">
         <f>E27*VALUE(LEFT(G27, FIND(":", G27)-1))</f>
         <v>0</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>6</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:11">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E28">
+        <v>205</v>
+      </c>
+      <c r="E28" t="s">
+        <v>314</v>
+      </c>
+      <c r="F28" s="1">
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H28">
         <f>E28*VALUE(LEFT(G28, FIND(":", G28)-1))</f>
         <v>0</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>6</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:11">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E29">
+        <v>206</v>
+      </c>
+      <c r="E29" t="s">
+        <v>314</v>
+      </c>
+      <c r="F29" s="1">
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H29">
         <f>E29*VALUE(LEFT(G29, FIND(":", G29)-1))</f>
         <v>0</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>6</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:11">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E30">
+        <v>207</v>
+      </c>
+      <c r="E30" t="s">
+        <v>314</v>
+      </c>
+      <c r="F30" s="1">
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H30">
         <f>E30*VALUE(LEFT(G30, FIND(":", G30)-1))</f>
         <v>0</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>6</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:11">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E31">
+        <v>208</v>
+      </c>
+      <c r="E31" t="s">
+        <v>314</v>
+      </c>
+      <c r="F31" s="1">
         <v>0</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H31">
         <f>E31*VALUE(LEFT(G31, FIND(":", G31)-1))</f>
         <v>0</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>6</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:11">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E32">
+        <v>209</v>
+      </c>
+      <c r="E32" t="s">
+        <v>314</v>
+      </c>
+      <c r="F32" s="1">
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H32">
         <f>E32*VALUE(LEFT(G32, FIND(":", G32)-1))</f>
         <v>0</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>6</v>
       </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:11">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E33">
+        <v>210</v>
+      </c>
+      <c r="E33" t="s">
+        <v>314</v>
+      </c>
+      <c r="F33" s="1">
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H33">
         <f>E33*VALUE(LEFT(G33, FIND(":", G33)-1))</f>
         <v>0</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>6</v>
       </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:11">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E34">
+        <v>211</v>
+      </c>
+      <c r="E34" t="s">
+        <v>314</v>
+      </c>
+      <c r="F34" s="1">
         <v>0</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H34">
         <f>E34*VALUE(LEFT(G34, FIND(":", G34)-1))</f>
         <v>0</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>6</v>
       </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:11">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E35">
+        <v>212</v>
+      </c>
+      <c r="E35" t="s">
+        <v>314</v>
+      </c>
+      <c r="F35" s="1">
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H35">
         <f>E35*VALUE(LEFT(G35, FIND(":", G35)-1))</f>
         <v>0</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>6</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:11">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E36">
+        <v>213</v>
+      </c>
+      <c r="E36" t="s">
+        <v>315</v>
+      </c>
+      <c r="F36" s="1">
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="H36">
         <f>E36*VALUE(LEFT(G36, FIND(":", G36)-1))</f>
         <v>0</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>6</v>
       </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:11">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E37">
+        <v>214</v>
+      </c>
+      <c r="E37" t="s">
+        <v>314</v>
+      </c>
+      <c r="F37" s="1">
         <v>0</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H37">
         <f>E37*VALUE(LEFT(G37, FIND(":", G37)-1))</f>
         <v>0</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>6</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:11">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E38">
+        <v>215</v>
+      </c>
+      <c r="E38" t="s">
+        <v>314</v>
+      </c>
+      <c r="F38" s="1">
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H38">
         <f>E38*VALUE(LEFT(G38, FIND(":", G38)-1))</f>
         <v>0</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>6</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:11">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E39">
+        <v>216</v>
+      </c>
+      <c r="E39" t="s">
+        <v>315</v>
+      </c>
+      <c r="F39" s="1">
         <v>1</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="H39">
         <f>E39*VALUE(LEFT(G39, FIND(":", G39)-1))</f>
         <v>0</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>6</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:11">
       <c r="A40" s="2"/>
       <c r="B40" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E40">
+        <v>217</v>
+      </c>
+      <c r="E40" t="s">
+        <v>314</v>
+      </c>
+      <c r="F40" s="1">
         <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H40">
         <f>E40*VALUE(LEFT(G40, FIND(":", G40)-1))</f>
         <v>0</v>
       </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>6</v>
       </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:11">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E41">
+        <v>218</v>
+      </c>
+      <c r="E41" t="s">
+        <v>314</v>
+      </c>
+      <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H41">
         <f>E41*VALUE(LEFT(G41, FIND(":", G41)-1))</f>
         <v>0</v>
       </c>
-      <c r="I41" t="s">
+      <c r="J41" t="s">
         <v>6</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:11">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E42">
+        <v>219</v>
+      </c>
+      <c r="E42" t="s">
+        <v>315</v>
+      </c>
+      <c r="F42" s="1">
         <v>1</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="G42" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H42">
         <f>E42*VALUE(LEFT(G42, FIND(":", G42)-1))</f>
         <v>0</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>6</v>
       </c>
-      <c r="J42" t="s">
+      <c r="K42" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:11">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E43">
+        <v>220</v>
+      </c>
+      <c r="E43" t="s">
+        <v>314</v>
+      </c>
+      <c r="F43" s="1">
         <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H43">
         <f>E43*VALUE(LEFT(G43, FIND(":", G43)-1))</f>
         <v>0</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>6</v>
       </c>
-      <c r="J43" t="s">
+      <c r="K43" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:11">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E44">
+        <v>221</v>
+      </c>
+      <c r="E44" t="s">
+        <v>314</v>
+      </c>
+      <c r="F44" s="1">
         <v>0</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H44">
         <f>E44*VALUE(LEFT(G44, FIND(":", G44)-1))</f>
         <v>0</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>6</v>
       </c>
-      <c r="J44" t="s">
+      <c r="K44" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:11">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E45">
+        <v>222</v>
+      </c>
+      <c r="E45" t="s">
+        <v>314</v>
+      </c>
+      <c r="F45" s="1">
         <v>0</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H45">
         <f>E45*VALUE(LEFT(G45, FIND(":", G45)-1))</f>
         <v>0</v>
       </c>
-      <c r="I45" t="s">
+      <c r="J45" t="s">
         <v>6</v>
       </c>
-      <c r="J45" t="s">
+      <c r="K45" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:11">
       <c r="A46" s="2" t="s">
         <v>7</v>
       </c>
@@ -3831,797 +3961,881 @@
         <v>13</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E46">
+        <v>223</v>
+      </c>
+      <c r="E46" t="s">
+        <v>315</v>
+      </c>
+      <c r="F46" s="1">
         <v>1</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="H46">
         <f>E46*VALUE(LEFT(G46, FIND(":", G46)-1))</f>
         <v>0</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>7</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:11">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E47">
+        <v>224</v>
+      </c>
+      <c r="E47" t="s">
+        <v>315</v>
+      </c>
+      <c r="F47" s="1">
         <v>1</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="G47" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H47">
         <f>E47*VALUE(LEFT(G47, FIND(":", G47)-1))</f>
         <v>0</v>
       </c>
-      <c r="I47" t="s">
+      <c r="J47" t="s">
         <v>7</v>
       </c>
-      <c r="J47" t="s">
+      <c r="K47" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:11">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E48">
+        <v>225</v>
+      </c>
+      <c r="E48" t="s">
+        <v>315</v>
+      </c>
+      <c r="F48" s="1">
         <v>1</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="H48">
         <f>E48*VALUE(LEFT(G48, FIND(":", G48)-1))</f>
         <v>0</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>7</v>
       </c>
-      <c r="J48" t="s">
+      <c r="K48" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:11">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E49">
+        <v>226</v>
+      </c>
+      <c r="E49" t="s">
+        <v>314</v>
+      </c>
+      <c r="F49" s="1">
         <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H49">
         <f>E49*VALUE(LEFT(G49, FIND(":", G49)-1))</f>
         <v>0</v>
       </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>7</v>
       </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:11">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E50">
+        <v>227</v>
+      </c>
+      <c r="E50" t="s">
+        <v>314</v>
+      </c>
+      <c r="F50" s="1">
         <v>0</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H50">
         <f>E50*VALUE(LEFT(G50, FIND(":", G50)-1))</f>
         <v>0</v>
       </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>7</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:11">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E51">
+        <v>228</v>
+      </c>
+      <c r="E51" t="s">
+        <v>314</v>
+      </c>
+      <c r="F51" s="1">
         <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H51">
         <f>E51*VALUE(LEFT(G51, FIND(":", G51)-1))</f>
         <v>0</v>
       </c>
-      <c r="I51" t="s">
+      <c r="J51" t="s">
         <v>7</v>
       </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:11">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E52">
+        <v>229</v>
+      </c>
+      <c r="E52" t="s">
+        <v>317</v>
+      </c>
+      <c r="F52" s="1">
         <v>0</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H52">
         <f>E52*VALUE(LEFT(G52, FIND(":", G52)-1))</f>
         <v>0</v>
       </c>
-      <c r="I52" t="s">
+      <c r="J52" t="s">
         <v>7</v>
       </c>
-      <c r="J52" t="s">
+      <c r="K52" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:11">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E53">
+        <v>230</v>
+      </c>
+      <c r="E53" t="s">
+        <v>317</v>
+      </c>
+      <c r="F53" s="1">
         <v>0</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H53">
         <f>E53*VALUE(LEFT(G53, FIND(":", G53)-1))</f>
         <v>0</v>
       </c>
-      <c r="I53" t="s">
+      <c r="J53" t="s">
         <v>7</v>
       </c>
-      <c r="J53" t="s">
+      <c r="K53" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:11">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="E54">
+        <v>231</v>
+      </c>
+      <c r="E54" t="s">
+        <v>317</v>
+      </c>
+      <c r="F54" s="1">
         <v>0</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H54">
         <f>E54*VALUE(LEFT(G54, FIND(":", G54)-1))</f>
         <v>0</v>
       </c>
-      <c r="I54" t="s">
+      <c r="J54" t="s">
         <v>7</v>
       </c>
-      <c r="J54" t="s">
+      <c r="K54" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:11">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E55">
+        <v>232</v>
+      </c>
+      <c r="E55" t="s">
+        <v>317</v>
+      </c>
+      <c r="F55" s="1">
         <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H55">
         <f>E55*VALUE(LEFT(G55, FIND(":", G55)-1))</f>
         <v>0</v>
       </c>
-      <c r="I55" t="s">
+      <c r="J55" t="s">
         <v>7</v>
       </c>
-      <c r="J55" t="s">
+      <c r="K55" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:11">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="E56">
+        <v>233</v>
+      </c>
+      <c r="E56" t="s">
+        <v>317</v>
+      </c>
+      <c r="F56" s="1">
         <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H56">
         <f>E56*VALUE(LEFT(G56, FIND(":", G56)-1))</f>
         <v>0</v>
       </c>
-      <c r="I56" t="s">
+      <c r="J56" t="s">
         <v>7</v>
       </c>
-      <c r="J56" t="s">
+      <c r="K56" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:11">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E57">
+        <v>234</v>
+      </c>
+      <c r="E57" t="s">
+        <v>317</v>
+      </c>
+      <c r="F57" s="1">
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H57">
         <f>E57*VALUE(LEFT(G57, FIND(":", G57)-1))</f>
         <v>0</v>
       </c>
-      <c r="I57" t="s">
+      <c r="J57" t="s">
         <v>7</v>
       </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:11">
       <c r="A58" s="2"/>
       <c r="B58" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E58">
+        <v>235</v>
+      </c>
+      <c r="E58" t="s">
+        <v>315</v>
+      </c>
+      <c r="F58" s="1">
         <v>1</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H58">
         <f>E58*VALUE(LEFT(G58, FIND(":", G58)-1))</f>
         <v>0</v>
       </c>
-      <c r="I58" t="s">
+      <c r="J58" t="s">
         <v>7</v>
       </c>
-      <c r="J58" t="s">
+      <c r="K58" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:11">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E59">
+        <v>236</v>
+      </c>
+      <c r="E59" t="s">
+        <v>314</v>
+      </c>
+      <c r="F59" s="1">
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H59">
         <f>E59*VALUE(LEFT(G59, FIND(":", G59)-1))</f>
         <v>0</v>
       </c>
-      <c r="I59" t="s">
+      <c r="J59" t="s">
         <v>7</v>
       </c>
-      <c r="J59" t="s">
+      <c r="K59" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:11">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E60">
+        <v>237</v>
+      </c>
+      <c r="E60" t="s">
+        <v>314</v>
+      </c>
+      <c r="F60" s="1">
         <v>0</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H60">
         <f>E60*VALUE(LEFT(G60, FIND(":", G60)-1))</f>
         <v>0</v>
       </c>
-      <c r="I60" t="s">
+      <c r="J60" t="s">
         <v>7</v>
       </c>
-      <c r="J60" t="s">
+      <c r="K60" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:11">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E61">
+        <v>238</v>
+      </c>
+      <c r="E61" t="s">
+        <v>315</v>
+      </c>
+      <c r="F61" s="1">
         <v>1</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="H61">
         <f>E61*VALUE(LEFT(G61, FIND(":", G61)-1))</f>
         <v>0</v>
       </c>
-      <c r="I61" t="s">
+      <c r="J61" t="s">
         <v>7</v>
       </c>
-      <c r="J61" t="s">
+      <c r="K61" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:11">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E62">
+        <v>239</v>
+      </c>
+      <c r="E62" t="s">
+        <v>314</v>
+      </c>
+      <c r="F62" s="1">
         <v>0</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H62">
         <f>E62*VALUE(LEFT(G62, FIND(":", G62)-1))</f>
         <v>0</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62" t="s">
         <v>7</v>
       </c>
-      <c r="J62" t="s">
+      <c r="K62" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:11">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E63">
+        <v>240</v>
+      </c>
+      <c r="E63" t="s">
+        <v>314</v>
+      </c>
+      <c r="F63" s="1">
         <v>0</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H63">
         <f>E63*VALUE(LEFT(G63, FIND(":", G63)-1))</f>
         <v>0</v>
       </c>
-      <c r="I63" t="s">
+      <c r="J63" t="s">
         <v>7</v>
       </c>
-      <c r="J63" t="s">
+      <c r="K63" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:11">
       <c r="A64" s="2"/>
       <c r="B64" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E64">
+        <v>241</v>
+      </c>
+      <c r="E64" t="s">
+        <v>315</v>
+      </c>
+      <c r="F64" s="1">
         <v>1</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="H64">
         <f>E64*VALUE(LEFT(G64, FIND(":", G64)-1))</f>
         <v>0</v>
       </c>
-      <c r="I64" t="s">
+      <c r="J64" t="s">
         <v>7</v>
       </c>
-      <c r="J64" t="s">
+      <c r="K64" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:11">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E65">
+        <v>242</v>
+      </c>
+      <c r="E65" t="s">
+        <v>315</v>
+      </c>
+      <c r="F65" s="1">
         <v>1</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="H65">
         <f>E65*VALUE(LEFT(G65, FIND(":", G65)-1))</f>
         <v>0</v>
       </c>
-      <c r="I65" t="s">
+      <c r="J65" t="s">
         <v>7</v>
       </c>
-      <c r="J65" t="s">
+      <c r="K65" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:11">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E66">
+        <v>243</v>
+      </c>
+      <c r="E66" t="s">
+        <v>314</v>
+      </c>
+      <c r="F66" s="1">
         <v>0</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H66">
         <f>E66*VALUE(LEFT(G66, FIND(":", G66)-1))</f>
         <v>0</v>
       </c>
-      <c r="I66" t="s">
+      <c r="J66" t="s">
         <v>7</v>
       </c>
-      <c r="J66" t="s">
+      <c r="K66" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:11">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E67">
+        <v>244</v>
+      </c>
+      <c r="E67" t="s">
+        <v>314</v>
+      </c>
+      <c r="F67" s="1">
         <v>0</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H67">
         <f>E67*VALUE(LEFT(G67, FIND(":", G67)-1))</f>
         <v>0</v>
       </c>
-      <c r="I67" t="s">
+      <c r="J67" t="s">
         <v>7</v>
       </c>
-      <c r="J67" t="s">
+      <c r="K67" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:11">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E68">
+        <v>245</v>
+      </c>
+      <c r="E68" t="s">
+        <v>314</v>
+      </c>
+      <c r="F68" s="1">
         <v>0</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H68">
         <f>E68*VALUE(LEFT(G68, FIND(":", G68)-1))</f>
         <v>0</v>
       </c>
-      <c r="I68" t="s">
+      <c r="J68" t="s">
         <v>7</v>
       </c>
-      <c r="J68" t="s">
+      <c r="K68" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:11">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E69">
+        <v>246</v>
+      </c>
+      <c r="E69" t="s">
+        <v>315</v>
+      </c>
+      <c r="F69" s="1">
         <v>1</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="G69" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H69">
         <f>E69*VALUE(LEFT(G69, FIND(":", G69)-1))</f>
         <v>0</v>
       </c>
-      <c r="I69" t="s">
+      <c r="J69" t="s">
         <v>7</v>
       </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:11">
       <c r="A70" s="2"/>
       <c r="B70" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E70">
+        <v>247</v>
+      </c>
+      <c r="E70" t="s">
+        <v>314</v>
+      </c>
+      <c r="F70" s="1">
         <v>0</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H70">
         <f>E70*VALUE(LEFT(G70, FIND(":", G70)-1))</f>
         <v>0</v>
       </c>
-      <c r="I70" t="s">
+      <c r="J70" t="s">
         <v>7</v>
       </c>
-      <c r="J70" t="s">
+      <c r="K70" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:11">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E71">
+        <v>248</v>
+      </c>
+      <c r="E71" t="s">
+        <v>315</v>
+      </c>
+      <c r="F71" s="1">
         <v>1</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="H71">
         <f>E71*VALUE(LEFT(G71, FIND(":", G71)-1))</f>
         <v>0</v>
       </c>
-      <c r="I71" t="s">
+      <c r="J71" t="s">
         <v>7</v>
       </c>
-      <c r="J71" t="s">
+      <c r="K71" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:11">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E72">
+        <v>249</v>
+      </c>
+      <c r="E72" t="s">
+        <v>315</v>
+      </c>
+      <c r="F72" s="1">
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H72">
         <f>E72*VALUE(LEFT(G72, FIND(":", G72)-1))</f>
         <v>0</v>
       </c>
-      <c r="I72" t="s">
+      <c r="J72" t="s">
         <v>7</v>
       </c>
-      <c r="J72" t="s">
+      <c r="K72" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:11">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E73">
+        <v>250</v>
+      </c>
+      <c r="E73" t="s">
+        <v>314</v>
+      </c>
+      <c r="F73" s="1">
         <v>0</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H73">
         <f>E73*VALUE(LEFT(G73, FIND(":", G73)-1))</f>
         <v>0</v>
       </c>
-      <c r="I73" t="s">
+      <c r="J73" t="s">
         <v>7</v>
       </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:11">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E74">
+        <v>251</v>
+      </c>
+      <c r="E74" t="s">
+        <v>314</v>
+      </c>
+      <c r="F74" s="1">
         <v>0</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H74">
         <f>E74*VALUE(LEFT(G74, FIND(":", G74)-1))</f>
         <v>0</v>
       </c>
-      <c r="I74" t="s">
+      <c r="J74" t="s">
         <v>7</v>
       </c>
-      <c r="J74" t="s">
+      <c r="K74" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:11">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E75">
+        <v>252</v>
+      </c>
+      <c r="E75" t="s">
+        <v>314</v>
+      </c>
+      <c r="F75" s="1">
         <v>0</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H75">
         <f>E75*VALUE(LEFT(G75, FIND(":", G75)-1))</f>
         <v>0</v>
       </c>
-      <c r="I75" t="s">
+      <c r="J75" t="s">
         <v>7</v>
       </c>
-      <c r="J75" t="s">
+      <c r="K75" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:11">
       <c r="A76" s="2" t="s">
         <v>8</v>
       </c>
@@ -4629,847 +4843,910 @@
         <v>14</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E76">
+        <v>253</v>
+      </c>
+      <c r="E76" t="s">
+        <v>314</v>
+      </c>
+      <c r="F76" s="1">
         <v>0</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H76">
         <f>E76*VALUE(LEFT(G76, FIND(":", G76)-1))</f>
         <v>0</v>
       </c>
-      <c r="I76" t="s">
+      <c r="J76" t="s">
         <v>8</v>
       </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:11">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E77">
+        <v>254</v>
+      </c>
+      <c r="E77" t="s">
+        <v>314</v>
+      </c>
+      <c r="F77" s="1">
         <v>0</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H77">
         <f>E77*VALUE(LEFT(G77, FIND(":", G77)-1))</f>
         <v>0</v>
       </c>
-      <c r="I77" t="s">
+      <c r="J77" t="s">
         <v>8</v>
       </c>
-      <c r="J77" t="s">
+      <c r="K77" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:11">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E78">
+        <v>255</v>
+      </c>
+      <c r="E78" t="s">
+        <v>314</v>
+      </c>
+      <c r="F78" s="1">
         <v>0</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H78">
         <f>E78*VALUE(LEFT(G78, FIND(":", G78)-1))</f>
         <v>0</v>
       </c>
-      <c r="I78" t="s">
+      <c r="J78" t="s">
         <v>8</v>
       </c>
-      <c r="J78" t="s">
+      <c r="K78" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:11">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="E79">
+        <v>256</v>
+      </c>
+      <c r="E79" t="s">
+        <v>314</v>
+      </c>
+      <c r="F79" s="1">
         <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H79">
         <f>E79*VALUE(LEFT(G79, FIND(":", G79)-1))</f>
         <v>0</v>
       </c>
-      <c r="I79" t="s">
+      <c r="J79" t="s">
         <v>8</v>
       </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:11">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E80">
+        <v>257</v>
+      </c>
+      <c r="E80" t="s">
+        <v>315</v>
+      </c>
+      <c r="F80" s="1">
         <v>1</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H80">
         <f>E80*VALUE(LEFT(G80, FIND(":", G80)-1))</f>
         <v>0</v>
       </c>
-      <c r="I80" t="s">
+      <c r="J80" t="s">
         <v>8</v>
       </c>
-      <c r="J80" t="s">
+      <c r="K80" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:11">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="E81">
+        <v>258</v>
+      </c>
+      <c r="E81" t="s">
+        <v>314</v>
+      </c>
+      <c r="F81" s="1">
         <v>0</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H81">
         <f>E81*VALUE(LEFT(G81, FIND(":", G81)-1))</f>
         <v>0</v>
       </c>
-      <c r="I81" t="s">
+      <c r="J81" t="s">
         <v>8</v>
       </c>
-      <c r="J81" t="s">
+      <c r="K81" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:11">
       <c r="A82" s="2"/>
       <c r="B82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E82">
+        <v>259</v>
+      </c>
+      <c r="E82" t="s">
+        <v>315</v>
+      </c>
+      <c r="F82" s="1">
         <v>1</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="H82">
         <f>E82*VALUE(LEFT(G82, FIND(":", G82)-1))</f>
         <v>0</v>
       </c>
-      <c r="I82" t="s">
+      <c r="J82" t="s">
         <v>8</v>
       </c>
-      <c r="J82" t="s">
+      <c r="K82" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:11">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E83">
+        <v>260</v>
+      </c>
+      <c r="E83" t="s">
+        <v>315</v>
+      </c>
+      <c r="F83" s="1">
         <v>1</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="H83">
         <f>E83*VALUE(LEFT(G83, FIND(":", G83)-1))</f>
         <v>0</v>
       </c>
-      <c r="I83" t="s">
+      <c r="J83" t="s">
         <v>8</v>
       </c>
-      <c r="J83" t="s">
+      <c r="K83" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:11">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E84">
+        <v>261</v>
+      </c>
+      <c r="E84" t="s">
+        <v>314</v>
+      </c>
+      <c r="F84" s="1">
         <v>0</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H84">
         <f>E84*VALUE(LEFT(G84, FIND(":", G84)-1))</f>
         <v>0</v>
       </c>
-      <c r="I84" t="s">
+      <c r="J84" t="s">
         <v>8</v>
       </c>
-      <c r="J84" t="s">
+      <c r="K84" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:11">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E85">
+        <v>262</v>
+      </c>
+      <c r="E85" t="s">
+        <v>314</v>
+      </c>
+      <c r="F85" s="1">
         <v>0</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H85">
         <f>E85*VALUE(LEFT(G85, FIND(":", G85)-1))</f>
         <v>0</v>
       </c>
-      <c r="I85" t="s">
+      <c r="J85" t="s">
         <v>8</v>
       </c>
-      <c r="J85" t="s">
+      <c r="K85" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:11">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E86">
+        <v>263</v>
+      </c>
+      <c r="E86" t="s">
+        <v>314</v>
+      </c>
+      <c r="F86" s="1">
         <v>0</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H86">
         <f>E86*VALUE(LEFT(G86, FIND(":", G86)-1))</f>
         <v>0</v>
       </c>
-      <c r="I86" t="s">
+      <c r="J86" t="s">
         <v>8</v>
       </c>
-      <c r="J86" t="s">
+      <c r="K86" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:11">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E87">
+        <v>264</v>
+      </c>
+      <c r="E87" t="s">
+        <v>314</v>
+      </c>
+      <c r="F87" s="1">
         <v>0</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H87">
         <f>E87*VALUE(LEFT(G87, FIND(":", G87)-1))</f>
         <v>0</v>
       </c>
-      <c r="I87" t="s">
+      <c r="J87" t="s">
         <v>8</v>
       </c>
-      <c r="J87" t="s">
+      <c r="K87" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:11">
       <c r="A88" s="2"/>
       <c r="B88" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="E88">
+        <v>265</v>
+      </c>
+      <c r="E88" t="s">
+        <v>314</v>
+      </c>
+      <c r="F88" s="1">
         <v>0</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H88">
         <f>E88*VALUE(LEFT(G88, FIND(":", G88)-1))</f>
         <v>0</v>
       </c>
-      <c r="I88" t="s">
+      <c r="J88" t="s">
         <v>8</v>
       </c>
-      <c r="J88" t="s">
+      <c r="K88" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:11">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="E89">
+        <v>266</v>
+      </c>
+      <c r="E89" t="s">
+        <v>315</v>
+      </c>
+      <c r="F89" s="1">
         <v>1</v>
       </c>
-      <c r="F89" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="G89" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H89">
         <f>E89*VALUE(LEFT(G89, FIND(":", G89)-1))</f>
         <v>0</v>
       </c>
-      <c r="I89" t="s">
+      <c r="J89" t="s">
         <v>8</v>
       </c>
-      <c r="J89" t="s">
+      <c r="K89" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:11">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="E90">
+        <v>267</v>
+      </c>
+      <c r="E90" t="s">
+        <v>315</v>
+      </c>
+      <c r="F90" s="1">
         <v>1</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H90">
         <f>E90*VALUE(LEFT(G90, FIND(":", G90)-1))</f>
         <v>0</v>
       </c>
-      <c r="I90" t="s">
+      <c r="J90" t="s">
         <v>8</v>
       </c>
-      <c r="J90" t="s">
+      <c r="K90" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:11">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E91">
+        <v>268</v>
+      </c>
+      <c r="E91" t="s">
+        <v>315</v>
+      </c>
+      <c r="F91" s="1">
         <v>1</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="G91" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H91">
         <f>E91*VALUE(LEFT(G91, FIND(":", G91)-1))</f>
         <v>0</v>
       </c>
-      <c r="I91" t="s">
+      <c r="J91" t="s">
         <v>8</v>
       </c>
-      <c r="J91" t="s">
+      <c r="K91" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:11">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="E92">
+        <v>269</v>
+      </c>
+      <c r="E92" t="s">
+        <v>315</v>
+      </c>
+      <c r="F92" s="1">
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H92">
         <f>E92*VALUE(LEFT(G92, FIND(":", G92)-1))</f>
         <v>0</v>
       </c>
-      <c r="I92" t="s">
+      <c r="J92" t="s">
         <v>8</v>
       </c>
-      <c r="J92" t="s">
+      <c r="K92" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:11">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="E93">
+        <v>270</v>
+      </c>
+      <c r="E93" t="s">
+        <v>315</v>
+      </c>
+      <c r="F93" s="1">
         <v>1</v>
       </c>
-      <c r="F93" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="G93" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H93">
         <f>E93*VALUE(LEFT(G93, FIND(":", G93)-1))</f>
         <v>0</v>
       </c>
-      <c r="I93" t="s">
+      <c r="J93" t="s">
         <v>8</v>
       </c>
-      <c r="J93" t="s">
+      <c r="K93" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:11">
       <c r="A94" s="2"/>
       <c r="B94" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="E94">
+        <v>271</v>
+      </c>
+      <c r="E94" t="s">
+        <v>316</v>
+      </c>
+      <c r="F94" s="1">
         <v>1</v>
       </c>
-      <c r="F94" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="G94" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H94">
         <f>E94*VALUE(LEFT(G94, FIND(":", G94)-1))</f>
         <v>0</v>
       </c>
-      <c r="I94" t="s">
+      <c r="J94" t="s">
         <v>8</v>
       </c>
-      <c r="J94" t="s">
+      <c r="K94" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:11">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E95">
+        <v>272</v>
+      </c>
+      <c r="E95" t="s">
+        <v>316</v>
+      </c>
+      <c r="F95" s="1">
         <v>1</v>
       </c>
-      <c r="F95" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="G95" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H95">
         <f>E95*VALUE(LEFT(G95, FIND(":", G95)-1))</f>
         <v>0</v>
       </c>
-      <c r="I95" t="s">
+      <c r="J95" t="s">
         <v>8</v>
       </c>
-      <c r="J95" t="s">
+      <c r="K95" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:11">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="E96">
+        <v>273</v>
+      </c>
+      <c r="E96" t="s">
+        <v>316</v>
+      </c>
+      <c r="F96" s="1">
         <v>1</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="G96" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H96">
         <f>E96*VALUE(LEFT(G96, FIND(":", G96)-1))</f>
         <v>0</v>
       </c>
-      <c r="I96" t="s">
+      <c r="J96" t="s">
         <v>8</v>
       </c>
-      <c r="J96" t="s">
+      <c r="K96" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:11">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E97">
+        <v>274</v>
+      </c>
+      <c r="E97" t="s">
+        <v>316</v>
+      </c>
+      <c r="F97" s="1">
         <v>1</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="G97" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H97">
         <f>E97*VALUE(LEFT(G97, FIND(":", G97)-1))</f>
         <v>0</v>
       </c>
-      <c r="I97" t="s">
+      <c r="J97" t="s">
         <v>8</v>
       </c>
-      <c r="J97" t="s">
+      <c r="K97" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:11">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="E98">
+        <v>275</v>
+      </c>
+      <c r="E98" t="s">
+        <v>315</v>
+      </c>
+      <c r="F98" s="1">
         <v>1</v>
       </c>
-      <c r="F98" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="G98" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H98">
         <f>E98*VALUE(LEFT(G98, FIND(":", G98)-1))</f>
         <v>0</v>
       </c>
-      <c r="I98" t="s">
+      <c r="J98" t="s">
         <v>8</v>
       </c>
-      <c r="J98" t="s">
+      <c r="K98" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:11">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="E99">
+        <v>276</v>
+      </c>
+      <c r="E99" t="s">
+        <v>315</v>
+      </c>
+      <c r="F99" s="1">
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H99">
         <f>E99*VALUE(LEFT(G99, FIND(":", G99)-1))</f>
         <v>0</v>
       </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>8</v>
       </c>
-      <c r="J99" t="s">
+      <c r="K99" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:11">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="E100">
+        <v>277</v>
+      </c>
+      <c r="E100" t="s">
+        <v>316</v>
+      </c>
+      <c r="F100" s="1">
         <v>1</v>
       </c>
-      <c r="F100" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="G100" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H100">
         <f>E100*VALUE(LEFT(G100, FIND(":", G100)-1))</f>
         <v>0</v>
       </c>
-      <c r="I100" t="s">
+      <c r="J100" t="s">
         <v>8</v>
       </c>
-      <c r="J100" t="s">
+      <c r="K100" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:11">
       <c r="A101" s="2"/>
       <c r="B101" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="E101">
+        <v>278</v>
+      </c>
+      <c r="E101" t="s">
+        <v>315</v>
+      </c>
+      <c r="F101" s="1">
         <v>1</v>
       </c>
-      <c r="F101" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="G101" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H101">
         <f>E101*VALUE(LEFT(G101, FIND(":", G101)-1))</f>
         <v>0</v>
       </c>
-      <c r="I101" t="s">
+      <c r="J101" t="s">
         <v>8</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:11">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E102">
+        <v>279</v>
+      </c>
+      <c r="E102" t="s">
+        <v>314</v>
+      </c>
+      <c r="F102" s="1">
         <v>0</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H102">
         <f>E102*VALUE(LEFT(G102, FIND(":", G102)-1))</f>
         <v>0</v>
       </c>
-      <c r="I102" t="s">
+      <c r="J102" t="s">
         <v>8</v>
       </c>
-      <c r="J102" t="s">
+      <c r="K102" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:11">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E103">
+        <v>280</v>
+      </c>
+      <c r="E103" t="s">
+        <v>314</v>
+      </c>
+      <c r="F103" s="1">
         <v>0</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H103">
         <f>E103*VALUE(LEFT(G103, FIND(":", G103)-1))</f>
         <v>0</v>
       </c>
-      <c r="I103" t="s">
+      <c r="J103" t="s">
         <v>8</v>
       </c>
-      <c r="J103" t="s">
+      <c r="K103" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:11">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E104">
+        <v>281</v>
+      </c>
+      <c r="E104" t="s">
+        <v>314</v>
+      </c>
+      <c r="F104" s="1">
         <v>0</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H104">
         <f>E104*VALUE(LEFT(G104, FIND(":", G104)-1))</f>
         <v>0</v>
       </c>
-      <c r="I104" t="s">
+      <c r="J104" t="s">
         <v>8</v>
       </c>
-      <c r="J104" t="s">
+      <c r="K104" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:11">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E105">
+        <v>282</v>
+      </c>
+      <c r="E105" t="s">
+        <v>314</v>
+      </c>
+      <c r="F105" s="1">
         <v>0</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H105">
         <f>E105*VALUE(LEFT(G105, FIND(":", G105)-1))</f>
         <v>0</v>
       </c>
-      <c r="I105" t="s">
+      <c r="J105" t="s">
         <v>8</v>
       </c>
-      <c r="J105" t="s">
+      <c r="K105" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:11">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="E106">
+        <v>283</v>
+      </c>
+      <c r="E106" t="s">
+        <v>315</v>
+      </c>
+      <c r="F106" s="1">
         <v>1</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H106">
         <f>E106*VALUE(LEFT(G106, FIND(":", G106)-1))</f>
         <v>0</v>
       </c>
-      <c r="I106" t="s">
+      <c r="J106" t="s">
         <v>8</v>
       </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:11">
       <c r="A107" s="2" t="s">
         <v>9</v>
       </c>
@@ -5477,824 +5754,875 @@
         <v>11</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E107">
+        <v>284</v>
+      </c>
+      <c r="E107" t="s">
+        <v>315</v>
+      </c>
+      <c r="F107" s="1">
         <v>1</v>
       </c>
-      <c r="F107" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="G107" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H107">
         <f>E107*VALUE(LEFT(G107, FIND(":", G107)-1))</f>
         <v>0</v>
       </c>
-      <c r="I107" t="s">
+      <c r="J107" t="s">
         <v>9</v>
       </c>
-      <c r="J107" t="s">
+      <c r="K107" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:11">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E108">
+        <v>285</v>
+      </c>
+      <c r="E108" t="s">
+        <v>315</v>
+      </c>
+      <c r="F108" s="1">
         <v>1</v>
       </c>
-      <c r="F108" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="G108" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H108">
         <f>E108*VALUE(LEFT(G108, FIND(":", G108)-1))</f>
         <v>0</v>
       </c>
-      <c r="I108" t="s">
+      <c r="J108" t="s">
         <v>9</v>
       </c>
-      <c r="J108" t="s">
+      <c r="K108" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:11">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="E109">
+        <v>286</v>
+      </c>
+      <c r="E109" t="s">
+        <v>315</v>
+      </c>
+      <c r="F109" s="1">
         <v>1</v>
       </c>
-      <c r="F109" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="G109" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H109">
         <f>E109*VALUE(LEFT(G109, FIND(":", G109)-1))</f>
         <v>0</v>
       </c>
-      <c r="I109" t="s">
+      <c r="J109" t="s">
         <v>9</v>
       </c>
-      <c r="J109" t="s">
+      <c r="K109" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:11">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E110">
+        <v>287</v>
+      </c>
+      <c r="E110" t="s">
+        <v>315</v>
+      </c>
+      <c r="F110" s="1">
         <v>1</v>
       </c>
-      <c r="F110" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="G110" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H110">
         <f>E110*VALUE(LEFT(G110, FIND(":", G110)-1))</f>
         <v>0</v>
       </c>
-      <c r="I110" t="s">
+      <c r="J110" t="s">
         <v>9</v>
       </c>
-      <c r="J110" t="s">
+      <c r="K110" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:11">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="E111">
+        <v>288</v>
+      </c>
+      <c r="E111" t="s">
+        <v>315</v>
+      </c>
+      <c r="F111" s="1">
         <v>1</v>
       </c>
-      <c r="F111" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="G111" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H111">
         <f>E111*VALUE(LEFT(G111, FIND(":", G111)-1))</f>
         <v>0</v>
       </c>
-      <c r="I111" t="s">
+      <c r="J111" t="s">
         <v>9</v>
       </c>
-      <c r="J111" t="s">
+      <c r="K111" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:11">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="E112">
+        <v>289</v>
+      </c>
+      <c r="E112" t="s">
+        <v>315</v>
+      </c>
+      <c r="F112" s="1">
         <v>1</v>
       </c>
-      <c r="F112" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="G112" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H112">
         <f>E112*VALUE(LEFT(G112, FIND(":", G112)-1))</f>
         <v>0</v>
       </c>
-      <c r="I112" t="s">
+      <c r="J112" t="s">
         <v>9</v>
       </c>
-      <c r="J112" t="s">
+      <c r="K112" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:11">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E113">
+        <v>290</v>
+      </c>
+      <c r="E113" t="s">
+        <v>314</v>
+      </c>
+      <c r="F113" s="1">
         <v>0</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H113">
         <f>E113*VALUE(LEFT(G113, FIND(":", G113)-1))</f>
         <v>0</v>
       </c>
-      <c r="I113" t="s">
+      <c r="J113" t="s">
         <v>9</v>
       </c>
-      <c r="J113" t="s">
+      <c r="K113" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:11">
       <c r="A114" s="2"/>
       <c r="B114" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="E114">
+        <v>291</v>
+      </c>
+      <c r="E114" t="s">
+        <v>315</v>
+      </c>
+      <c r="F114" s="1">
         <v>1</v>
       </c>
-      <c r="F114" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="G114" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H114">
         <f>E114*VALUE(LEFT(G114, FIND(":", G114)-1))</f>
         <v>0</v>
       </c>
-      <c r="I114" t="s">
+      <c r="J114" t="s">
         <v>9</v>
       </c>
-      <c r="J114" t="s">
+      <c r="K114" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:11">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E115">
+        <v>292</v>
+      </c>
+      <c r="E115" t="s">
+        <v>315</v>
+      </c>
+      <c r="F115" s="1">
         <v>1</v>
       </c>
-      <c r="F115" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="G115" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H115">
         <f>E115*VALUE(LEFT(G115, FIND(":", G115)-1))</f>
         <v>0</v>
       </c>
-      <c r="I115" t="s">
+      <c r="J115" t="s">
         <v>9</v>
       </c>
-      <c r="J115" t="s">
+      <c r="K115" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:11">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="E116">
+        <v>293</v>
+      </c>
+      <c r="E116" t="s">
+        <v>315</v>
+      </c>
+      <c r="F116" s="1">
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="H116">
         <f>E116*VALUE(LEFT(G116, FIND(":", G116)-1))</f>
         <v>0</v>
       </c>
-      <c r="I116" t="s">
+      <c r="J116" t="s">
         <v>9</v>
       </c>
-      <c r="J116" t="s">
+      <c r="K116" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:11">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="E117">
+        <v>294</v>
+      </c>
+      <c r="E117" t="s">
+        <v>314</v>
+      </c>
+      <c r="F117" s="1">
         <v>0</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H117">
         <f>E117*VALUE(LEFT(G117, FIND(":", G117)-1))</f>
         <v>0</v>
       </c>
-      <c r="I117" t="s">
+      <c r="J117" t="s">
         <v>9</v>
       </c>
-      <c r="J117" t="s">
+      <c r="K117" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:11">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="E118">
+        <v>295</v>
+      </c>
+      <c r="E118" t="s">
+        <v>314</v>
+      </c>
+      <c r="F118" s="1">
         <v>0</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H118">
         <f>E118*VALUE(LEFT(G118, FIND(":", G118)-1))</f>
         <v>0</v>
       </c>
-      <c r="I118" t="s">
+      <c r="J118" t="s">
         <v>9</v>
       </c>
-      <c r="J118" t="s">
+      <c r="K118" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:11">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E119">
+        <v>296</v>
+      </c>
+      <c r="E119" t="s">
+        <v>315</v>
+      </c>
+      <c r="F119" s="1">
         <v>1</v>
       </c>
-      <c r="F119" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="G119" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H119">
         <f>E119*VALUE(LEFT(G119, FIND(":", G119)-1))</f>
         <v>0</v>
       </c>
-      <c r="I119" t="s">
+      <c r="J119" t="s">
         <v>9</v>
       </c>
-      <c r="J119" t="s">
+      <c r="K119" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:11">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E120">
+        <v>297</v>
+      </c>
+      <c r="E120" t="s">
+        <v>314</v>
+      </c>
+      <c r="F120" s="1">
         <v>0</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H120">
         <f>E120*VALUE(LEFT(G120, FIND(":", G120)-1))</f>
         <v>0</v>
       </c>
-      <c r="I120" t="s">
+      <c r="J120" t="s">
         <v>9</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:11">
       <c r="A121" s="2"/>
       <c r="B121" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E121">
+        <v>298</v>
+      </c>
+      <c r="E121" t="s">
+        <v>314</v>
+      </c>
+      <c r="F121" s="1">
         <v>0</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H121">
         <f>E121*VALUE(LEFT(G121, FIND(":", G121)-1))</f>
         <v>0</v>
       </c>
-      <c r="I121" t="s">
+      <c r="J121" t="s">
         <v>9</v>
       </c>
-      <c r="J121" t="s">
+      <c r="K121" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:11">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="E122">
+        <v>299</v>
+      </c>
+      <c r="E122" t="s">
+        <v>314</v>
+      </c>
+      <c r="F122" s="1">
         <v>0</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H122">
         <f>E122*VALUE(LEFT(G122, FIND(":", G122)-1))</f>
         <v>0</v>
       </c>
-      <c r="I122" t="s">
+      <c r="J122" t="s">
         <v>9</v>
       </c>
-      <c r="J122" t="s">
+      <c r="K122" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:11">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E123">
+        <v>300</v>
+      </c>
+      <c r="E123" t="s">
+        <v>314</v>
+      </c>
+      <c r="F123" s="1">
         <v>0</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H123">
         <f>E123*VALUE(LEFT(G123, FIND(":", G123)-1))</f>
         <v>0</v>
       </c>
-      <c r="I123" t="s">
+      <c r="J123" t="s">
         <v>9</v>
       </c>
-      <c r="J123" t="s">
+      <c r="K123" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:11">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E124">
+        <v>301</v>
+      </c>
+      <c r="E124" t="s">
+        <v>315</v>
+      </c>
+      <c r="F124" s="1">
         <v>1</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H124">
         <f>E124*VALUE(LEFT(G124, FIND(":", G124)-1))</f>
         <v>0</v>
       </c>
-      <c r="I124" t="s">
+      <c r="J124" t="s">
         <v>9</v>
       </c>
-      <c r="J124" t="s">
+      <c r="K124" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:11">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E125">
+        <v>302</v>
+      </c>
+      <c r="E125" t="s">
+        <v>314</v>
+      </c>
+      <c r="F125" s="1">
         <v>0</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H125">
         <f>E125*VALUE(LEFT(G125, FIND(":", G125)-1))</f>
         <v>0</v>
       </c>
-      <c r="I125" t="s">
+      <c r="J125" t="s">
         <v>9</v>
       </c>
-      <c r="J125" t="s">
+      <c r="K125" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:11">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="E126">
+        <v>303</v>
+      </c>
+      <c r="E126" t="s">
+        <v>315</v>
+      </c>
+      <c r="F126" s="1">
         <v>1</v>
       </c>
-      <c r="F126" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="G126" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H126">
         <f>E126*VALUE(LEFT(G126, FIND(":", G126)-1))</f>
         <v>0</v>
       </c>
-      <c r="I126" t="s">
+      <c r="J126" t="s">
         <v>9</v>
       </c>
-      <c r="J126" t="s">
+      <c r="K126" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:11">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="E127">
+        <v>304</v>
+      </c>
+      <c r="E127" t="s">
+        <v>315</v>
+      </c>
+      <c r="F127" s="1">
         <v>1</v>
       </c>
-      <c r="F127" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="G127" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H127">
         <f>E127*VALUE(LEFT(G127, FIND(":", G127)-1))</f>
         <v>0</v>
       </c>
-      <c r="I127" t="s">
+      <c r="J127" t="s">
         <v>9</v>
       </c>
-      <c r="J127" t="s">
+      <c r="K127" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:11">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="E128">
+        <v>305</v>
+      </c>
+      <c r="E128" t="s">
+        <v>314</v>
+      </c>
+      <c r="F128" s="1">
         <v>0</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H128">
         <f>E128*VALUE(LEFT(G128, FIND(":", G128)-1))</f>
         <v>0</v>
       </c>
-      <c r="I128" t="s">
+      <c r="J128" t="s">
         <v>9</v>
       </c>
-      <c r="J128" t="s">
+      <c r="K128" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:11">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E129">
+        <v>306</v>
+      </c>
+      <c r="E129" t="s">
+        <v>318</v>
+      </c>
+      <c r="F129" s="1">
         <v>1</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H129">
         <f>E129*VALUE(LEFT(G129, FIND(":", G129)-1))</f>
         <v>0</v>
       </c>
-      <c r="I129" t="s">
+      <c r="J129" t="s">
         <v>9</v>
       </c>
-      <c r="J129" t="s">
+      <c r="K129" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:11">
       <c r="A130" s="2"/>
       <c r="B130" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="E130">
+        <v>307</v>
+      </c>
+      <c r="E130" t="s">
+        <v>314</v>
+      </c>
+      <c r="F130" s="1">
         <v>0</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H130">
         <f>E130*VALUE(LEFT(G130, FIND(":", G130)-1))</f>
         <v>0</v>
       </c>
-      <c r="I130" t="s">
+      <c r="J130" t="s">
         <v>9</v>
       </c>
-      <c r="J130" t="s">
+      <c r="K130" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:11">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E131">
+        <v>308</v>
+      </c>
+      <c r="E131" t="s">
+        <v>315</v>
+      </c>
+      <c r="F131" s="1">
         <v>1</v>
       </c>
-      <c r="F131" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="G131" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H131">
         <f>E131*VALUE(LEFT(G131, FIND(":", G131)-1))</f>
         <v>0</v>
       </c>
-      <c r="I131" t="s">
+      <c r="J131" t="s">
         <v>9</v>
       </c>
-      <c r="J131" t="s">
+      <c r="K131" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:11">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="E132">
+        <v>309</v>
+      </c>
+      <c r="E132" t="s">
+        <v>315</v>
+      </c>
+      <c r="F132" s="1">
         <v>1</v>
       </c>
-      <c r="F132" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="G132" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H132">
         <f>E132*VALUE(LEFT(G132, FIND(":", G132)-1))</f>
         <v>0</v>
       </c>
-      <c r="I132" t="s">
+      <c r="J132" t="s">
         <v>9</v>
       </c>
-      <c r="J132" t="s">
+      <c r="K132" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:11">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="E133">
+        <v>310</v>
+      </c>
+      <c r="E133" t="s">
+        <v>314</v>
+      </c>
+      <c r="F133" s="1">
         <v>0</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H133">
         <f>E133*VALUE(LEFT(G133, FIND(":", G133)-1))</f>
         <v>0</v>
       </c>
-      <c r="I133" t="s">
+      <c r="J133" t="s">
         <v>9</v>
       </c>
-      <c r="J133" t="s">
+      <c r="K133" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:11">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="E134">
+        <v>311</v>
+      </c>
+      <c r="E134" t="s">
+        <v>315</v>
+      </c>
+      <c r="F134" s="1">
         <v>1</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H134">
         <f>E134*VALUE(LEFT(G134, FIND(":", G134)-1))</f>
         <v>0</v>
       </c>
-      <c r="I134" t="s">
+      <c r="J134" t="s">
         <v>9</v>
       </c>
-      <c r="J134" t="s">
+      <c r="K134" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:11">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E135">
+        <v>312</v>
+      </c>
+      <c r="E135" t="s">
+        <v>314</v>
+      </c>
+      <c r="F135" s="1">
         <v>0</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H135">
         <f>E135*VALUE(LEFT(G135, FIND(":", G135)-1))</f>
         <v>0</v>
       </c>
-      <c r="I135" t="s">
+      <c r="J135" t="s">
         <v>9</v>
       </c>
-      <c r="J135" t="s">
+      <c r="K135" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:11">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="E136">
+        <v>313</v>
+      </c>
+      <c r="E136" t="s">
+        <v>314</v>
+      </c>
+      <c r="F136" s="1">
         <v>0</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H136">
         <f>E136*VALUE(LEFT(G136, FIND(":", G136)-1))</f>
         <v>0</v>
       </c>
-      <c r="I136" t="s">
+      <c r="J136" t="s">
         <v>9</v>
       </c>
-      <c r="J136" t="s">
+      <c r="K136" t="s">
         <v>30</v>
       </c>
     </row>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="395">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -58,21 +58,15 @@
     <t>Anomaly Management</t>
   </si>
   <si>
-    <t>Architecting for Cloud</t>
-  </si>
-  <si>
-    <t>Benchmarking</t>
+    <t>Architecting &amp; Workload Placement</t>
+  </si>
+  <si>
+    <t>Automation, Tools &amp; Services</t>
   </si>
   <si>
     <t>Budgeting</t>
   </si>
   <si>
-    <t>Cloud Policy &amp; Governance</t>
-  </si>
-  <si>
-    <t>Cloud Sustainability</t>
-  </si>
-  <si>
     <t>Data Ingestion</t>
   </si>
   <si>
@@ -85,24 +79,24 @@
     <t>FinOps Practice Operations</t>
   </si>
   <si>
-    <t>FinOps Tools &amp; Services</t>
-  </si>
-  <si>
     <t>Forecasting</t>
   </si>
   <si>
+    <t>Governance, Policy &amp; Risk</t>
+  </si>
+  <si>
     <t>Intersecting Disciplines</t>
   </si>
   <si>
     <t>Invoicing &amp; Chargeback</t>
   </si>
   <si>
+    <t>KPIs &amp; Benchmarking</t>
+  </si>
+  <si>
     <t>Licensing &amp; SaaS</t>
   </si>
   <si>
-    <t>Onboarding Workloads</t>
-  </si>
-  <si>
     <t>Planning &amp; Estimating</t>
   </si>
   <si>
@@ -112,10 +106,13 @@
     <t>Reporting &amp; Analytics</t>
   </si>
   <si>
+    <t>Sustainability</t>
+  </si>
+  <si>
     <t>Unit Economics</t>
   </si>
   <si>
-    <t>Workload Optimization</t>
+    <t>Usage Optimization</t>
   </si>
   <si>
     <t>serial number</t>
@@ -265,6 +262,24 @@
     <t>Resolve Variances &amp; Increase Coverage</t>
   </si>
   <si>
+    <t>Establish Architecture Review Process</t>
+  </si>
+  <si>
+    <t>Assess Workloads for Modernization</t>
+  </si>
+  <si>
+    <t>Estimate Trade-Offs &amp; Document Cases</t>
+  </si>
+  <si>
+    <t>Implement Iteratively &amp; Measure Results</t>
+  </si>
+  <si>
+    <t>Publish Benefits &amp; Update References</t>
+  </si>
+  <si>
+    <t>Strengthen Architecture Collaboration</t>
+  </si>
+  <si>
     <t>Create Workload Selection Criteria</t>
   </si>
   <si>
@@ -283,24 +298,6 @@
     <t>Review Outcomes &amp; Adjust Patterns</t>
   </si>
   <si>
-    <t>Establish Architecture Review Process</t>
-  </si>
-  <si>
-    <t>Assess Workloads for Modernization</t>
-  </si>
-  <si>
-    <t>Estimate Trade-Offs &amp; Document Cases</t>
-  </si>
-  <si>
-    <t>Implement Iteratively &amp; Measure Results</t>
-  </si>
-  <si>
-    <t>Publish Benefits &amp; Update References</t>
-  </si>
-  <si>
-    <t>Strengthen Architecture Collaboration</t>
-  </si>
-  <si>
     <t>Aggregate emissions data by region/service/account with lineage.</t>
   </si>
   <si>
@@ -670,6 +667,24 @@
     <t>112</t>
   </si>
   <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>062</t>
+  </si>
+  <si>
+    <t>063</t>
+  </si>
+  <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>066</t>
+  </si>
+  <si>
     <t>118</t>
   </si>
   <si>
@@ -686,24 +701,6 @@
   </si>
   <si>
     <t>123</t>
-  </si>
-  <si>
-    <t>061</t>
-  </si>
-  <si>
-    <t>062</t>
-  </si>
-  <si>
-    <t>063</t>
-  </si>
-  <si>
-    <t>064</t>
-  </si>
-  <si>
-    <t>065</t>
-  </si>
-  <si>
-    <t>066</t>
   </si>
   <si>
     <t>085</t>
@@ -1021,18 +1018,18 @@
 10*Ceil(x/5)</t>
   </si>
   <si>
-    <t>* Process defined for new accounts and resources deployed
-* Train teams on process
-* Automate process
-10*Ceil(x/3)</t>
-  </si>
-  <si>
     <t>* Define process to address notifications from CSPs
 * Define cadence for review
 * Define exception criteria
 * Define thresholds to change
 * Combine with architecture analysis for SP &amp; RIs
 10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Process defined for new accounts and resources deployed
+* Train teams on process
+* Automate process
+10*Ceil(x/3)</t>
   </si>
   <si>
     <t>* Process for evaluating spot periodically
@@ -1608,9 +1605,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Overview!$A$12:$A$33</c:f>
+              <c:f>Overview!$A$12:$A$32</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>Allocation</c:v>
                 </c:pt>
@@ -1618,74 +1615,71 @@
                   <c:v>Anomaly Management</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Architecting for Cloud</c:v>
+                  <c:v>Architecting &amp; Workload Placement</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Benchmarking</c:v>
+                  <c:v>Automation, Tools &amp; Services</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Budgeting</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Cloud Policy &amp; Governance</c:v>
+                  <c:v>Data Ingestion</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Cloud Sustainability</c:v>
+                  <c:v>FinOps Assessment</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Data Ingestion</c:v>
+                  <c:v>FinOps Education &amp; Enablement</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>FinOps Assessment</c:v>
+                  <c:v>FinOps Practice Operations</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>FinOps Education &amp; Enablement</c:v>
+                  <c:v>Forecasting</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>FinOps Practice Operations</c:v>
+                  <c:v>Governance, Policy &amp; Risk</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>FinOps Tools &amp; Services</c:v>
+                  <c:v>Intersecting Disciplines</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Forecasting</c:v>
+                  <c:v>Invoicing &amp; Chargeback</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Intersecting Disciplines</c:v>
+                  <c:v>KPIs &amp; Benchmarking</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Invoicing &amp; Chargeback</c:v>
+                  <c:v>Licensing &amp; SaaS</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Licensing &amp; SaaS</c:v>
+                  <c:v>Planning &amp; Estimating</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>Onboarding Workloads</c:v>
+                  <c:v>Rate Optimization</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>Planning &amp; Estimating</c:v>
+                  <c:v>Reporting &amp; Analytics</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>Rate Optimization</c:v>
+                  <c:v>Sustainability</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>Reporting &amp; Analytics</c:v>
+                  <c:v>Unit Economics</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>Unit Economics</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>Workload Optimization</c:v>
+                  <c:v>Usage Optimization</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Overview!$U$12:$U$33</c:f>
+              <c:f>Overview!$U$12:$U$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1747,9 +1741,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1921,7 +1912,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A11:B33" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A11:B32" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" name="Capability"/>
     <tableColumn id="2" name="Action Count"/>
@@ -2215,10 +2206,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
@@ -2268,7 +2259,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="U5">
         <f>SUMIF(Scoring!I2:I136,A5,Scoring!H2:H136)/SUMIF(Scoring!I2:I136,A5,Scoring!E2:E136)</f>
@@ -2280,7 +2271,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="U6">
         <f>SUMIF(Scoring!I2:I136,A6,Scoring!H2:H136)/SUMIF(Scoring!I2:I136,A6,Scoring!E2:E136)</f>
@@ -2354,7 +2345,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U14">
         <f>SUMIF(Scoring!J2:J136,A14,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A14,Scoring!E2:E136)</f>
@@ -2366,7 +2357,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <f>SUMIF(Scoring!J2:J136,A15,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A15,Scoring!E2:E136)</f>
@@ -2390,7 +2381,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <f>SUMIF(Scoring!J2:J136,A17,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A17,Scoring!E2:E136)</f>
@@ -2402,7 +2393,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <f>SUMIF(Scoring!J2:J136,A18,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A18,Scoring!E2:E136)</f>
@@ -2414,7 +2405,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <f>SUMIF(Scoring!J2:J136,A19,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A19,Scoring!E2:E136)</f>
@@ -2426,7 +2417,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <f>SUMIF(Scoring!J2:J136,A20,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A20,Scoring!E2:E136)</f>
@@ -2438,7 +2429,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <f>SUMIF(Scoring!J2:J136,A21,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A21,Scoring!E2:E136)</f>
@@ -2450,7 +2441,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <f>SUMIF(Scoring!J2:J136,A22,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A22,Scoring!E2:E136)</f>
@@ -2462,7 +2453,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <f>SUMIF(Scoring!J2:J136,A23,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A23,Scoring!E2:E136)</f>
@@ -2510,7 +2501,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <f>SUMIF(Scoring!J2:J136,A27,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A27,Scoring!E2:E136)</f>
@@ -2558,7 +2549,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U31">
         <f>SUMIF(Scoring!J2:J136,A31,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A31,Scoring!E2:E136)</f>
@@ -2577,21 +2568,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
+    <row r="33" spans="2:2">
       <c r="B33">
-        <v>6</v>
-      </c>
-      <c r="U33">
-        <f>SUMIF(Scoring!J2:J136,A33,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A33,Scoring!E2:E136)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21">
-      <c r="B34">
-        <f>SUM(Overview!$B$12:$B$33)</f>
+        <f>SUM(Overview!$B$12:$B$32)</f>
         <v>0</v>
       </c>
     </row>
@@ -2612,7 +2591,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="63" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -2620,43 +2599,43 @@
     <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.5703125" hidden="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25.42578125" hidden="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.28515625" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.42578125" hidden="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="D1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2664,22 +2643,22 @@
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H2">
         <f>E2*VALUE(LEFT(G2, FIND(":", G2)-1))</f>
@@ -2689,26 +2668,26 @@
         <v>6</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H3">
         <f>E3*VALUE(LEFT(G3, FIND(":", G3)-1))</f>
@@ -2718,26 +2697,26 @@
         <v>6</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H4">
         <f>E4*VALUE(LEFT(G4, FIND(":", G4)-1))</f>
@@ -2747,26 +2726,26 @@
         <v>6</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H5">
         <f>E5*VALUE(LEFT(G5, FIND(":", G5)-1))</f>
@@ -2776,26 +2755,26 @@
         <v>6</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H6">
         <f>E6*VALUE(LEFT(G6, FIND(":", G6)-1))</f>
@@ -2805,28 +2784,28 @@
         <v>6</v>
       </c>
       <c r="K6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H7">
         <f>E7*VALUE(LEFT(G7, FIND(":", G7)-1))</f>
@@ -2836,26 +2815,26 @@
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H8">
         <f>E8*VALUE(LEFT(G8, FIND(":", G8)-1))</f>
@@ -2865,26 +2844,26 @@
         <v>6</v>
       </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H9">
         <f>E9*VALUE(LEFT(G9, FIND(":", G9)-1))</f>
@@ -2894,26 +2873,26 @@
         <v>6</v>
       </c>
       <c r="K9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H10">
         <f>E10*VALUE(LEFT(G10, FIND(":", G10)-1))</f>
@@ -2923,26 +2902,26 @@
         <v>6</v>
       </c>
       <c r="K10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H11">
         <f>E11*VALUE(LEFT(G11, FIND(":", G11)-1))</f>
@@ -2952,28 +2931,28 @@
         <v>6</v>
       </c>
       <c r="K11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H12">
         <f>E12*VALUE(LEFT(G12, FIND(":", G12)-1))</f>
@@ -2983,26 +2962,26 @@
         <v>6</v>
       </c>
       <c r="K12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H13">
         <f>E13*VALUE(LEFT(G13, FIND(":", G13)-1))</f>
@@ -3012,26 +2991,26 @@
         <v>6</v>
       </c>
       <c r="K13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H14">
         <f>E14*VALUE(LEFT(G14, FIND(":", G14)-1))</f>
@@ -3041,26 +3020,26 @@
         <v>6</v>
       </c>
       <c r="K14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E15" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H15">
         <f>E15*VALUE(LEFT(G15, FIND(":", G15)-1))</f>
@@ -3070,26 +3049,26 @@
         <v>6</v>
       </c>
       <c r="K15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E16" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H16">
         <f>E16*VALUE(LEFT(G16, FIND(":", G16)-1))</f>
@@ -3099,28 +3078,28 @@
         <v>6</v>
       </c>
       <c r="K16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H17">
         <f>E17*VALUE(LEFT(G17, FIND(":", G17)-1))</f>
@@ -3130,26 +3109,26 @@
         <v>6</v>
       </c>
       <c r="K17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E18" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H18">
         <f>E18*VALUE(LEFT(G18, FIND(":", G18)-1))</f>
@@ -3159,26 +3138,26 @@
         <v>6</v>
       </c>
       <c r="K18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E19" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H19">
         <f>E19*VALUE(LEFT(G19, FIND(":", G19)-1))</f>
@@ -3188,26 +3167,26 @@
         <v>6</v>
       </c>
       <c r="K19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E20" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H20">
         <f>E20*VALUE(LEFT(G20, FIND(":", G20)-1))</f>
@@ -3217,26 +3196,26 @@
         <v>6</v>
       </c>
       <c r="K20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E21" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H21">
         <f>E21*VALUE(LEFT(G21, FIND(":", G21)-1))</f>
@@ -3246,26 +3225,26 @@
         <v>6</v>
       </c>
       <c r="K21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E22" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H22">
         <f>E22*VALUE(LEFT(G22, FIND(":", G22)-1))</f>
@@ -3275,28 +3254,28 @@
         <v>6</v>
       </c>
       <c r="K22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E23" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H23">
         <f>E23*VALUE(LEFT(G23, FIND(":", G23)-1))</f>
@@ -3306,26 +3285,26 @@
         <v>6</v>
       </c>
       <c r="K23" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F24" s="1">
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H24">
         <f>E24*VALUE(LEFT(G24, FIND(":", G24)-1))</f>
@@ -3335,26 +3314,26 @@
         <v>6</v>
       </c>
       <c r="K24" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E25" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H25">
         <f>E25*VALUE(LEFT(G25, FIND(":", G25)-1))</f>
@@ -3364,26 +3343,26 @@
         <v>6</v>
       </c>
       <c r="K25" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E26" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F26" s="1">
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H26">
         <f>E26*VALUE(LEFT(G26, FIND(":", G26)-1))</f>
@@ -3393,26 +3372,26 @@
         <v>6</v>
       </c>
       <c r="K26" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E27" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H27">
         <f>E27*VALUE(LEFT(G27, FIND(":", G27)-1))</f>
@@ -3422,28 +3401,28 @@
         <v>6</v>
       </c>
       <c r="K27" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E28" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H28">
         <f>E28*VALUE(LEFT(G28, FIND(":", G28)-1))</f>
@@ -3453,26 +3432,26 @@
         <v>6</v>
       </c>
       <c r="K28" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E29" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H29">
         <f>E29*VALUE(LEFT(G29, FIND(":", G29)-1))</f>
@@ -3482,26 +3461,26 @@
         <v>6</v>
       </c>
       <c r="K29" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E30" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H30">
         <f>E30*VALUE(LEFT(G30, FIND(":", G30)-1))</f>
@@ -3511,26 +3490,26 @@
         <v>6</v>
       </c>
       <c r="K30" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E31" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H31">
         <f>E31*VALUE(LEFT(G31, FIND(":", G31)-1))</f>
@@ -3540,26 +3519,26 @@
         <v>6</v>
       </c>
       <c r="K31" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E32" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H32">
         <f>E32*VALUE(LEFT(G32, FIND(":", G32)-1))</f>
@@ -3569,26 +3548,26 @@
         <v>6</v>
       </c>
       <c r="K32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E33" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H33">
         <f>E33*VALUE(LEFT(G33, FIND(":", G33)-1))</f>
@@ -3598,28 +3577,28 @@
         <v>6</v>
       </c>
       <c r="K33" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E34" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H34">
         <f>E34*VALUE(LEFT(G34, FIND(":", G34)-1))</f>
@@ -3629,26 +3608,26 @@
         <v>6</v>
       </c>
       <c r="K34" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E35" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H35">
         <f>E35*VALUE(LEFT(G35, FIND(":", G35)-1))</f>
@@ -3658,26 +3637,26 @@
         <v>6</v>
       </c>
       <c r="K35" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F36" s="1">
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H36">
         <f>E36*VALUE(LEFT(G36, FIND(":", G36)-1))</f>
@@ -3687,26 +3666,26 @@
         <v>6</v>
       </c>
       <c r="K36" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E37" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H37">
         <f>E37*VALUE(LEFT(G37, FIND(":", G37)-1))</f>
@@ -3716,26 +3695,26 @@
         <v>6</v>
       </c>
       <c r="K37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E38" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H38">
         <f>E38*VALUE(LEFT(G38, FIND(":", G38)-1))</f>
@@ -3745,26 +3724,26 @@
         <v>6</v>
       </c>
       <c r="K38" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F39" s="1">
         <v>1</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H39">
         <f>E39*VALUE(LEFT(G39, FIND(":", G39)-1))</f>
@@ -3774,206 +3753,204 @@
         <v>6</v>
       </c>
       <c r="K39" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="2"/>
+      <c r="A40" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="B40" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E40" t="s">
         <v>314</v>
       </c>
       <c r="F40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H40">
         <f>E40*VALUE(LEFT(G40, FIND(":", G40)-1))</f>
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K40" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E41" t="s">
         <v>314</v>
       </c>
       <c r="F41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H41">
         <f>E41*VALUE(LEFT(G41, FIND(":", G41)-1))</f>
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K41" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E42" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F42" s="1">
         <v>1</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="H42">
         <f>E42*VALUE(LEFT(G42, FIND(":", G42)-1))</f>
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K42" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E43" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H43">
         <f>E43*VALUE(LEFT(G43, FIND(":", G43)-1))</f>
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K43" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E44" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H44">
         <f>E44*VALUE(LEFT(G44, FIND(":", G44)-1))</f>
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K44" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E45" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H45">
         <f>E45*VALUE(LEFT(G45, FIND(":", G45)-1))</f>
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K45" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
       <c r="C46" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E46" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="H46">
         <f>E46*VALUE(LEFT(G46, FIND(":", G46)-1))</f>
@@ -3990,19 +3967,19 @@
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E47" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="H47">
         <f>E47*VALUE(LEFT(G47, FIND(":", G47)-1))</f>
@@ -4019,19 +3996,19 @@
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E48" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F48" s="1">
         <v>1</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="H48">
         <f>E48*VALUE(LEFT(G48, FIND(":", G48)-1))</f>
@@ -4048,19 +4025,19 @@
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E49" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H49">
         <f>E49*VALUE(LEFT(G49, FIND(":", G49)-1))</f>
@@ -4077,19 +4054,19 @@
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E50" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H50">
         <f>E50*VALUE(LEFT(G50, FIND(":", G50)-1))</f>
@@ -4106,19 +4083,19 @@
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E51" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H51">
         <f>E51*VALUE(LEFT(G51, FIND(":", G51)-1))</f>
@@ -4134,22 +4111,22 @@
     <row r="52" spans="1:11">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E52" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H52">
         <f>E52*VALUE(LEFT(G52, FIND(":", G52)-1))</f>
@@ -4159,26 +4136,26 @@
         <v>7</v>
       </c>
       <c r="K52" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E53" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H53">
         <f>E53*VALUE(LEFT(G53, FIND(":", G53)-1))</f>
@@ -4188,26 +4165,26 @@
         <v>7</v>
       </c>
       <c r="K53" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E54" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H54">
         <f>E54*VALUE(LEFT(G54, FIND(":", G54)-1))</f>
@@ -4217,26 +4194,26 @@
         <v>7</v>
       </c>
       <c r="K54" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E55" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H55">
         <f>E55*VALUE(LEFT(G55, FIND(":", G55)-1))</f>
@@ -4246,26 +4223,26 @@
         <v>7</v>
       </c>
       <c r="K55" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E56" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H56">
         <f>E56*VALUE(LEFT(G56, FIND(":", G56)-1))</f>
@@ -4275,26 +4252,26 @@
         <v>7</v>
       </c>
       <c r="K56" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E57" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H57">
         <f>E57*VALUE(LEFT(G57, FIND(":", G57)-1))</f>
@@ -4304,28 +4281,28 @@
         <v>7</v>
       </c>
       <c r="K57" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="2"/>
       <c r="B58" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E58" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F58" s="1">
         <v>1</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H58">
         <f>E58*VALUE(LEFT(G58, FIND(":", G58)-1))</f>
@@ -4335,26 +4312,26 @@
         <v>7</v>
       </c>
       <c r="K58" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E59" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H59">
         <f>E59*VALUE(LEFT(G59, FIND(":", G59)-1))</f>
@@ -4364,26 +4341,26 @@
         <v>7</v>
       </c>
       <c r="K59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E60" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H60">
         <f>E60*VALUE(LEFT(G60, FIND(":", G60)-1))</f>
@@ -4393,26 +4370,26 @@
         <v>7</v>
       </c>
       <c r="K60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E61" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F61" s="1">
         <v>1</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H61">
         <f>E61*VALUE(LEFT(G61, FIND(":", G61)-1))</f>
@@ -4422,26 +4399,26 @@
         <v>7</v>
       </c>
       <c r="K61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E62" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H62">
         <f>E62*VALUE(LEFT(G62, FIND(":", G62)-1))</f>
@@ -4451,26 +4428,26 @@
         <v>7</v>
       </c>
       <c r="K62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E63" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H63">
         <f>E63*VALUE(LEFT(G63, FIND(":", G63)-1))</f>
@@ -4480,28 +4457,28 @@
         <v>7</v>
       </c>
       <c r="K63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="2"/>
       <c r="B64" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E64" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F64" s="1">
         <v>1</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H64">
         <f>E64*VALUE(LEFT(G64, FIND(":", G64)-1))</f>
@@ -4511,26 +4488,26 @@
         <v>7</v>
       </c>
       <c r="K64" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E65" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F65" s="1">
         <v>1</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H65">
         <f>E65*VALUE(LEFT(G65, FIND(":", G65)-1))</f>
@@ -4540,26 +4517,26 @@
         <v>7</v>
       </c>
       <c r="K65" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E66" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H66">
         <f>E66*VALUE(LEFT(G66, FIND(":", G66)-1))</f>
@@ -4569,26 +4546,26 @@
         <v>7</v>
       </c>
       <c r="K66" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E67" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H67">
         <f>E67*VALUE(LEFT(G67, FIND(":", G67)-1))</f>
@@ -4598,26 +4575,26 @@
         <v>7</v>
       </c>
       <c r="K67" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E68" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H68">
         <f>E68*VALUE(LEFT(G68, FIND(":", G68)-1))</f>
@@ -4627,26 +4604,26 @@
         <v>7</v>
       </c>
       <c r="K68" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E69" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F69" s="1">
         <v>1</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H69">
         <f>E69*VALUE(LEFT(G69, FIND(":", G69)-1))</f>
@@ -4656,28 +4633,28 @@
         <v>7</v>
       </c>
       <c r="K69" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="2"/>
       <c r="B70" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E70" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H70">
         <f>E70*VALUE(LEFT(G70, FIND(":", G70)-1))</f>
@@ -4687,26 +4664,26 @@
         <v>7</v>
       </c>
       <c r="K70" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E71" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F71" s="1">
         <v>1</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H71">
         <f>E71*VALUE(LEFT(G71, FIND(":", G71)-1))</f>
@@ -4716,26 +4693,26 @@
         <v>7</v>
       </c>
       <c r="K71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E72" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F72" s="1">
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H72">
         <f>E72*VALUE(LEFT(G72, FIND(":", G72)-1))</f>
@@ -4745,26 +4722,26 @@
         <v>7</v>
       </c>
       <c r="K72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E73" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H73">
         <f>E73*VALUE(LEFT(G73, FIND(":", G73)-1))</f>
@@ -4774,26 +4751,26 @@
         <v>7</v>
       </c>
       <c r="K73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E74" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H74">
         <f>E74*VALUE(LEFT(G74, FIND(":", G74)-1))</f>
@@ -4803,26 +4780,26 @@
         <v>7</v>
       </c>
       <c r="K74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E75" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H75">
         <f>E75*VALUE(LEFT(G75, FIND(":", G75)-1))</f>
@@ -4832,7 +4809,7 @@
         <v>7</v>
       </c>
       <c r="K75" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -4840,22 +4817,22 @@
         <v>8</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E76" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H76">
         <f>E76*VALUE(LEFT(G76, FIND(":", G76)-1))</f>
@@ -4865,26 +4842,26 @@
         <v>8</v>
       </c>
       <c r="K76" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E77" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H77">
         <f>E77*VALUE(LEFT(G77, FIND(":", G77)-1))</f>
@@ -4894,26 +4871,26 @@
         <v>8</v>
       </c>
       <c r="K77" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E78" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H78">
         <f>E78*VALUE(LEFT(G78, FIND(":", G78)-1))</f>
@@ -4923,26 +4900,26 @@
         <v>8</v>
       </c>
       <c r="K78" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E79" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H79">
         <f>E79*VALUE(LEFT(G79, FIND(":", G79)-1))</f>
@@ -4952,26 +4929,26 @@
         <v>8</v>
       </c>
       <c r="K79" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E80" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F80" s="1">
         <v>1</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H80">
         <f>E80*VALUE(LEFT(G80, FIND(":", G80)-1))</f>
@@ -4981,26 +4958,26 @@
         <v>8</v>
       </c>
       <c r="K80" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E81" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H81">
         <f>E81*VALUE(LEFT(G81, FIND(":", G81)-1))</f>
@@ -5010,7 +4987,7 @@
         <v>8</v>
       </c>
       <c r="K81" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -5019,19 +4996,19 @@
         <v>15</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E82" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F82" s="1">
         <v>1</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H82">
         <f>E82*VALUE(LEFT(G82, FIND(":", G82)-1))</f>
@@ -5048,19 +5025,19 @@
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E83" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F83" s="1">
         <v>1</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H83">
         <f>E83*VALUE(LEFT(G83, FIND(":", G83)-1))</f>
@@ -5077,19 +5054,19 @@
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E84" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H84">
         <f>E84*VALUE(LEFT(G84, FIND(":", G84)-1))</f>
@@ -5106,19 +5083,19 @@
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E85" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H85">
         <f>E85*VALUE(LEFT(G85, FIND(":", G85)-1))</f>
@@ -5135,19 +5112,19 @@
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E86" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H86">
         <f>E86*VALUE(LEFT(G86, FIND(":", G86)-1))</f>
@@ -5164,19 +5141,19 @@
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E87" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H87">
         <f>E87*VALUE(LEFT(G87, FIND(":", G87)-1))</f>
@@ -5192,22 +5169,22 @@
     <row r="88" spans="1:11">
       <c r="A88" s="2"/>
       <c r="B88" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E88" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H88">
         <f>E88*VALUE(LEFT(G88, FIND(":", G88)-1))</f>
@@ -5217,26 +5194,26 @@
         <v>8</v>
       </c>
       <c r="K88" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E89" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F89" s="1">
         <v>1</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H89">
         <f>E89*VALUE(LEFT(G89, FIND(":", G89)-1))</f>
@@ -5246,26 +5223,26 @@
         <v>8</v>
       </c>
       <c r="K89" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E90" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F90" s="1">
         <v>1</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H90">
         <f>E90*VALUE(LEFT(G90, FIND(":", G90)-1))</f>
@@ -5275,26 +5252,26 @@
         <v>8</v>
       </c>
       <c r="K90" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E91" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F91" s="1">
         <v>1</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H91">
         <f>E91*VALUE(LEFT(G91, FIND(":", G91)-1))</f>
@@ -5304,26 +5281,26 @@
         <v>8</v>
       </c>
       <c r="K91" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E92" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F92" s="1">
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H92">
         <f>E92*VALUE(LEFT(G92, FIND(":", G92)-1))</f>
@@ -5333,26 +5310,26 @@
         <v>8</v>
       </c>
       <c r="K92" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E93" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F93" s="1">
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H93">
         <f>E93*VALUE(LEFT(G93, FIND(":", G93)-1))</f>
@@ -5362,28 +5339,28 @@
         <v>8</v>
       </c>
       <c r="K93" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="2"/>
       <c r="B94" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E94" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F94" s="1">
         <v>1</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H94">
         <f>E94*VALUE(LEFT(G94, FIND(":", G94)-1))</f>
@@ -5393,26 +5370,26 @@
         <v>8</v>
       </c>
       <c r="K94" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E95" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F95" s="1">
         <v>1</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H95">
         <f>E95*VALUE(LEFT(G95, FIND(":", G95)-1))</f>
@@ -5422,26 +5399,26 @@
         <v>8</v>
       </c>
       <c r="K95" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E96" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F96" s="1">
         <v>1</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H96">
         <f>E96*VALUE(LEFT(G96, FIND(":", G96)-1))</f>
@@ -5451,26 +5428,26 @@
         <v>8</v>
       </c>
       <c r="K96" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E97" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F97" s="1">
         <v>1</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H97">
         <f>E97*VALUE(LEFT(G97, FIND(":", G97)-1))</f>
@@ -5480,26 +5457,26 @@
         <v>8</v>
       </c>
       <c r="K97" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E98" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F98" s="1">
         <v>1</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H98">
         <f>E98*VALUE(LEFT(G98, FIND(":", G98)-1))</f>
@@ -5509,26 +5486,26 @@
         <v>8</v>
       </c>
       <c r="K98" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E99" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F99" s="1">
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H99">
         <f>E99*VALUE(LEFT(G99, FIND(":", G99)-1))</f>
@@ -5538,26 +5515,26 @@
         <v>8</v>
       </c>
       <c r="K99" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E100" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F100" s="1">
         <v>1</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H100">
         <f>E100*VALUE(LEFT(G100, FIND(":", G100)-1))</f>
@@ -5567,28 +5544,28 @@
         <v>8</v>
       </c>
       <c r="K100" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="2"/>
       <c r="B101" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E101" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F101" s="1">
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H101">
         <f>E101*VALUE(LEFT(G101, FIND(":", G101)-1))</f>
@@ -5598,26 +5575,26 @@
         <v>8</v>
       </c>
       <c r="K101" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E102" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H102">
         <f>E102*VALUE(LEFT(G102, FIND(":", G102)-1))</f>
@@ -5627,26 +5604,26 @@
         <v>8</v>
       </c>
       <c r="K102" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E103" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F103" s="1">
         <v>0</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H103">
         <f>E103*VALUE(LEFT(G103, FIND(":", G103)-1))</f>
@@ -5656,26 +5633,26 @@
         <v>8</v>
       </c>
       <c r="K103" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E104" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H104">
         <f>E104*VALUE(LEFT(G104, FIND(":", G104)-1))</f>
@@ -5685,26 +5662,26 @@
         <v>8</v>
       </c>
       <c r="K104" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E105" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F105" s="1">
         <v>0</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H105">
         <f>E105*VALUE(LEFT(G105, FIND(":", G105)-1))</f>
@@ -5714,26 +5691,26 @@
         <v>8</v>
       </c>
       <c r="K105" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E106" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F106" s="1">
         <v>1</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H106">
         <f>E106*VALUE(LEFT(G106, FIND(":", G106)-1))</f>
@@ -5743,7 +5720,7 @@
         <v>8</v>
       </c>
       <c r="K106" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -5754,19 +5731,19 @@
         <v>11</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E107" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F107" s="1">
         <v>1</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H107">
         <f>E107*VALUE(LEFT(G107, FIND(":", G107)-1))</f>
@@ -5783,19 +5760,19 @@
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E108" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F108" s="1">
         <v>1</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H108">
         <f>E108*VALUE(LEFT(G108, FIND(":", G108)-1))</f>
@@ -5812,19 +5789,19 @@
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E109" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F109" s="1">
         <v>1</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H109">
         <f>E109*VALUE(LEFT(G109, FIND(":", G109)-1))</f>
@@ -5841,19 +5818,19 @@
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E110" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H110">
         <f>E110*VALUE(LEFT(G110, FIND(":", G110)-1))</f>
@@ -5870,19 +5847,19 @@
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E111" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F111" s="1">
         <v>1</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H111">
         <f>E111*VALUE(LEFT(G111, FIND(":", G111)-1))</f>
@@ -5899,19 +5876,19 @@
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E112" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F112" s="1">
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H112">
         <f>E112*VALUE(LEFT(G112, FIND(":", G112)-1))</f>
@@ -5928,19 +5905,19 @@
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E113" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H113">
         <f>E113*VALUE(LEFT(G113, FIND(":", G113)-1))</f>
@@ -5959,19 +5936,19 @@
         <v>12</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E114" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F114" s="1">
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H114">
         <f>E114*VALUE(LEFT(G114, FIND(":", G114)-1))</f>
@@ -5988,19 +5965,19 @@
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E115" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F115" s="1">
         <v>1</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H115">
         <f>E115*VALUE(LEFT(G115, FIND(":", G115)-1))</f>
@@ -6017,19 +5994,19 @@
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E116" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F116" s="1">
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H116">
         <f>E116*VALUE(LEFT(G116, FIND(":", G116)-1))</f>
@@ -6046,19 +6023,19 @@
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E117" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H117">
         <f>E117*VALUE(LEFT(G117, FIND(":", G117)-1))</f>
@@ -6075,19 +6052,19 @@
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E118" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F118" s="1">
         <v>0</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H118">
         <f>E118*VALUE(LEFT(G118, FIND(":", G118)-1))</f>
@@ -6104,19 +6081,19 @@
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E119" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F119" s="1">
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H119">
         <f>E119*VALUE(LEFT(G119, FIND(":", G119)-1))</f>
@@ -6133,19 +6110,19 @@
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E120" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F120" s="1">
         <v>0</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H120">
         <f>E120*VALUE(LEFT(G120, FIND(":", G120)-1))</f>
@@ -6161,22 +6138,22 @@
     <row r="121" spans="1:11">
       <c r="A121" s="2"/>
       <c r="B121" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E121" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F121" s="1">
         <v>0</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H121">
         <f>E121*VALUE(LEFT(G121, FIND(":", G121)-1))</f>
@@ -6186,26 +6163,26 @@
         <v>9</v>
       </c>
       <c r="K121" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E122" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F122" s="1">
         <v>0</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H122">
         <f>E122*VALUE(LEFT(G122, FIND(":", G122)-1))</f>
@@ -6215,26 +6192,26 @@
         <v>9</v>
       </c>
       <c r="K122" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E123" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H123">
         <f>E123*VALUE(LEFT(G123, FIND(":", G123)-1))</f>
@@ -6244,26 +6221,26 @@
         <v>9</v>
       </c>
       <c r="K123" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E124" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F124" s="1">
         <v>1</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H124">
         <f>E124*VALUE(LEFT(G124, FIND(":", G124)-1))</f>
@@ -6273,26 +6250,26 @@
         <v>9</v>
       </c>
       <c r="K124" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E125" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F125" s="1">
         <v>0</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H125">
         <f>E125*VALUE(LEFT(G125, FIND(":", G125)-1))</f>
@@ -6302,26 +6279,26 @@
         <v>9</v>
       </c>
       <c r="K125" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E126" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F126" s="1">
         <v>1</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H126">
         <f>E126*VALUE(LEFT(G126, FIND(":", G126)-1))</f>
@@ -6331,26 +6308,26 @@
         <v>9</v>
       </c>
       <c r="K126" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E127" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H127">
         <f>E127*VALUE(LEFT(G127, FIND(":", G127)-1))</f>
@@ -6360,26 +6337,26 @@
         <v>9</v>
       </c>
       <c r="K127" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E128" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H128">
         <f>E128*VALUE(LEFT(G128, FIND(":", G128)-1))</f>
@@ -6389,26 +6366,26 @@
         <v>9</v>
       </c>
       <c r="K128" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E129" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F129" s="1">
         <v>1</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H129">
         <f>E129*VALUE(LEFT(G129, FIND(":", G129)-1))</f>
@@ -6418,28 +6395,28 @@
         <v>9</v>
       </c>
       <c r="K129" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="2"/>
       <c r="B130" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E130" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H130">
         <f>E130*VALUE(LEFT(G130, FIND(":", G130)-1))</f>
@@ -6449,26 +6426,26 @@
         <v>9</v>
       </c>
       <c r="K130" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="131" spans="1:11">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E131" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F131" s="1">
         <v>1</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H131">
         <f>E131*VALUE(LEFT(G131, FIND(":", G131)-1))</f>
@@ -6478,26 +6455,26 @@
         <v>9</v>
       </c>
       <c r="K131" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E132" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F132" s="1">
         <v>1</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H132">
         <f>E132*VALUE(LEFT(G132, FIND(":", G132)-1))</f>
@@ -6507,26 +6484,26 @@
         <v>9</v>
       </c>
       <c r="K132" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E133" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H133">
         <f>E133*VALUE(LEFT(G133, FIND(":", G133)-1))</f>
@@ -6536,26 +6513,26 @@
         <v>9</v>
       </c>
       <c r="K133" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E134" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F134" s="1">
         <v>1</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H134">
         <f>E134*VALUE(LEFT(G134, FIND(":", G134)-1))</f>
@@ -6565,26 +6542,26 @@
         <v>9</v>
       </c>
       <c r="K134" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E135" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H135">
         <f>E135*VALUE(LEFT(G135, FIND(":", G135)-1))</f>
@@ -6594,26 +6571,26 @@
         <v>9</v>
       </c>
       <c r="K135" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E136" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F136" s="1">
         <v>0</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H136">
         <f>E136*VALUE(LEFT(G136, FIND(":", G136)-1))</f>
@@ -6623,13 +6600,13 @@
         <v>9</v>
       </c>
       <c r="K136" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A2:A45"/>
-    <mergeCell ref="A46:A75"/>
+  <mergeCells count="25">
+    <mergeCell ref="A2:A39"/>
+    <mergeCell ref="A40:A75"/>
     <mergeCell ref="A76:A106"/>
     <mergeCell ref="A107:A136"/>
     <mergeCell ref="B2:B6"/>
@@ -6639,8 +6616,7 @@
     <mergeCell ref="B23:B27"/>
     <mergeCell ref="B28:B33"/>
     <mergeCell ref="B34:B39"/>
-    <mergeCell ref="B40:B45"/>
-    <mergeCell ref="B46:B51"/>
+    <mergeCell ref="B40:B51"/>
     <mergeCell ref="B52:B57"/>
     <mergeCell ref="B58:B63"/>
     <mergeCell ref="B64:B69"/>
@@ -6771,31 +6747,31 @@
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G40">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G41">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G42">
+      <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G43">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G44">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G45">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G46">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G47">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G48">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G43">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G44">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G45">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G46">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G47">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G48">
-      <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G49">
       <formula1>"0: None"</formula1>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="396">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -968,6 +968,9 @@
   </si>
   <si>
     <t>0.5.0</t>
+  </si>
+  <si>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>1.5.0</t>
@@ -2231,14 +2234,14 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2">
-        <f>SUM(Scoring!E2:E136)</f>
+        <f>SUM(Scoring!F2:F136)</f>
         <v>0</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2">
-        <f>SUM(Scoring!H2:H136)/A2</f>
+        <f>SUM(Scoring!I2:I136)/A2</f>
         <v>0</v>
       </c>
       <c r="D2">
@@ -2262,7 +2265,7 @@
         <v>38</v>
       </c>
       <c r="U5">
-        <f>SUMIF(Scoring!I2:I136,A5,Scoring!H2:H136)/SUMIF(Scoring!I2:I136,A5,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!J2:J136,A5,Scoring!I2:I136)/SUMIF(Scoring!J2:J136,A5,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2274,7 +2277,7 @@
         <v>36</v>
       </c>
       <c r="U6">
-        <f>SUMIF(Scoring!I2:I136,A6,Scoring!H2:H136)/SUMIF(Scoring!I2:I136,A6,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!J2:J136,A6,Scoring!I2:I136)/SUMIF(Scoring!J2:J136,A6,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2286,7 +2289,7 @@
         <v>31</v>
       </c>
       <c r="U7">
-        <f>SUMIF(Scoring!I2:I136,A7,Scoring!H2:H136)/SUMIF(Scoring!I2:I136,A7,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!J2:J136,A7,Scoring!I2:I136)/SUMIF(Scoring!J2:J136,A7,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2298,7 +2301,7 @@
         <v>30</v>
       </c>
       <c r="U8">
-        <f>SUMIF(Scoring!I2:I136,A8,Scoring!H2:H136)/SUMIF(Scoring!I2:I136,A8,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!J2:J136,A8,Scoring!I2:I136)/SUMIF(Scoring!J2:J136,A8,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2324,7 +2327,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <f>SUMIF(Scoring!J2:J136,A12,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A12,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A12,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A12,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2336,7 +2339,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <f>SUMIF(Scoring!J2:J136,A13,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A13,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A13,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A13,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2348,7 +2351,7 @@
         <v>12</v>
       </c>
       <c r="U14">
-        <f>SUMIF(Scoring!J2:J136,A14,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A14,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A14,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A14,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2360,7 +2363,7 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <f>SUMIF(Scoring!J2:J136,A15,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A15,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A15,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A15,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2372,7 +2375,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <f>SUMIF(Scoring!J2:J136,A16,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A16,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A16,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A16,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2384,7 +2387,7 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <f>SUMIF(Scoring!J2:J136,A17,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A17,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A17,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A17,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2396,7 +2399,7 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <f>SUMIF(Scoring!J2:J136,A18,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A18,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A18,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A18,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2408,7 +2411,7 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <f>SUMIF(Scoring!J2:J136,A19,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A19,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A19,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A19,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2420,7 +2423,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <f>SUMIF(Scoring!J2:J136,A20,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A20,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A20,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A20,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2432,7 +2435,7 @@
         <v>6</v>
       </c>
       <c r="U21">
-        <f>SUMIF(Scoring!J2:J136,A21,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A21,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A21,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A21,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2444,7 +2447,7 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <f>SUMIF(Scoring!J2:J136,A22,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A22,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A22,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A22,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2456,7 +2459,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <f>SUMIF(Scoring!J2:J136,A23,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A23,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A23,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A23,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2468,7 +2471,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <f>SUMIF(Scoring!J2:J136,A24,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A24,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A24,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A24,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2480,7 +2483,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <f>SUMIF(Scoring!J2:J136,A25,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A25,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A25,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A25,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2492,7 +2495,7 @@
         <v>6</v>
       </c>
       <c r="U26">
-        <f>SUMIF(Scoring!J2:J136,A26,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A26,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A26,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A26,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2504,7 +2507,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <f>SUMIF(Scoring!J2:J136,A27,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A27,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A27,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A27,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2516,7 +2519,7 @@
         <v>6</v>
       </c>
       <c r="U28">
-        <f>SUMIF(Scoring!J2:J136,A28,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A28,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A28,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A28,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2528,7 +2531,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <f>SUMIF(Scoring!J2:J136,A29,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A29,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A29,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A29,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2540,7 +2543,7 @@
         <v>6</v>
       </c>
       <c r="U30">
-        <f>SUMIF(Scoring!J2:J136,A30,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A30,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A30,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A30,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2552,7 +2555,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <f>SUMIF(Scoring!J2:J136,A31,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A31,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A31,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A31,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2564,7 +2567,7 @@
         <v>6</v>
       </c>
       <c r="U32">
-        <f>SUMIF(Scoring!J2:J136,A32,Scoring!H2:H136)/SUMIF(Scoring!J2:J136,A32,Scoring!E2:E136)</f>
+        <f>SUMIF(Scoring!K2:K136,A32,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A32,Scoring!F2:F136)</f>
         <v>0</v>
       </c>
     </row>
@@ -2595,9 +2598,9 @@
     <col min="3" max="3" width="63" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="40.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="40.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25.42578125" hidden="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="32.42578125" hidden="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="0" hidden="1" customWidth="1"/>
@@ -2654,14 +2657,14 @@
       <c r="E2" t="s">
         <v>313</v>
       </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H2">
-        <f>E2*VALUE(LEFT(G2, FIND(":", G2)-1))</f>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I2">
+        <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
         <v>0</v>
       </c>
       <c r="J2" t="s">
@@ -2683,14 +2686,14 @@
       <c r="E3" t="s">
         <v>313</v>
       </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H3">
-        <f>E3*VALUE(LEFT(G3, FIND(":", G3)-1))</f>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I3">
+        <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
         <v>0</v>
       </c>
       <c r="J3" t="s">
@@ -2712,14 +2715,14 @@
       <c r="E4" t="s">
         <v>313</v>
       </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H4">
-        <f>E4*VALUE(LEFT(G4, FIND(":", G4)-1))</f>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I4">
+        <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
         <v>0</v>
       </c>
       <c r="J4" t="s">
@@ -2741,14 +2744,14 @@
       <c r="E5" t="s">
         <v>314</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="H5">
-        <f>E5*VALUE(LEFT(G5, FIND(":", G5)-1))</f>
+      <c r="H5" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="I5">
+        <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
         <v>0</v>
       </c>
       <c r="J5" t="s">
@@ -2770,14 +2773,14 @@
       <c r="E6" t="s">
         <v>313</v>
       </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H6">
-        <f>E6*VALUE(LEFT(G6, FIND(":", G6)-1))</f>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I6">
+        <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
         <v>0</v>
       </c>
       <c r="J6" t="s">
@@ -2801,14 +2804,17 @@
       <c r="E7" t="s">
         <v>315</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="H7">
-        <f>E7*VALUE(LEFT(G7, FIND(":", G7)-1))</f>
+        <v>319</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="I7">
+        <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
         <v>0</v>
       </c>
       <c r="J7" t="s">
@@ -2830,14 +2836,17 @@
       <c r="E8" t="s">
         <v>315</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H8">
-        <f>E8*VALUE(LEFT(G8, FIND(":", G8)-1))</f>
+        <v>320</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I8">
+        <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
         <v>0</v>
       </c>
       <c r="J8" t="s">
@@ -2859,14 +2868,17 @@
       <c r="E9" t="s">
         <v>315</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H9">
-        <f>E9*VALUE(LEFT(G9, FIND(":", G9)-1))</f>
+        <v>321</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I9">
+        <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
         <v>0</v>
       </c>
       <c r="J9" t="s">
@@ -2888,14 +2900,17 @@
       <c r="E10" t="s">
         <v>313</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H10">
-        <f>E10*VALUE(LEFT(G10, FIND(":", G10)-1))</f>
+        <v>322</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I10">
+        <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
         <v>0</v>
       </c>
       <c r="J10" t="s">
@@ -2917,14 +2932,17 @@
       <c r="E11" t="s">
         <v>313</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11">
         <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H11">
-        <f>E11*VALUE(LEFT(G11, FIND(":", G11)-1))</f>
+        <v>323</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I11">
+        <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
         <v>0</v>
       </c>
       <c r="J11" t="s">
@@ -2948,14 +2966,14 @@
       <c r="E12" t="s">
         <v>313</v>
       </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H12">
-        <f>E12*VALUE(LEFT(G12, FIND(":", G12)-1))</f>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I12">
+        <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
         <v>0</v>
       </c>
       <c r="J12" t="s">
@@ -2977,14 +2995,14 @@
       <c r="E13" t="s">
         <v>313</v>
       </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H13">
-        <f>E13*VALUE(LEFT(G13, FIND(":", G13)-1))</f>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I13">
+        <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
         <v>0</v>
       </c>
       <c r="J13" t="s">
@@ -3006,14 +3024,14 @@
       <c r="E14" t="s">
         <v>313</v>
       </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H14">
-        <f>E14*VALUE(LEFT(G14, FIND(":", G14)-1))</f>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I14">
+        <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
         <v>0</v>
       </c>
       <c r="J14" t="s">
@@ -3035,14 +3053,17 @@
       <c r="E15" t="s">
         <v>314</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H15">
-        <f>E15*VALUE(LEFT(G15, FIND(":", G15)-1))</f>
+        <v>324</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I15">
+        <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
         <v>0</v>
       </c>
       <c r="J15" t="s">
@@ -3064,14 +3085,14 @@
       <c r="E16" t="s">
         <v>313</v>
       </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H16">
-        <f>E16*VALUE(LEFT(G16, FIND(":", G16)-1))</f>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I16">
+        <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
         <v>0</v>
       </c>
       <c r="J16" t="s">
@@ -3095,14 +3116,14 @@
       <c r="E17" t="s">
         <v>314</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17">
         <v>1</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="H17">
-        <f>E17*VALUE(LEFT(G17, FIND(":", G17)-1))</f>
+      <c r="H17" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="I17">
+        <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
         <v>0</v>
       </c>
       <c r="J17" t="s">
@@ -3124,14 +3145,14 @@
       <c r="E18" t="s">
         <v>313</v>
       </c>
-      <c r="F18" s="1">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H18">
-        <f>E18*VALUE(LEFT(G18, FIND(":", G18)-1))</f>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I18">
+        <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
         <v>0</v>
       </c>
       <c r="J18" t="s">
@@ -3153,14 +3174,14 @@
       <c r="E19" t="s">
         <v>313</v>
       </c>
-      <c r="F19" s="1">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H19">
-        <f>E19*VALUE(LEFT(G19, FIND(":", G19)-1))</f>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I19">
+        <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
         <v>0</v>
       </c>
       <c r="J19" t="s">
@@ -3182,14 +3203,14 @@
       <c r="E20" t="s">
         <v>313</v>
       </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H20">
-        <f>E20*VALUE(LEFT(G20, FIND(":", G20)-1))</f>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I20">
+        <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
         <v>0</v>
       </c>
       <c r="J20" t="s">
@@ -3211,14 +3232,14 @@
       <c r="E21" t="s">
         <v>313</v>
       </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H21">
-        <f>E21*VALUE(LEFT(G21, FIND(":", G21)-1))</f>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I21">
+        <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
         <v>0</v>
       </c>
       <c r="J21" t="s">
@@ -3240,14 +3261,14 @@
       <c r="E22" t="s">
         <v>313</v>
       </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H22">
-        <f>E22*VALUE(LEFT(G22, FIND(":", G22)-1))</f>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I22">
+        <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
         <v>0</v>
       </c>
       <c r="J22" t="s">
@@ -3271,14 +3292,14 @@
       <c r="E23" t="s">
         <v>313</v>
       </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H23">
-        <f>E23*VALUE(LEFT(G23, FIND(":", G23)-1))</f>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I23">
+        <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
         <v>0</v>
       </c>
       <c r="J23" t="s">
@@ -3300,14 +3321,14 @@
       <c r="E24" t="s">
         <v>314</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24">
         <v>1</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="H24">
-        <f>E24*VALUE(LEFT(G24, FIND(":", G24)-1))</f>
+      <c r="H24" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="I24">
+        <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
         <v>0</v>
       </c>
       <c r="J24" t="s">
@@ -3329,14 +3350,14 @@
       <c r="E25" t="s">
         <v>313</v>
       </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H25">
-        <f>E25*VALUE(LEFT(G25, FIND(":", G25)-1))</f>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I25">
+        <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
         <v>0</v>
       </c>
       <c r="J25" t="s">
@@ -3358,14 +3379,17 @@
       <c r="E26" t="s">
         <v>314</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H26">
-        <f>E26*VALUE(LEFT(G26, FIND(":", G26)-1))</f>
+        <v>325</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I26">
+        <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
         <v>0</v>
       </c>
       <c r="J26" t="s">
@@ -3387,14 +3411,14 @@
       <c r="E27" t="s">
         <v>313</v>
       </c>
-      <c r="F27" s="1">
-        <v>0</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H27">
-        <f>E27*VALUE(LEFT(G27, FIND(":", G27)-1))</f>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I27">
+        <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
         <v>0</v>
       </c>
       <c r="J27" t="s">
@@ -3418,14 +3442,14 @@
       <c r="E28" t="s">
         <v>313</v>
       </c>
-      <c r="F28" s="1">
-        <v>0</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H28">
-        <f>E28*VALUE(LEFT(G28, FIND(":", G28)-1))</f>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I28">
+        <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
         <v>0</v>
       </c>
       <c r="J28" t="s">
@@ -3447,14 +3471,14 @@
       <c r="E29" t="s">
         <v>313</v>
       </c>
-      <c r="F29" s="1">
-        <v>0</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H29">
-        <f>E29*VALUE(LEFT(G29, FIND(":", G29)-1))</f>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I29">
+        <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
         <v>0</v>
       </c>
       <c r="J29" t="s">
@@ -3476,14 +3500,14 @@
       <c r="E30" t="s">
         <v>313</v>
       </c>
-      <c r="F30" s="1">
-        <v>0</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H30">
-        <f>E30*VALUE(LEFT(G30, FIND(":", G30)-1))</f>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I30">
+        <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
         <v>0</v>
       </c>
       <c r="J30" t="s">
@@ -3505,14 +3529,14 @@
       <c r="E31" t="s">
         <v>313</v>
       </c>
-      <c r="F31" s="1">
-        <v>0</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H31">
-        <f>E31*VALUE(LEFT(G31, FIND(":", G31)-1))</f>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I31">
+        <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
         <v>0</v>
       </c>
       <c r="J31" t="s">
@@ -3534,14 +3558,14 @@
       <c r="E32" t="s">
         <v>313</v>
       </c>
-      <c r="F32" s="1">
-        <v>0</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H32">
-        <f>E32*VALUE(LEFT(G32, FIND(":", G32)-1))</f>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I32">
+        <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
         <v>0</v>
       </c>
       <c r="J32" t="s">
@@ -3563,14 +3587,14 @@
       <c r="E33" t="s">
         <v>313</v>
       </c>
-      <c r="F33" s="1">
-        <v>0</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H33">
-        <f>E33*VALUE(LEFT(G33, FIND(":", G33)-1))</f>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I33">
+        <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
         <v>0</v>
       </c>
       <c r="J33" t="s">
@@ -3594,14 +3618,14 @@
       <c r="E34" t="s">
         <v>313</v>
       </c>
-      <c r="F34" s="1">
-        <v>0</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H34">
-        <f>E34*VALUE(LEFT(G34, FIND(":", G34)-1))</f>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I34">
+        <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
         <v>0</v>
       </c>
       <c r="J34" t="s">
@@ -3623,14 +3647,14 @@
       <c r="E35" t="s">
         <v>313</v>
       </c>
-      <c r="F35" s="1">
-        <v>0</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H35">
-        <f>E35*VALUE(LEFT(G35, FIND(":", G35)-1))</f>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I35">
+        <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
         <v>0</v>
       </c>
       <c r="J35" t="s">
@@ -3652,14 +3676,14 @@
       <c r="E36" t="s">
         <v>314</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36">
         <v>1</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="H36">
-        <f>E36*VALUE(LEFT(G36, FIND(":", G36)-1))</f>
+      <c r="H36" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="I36">
+        <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
         <v>0</v>
       </c>
       <c r="J36" t="s">
@@ -3681,14 +3705,14 @@
       <c r="E37" t="s">
         <v>313</v>
       </c>
-      <c r="F37" s="1">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H37">
-        <f>E37*VALUE(LEFT(G37, FIND(":", G37)-1))</f>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I37">
+        <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
         <v>0</v>
       </c>
       <c r="J37" t="s">
@@ -3710,14 +3734,14 @@
       <c r="E38" t="s">
         <v>313</v>
       </c>
-      <c r="F38" s="1">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H38">
-        <f>E38*VALUE(LEFT(G38, FIND(":", G38)-1))</f>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I38">
+        <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
         <v>0</v>
       </c>
       <c r="J38" t="s">
@@ -3739,14 +3763,14 @@
       <c r="E39" t="s">
         <v>314</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39">
         <v>1</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="H39">
-        <f>E39*VALUE(LEFT(G39, FIND(":", G39)-1))</f>
+      <c r="H39" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="I39">
+        <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
         <v>0</v>
       </c>
       <c r="J39" t="s">
@@ -3772,14 +3796,14 @@
       <c r="E40" t="s">
         <v>314</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40">
         <v>1</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="H40">
-        <f>E40*VALUE(LEFT(G40, FIND(":", G40)-1))</f>
+      <c r="H40" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="I40">
+        <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
         <v>0</v>
       </c>
       <c r="J40" t="s">
@@ -3801,14 +3825,17 @@
       <c r="E41" t="s">
         <v>314</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41">
         <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H41">
-        <f>E41*VALUE(LEFT(G41, FIND(":", G41)-1))</f>
+        <v>326</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I41">
+        <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
         <v>0</v>
       </c>
       <c r="J41" t="s">
@@ -3830,14 +3857,14 @@
       <c r="E42" t="s">
         <v>314</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42">
         <v>1</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="H42">
-        <f>E42*VALUE(LEFT(G42, FIND(":", G42)-1))</f>
+      <c r="H42" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="I42">
+        <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
         <v>0</v>
       </c>
       <c r="J42" t="s">
@@ -3859,14 +3886,14 @@
       <c r="E43" t="s">
         <v>313</v>
       </c>
-      <c r="F43" s="1">
-        <v>0</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H43">
-        <f>E43*VALUE(LEFT(G43, FIND(":", G43)-1))</f>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I43">
+        <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
         <v>0</v>
       </c>
       <c r="J43" t="s">
@@ -3888,14 +3915,14 @@
       <c r="E44" t="s">
         <v>313</v>
       </c>
-      <c r="F44" s="1">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H44">
-        <f>E44*VALUE(LEFT(G44, FIND(":", G44)-1))</f>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I44">
+        <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
         <v>0</v>
       </c>
       <c r="J44" t="s">
@@ -3917,14 +3944,14 @@
       <c r="E45" t="s">
         <v>313</v>
       </c>
-      <c r="F45" s="1">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H45">
-        <f>E45*VALUE(LEFT(G45, FIND(":", G45)-1))</f>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I45">
+        <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
         <v>0</v>
       </c>
       <c r="J45" t="s">
@@ -3946,14 +3973,14 @@
       <c r="E46" t="s">
         <v>313</v>
       </c>
-      <c r="F46" s="1">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H46">
-        <f>E46*VALUE(LEFT(G46, FIND(":", G46)-1))</f>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I46">
+        <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
         <v>0</v>
       </c>
       <c r="J46" t="s">
@@ -3975,14 +4002,14 @@
       <c r="E47" t="s">
         <v>313</v>
       </c>
-      <c r="F47" s="1">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H47">
-        <f>E47*VALUE(LEFT(G47, FIND(":", G47)-1))</f>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I47">
+        <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
         <v>0</v>
       </c>
       <c r="J47" t="s">
@@ -4004,14 +4031,17 @@
       <c r="E48" t="s">
         <v>314</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48">
         <v>1</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H48">
-        <f>E48*VALUE(LEFT(G48, FIND(":", G48)-1))</f>
+        <v>327</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I48">
+        <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
         <v>0</v>
       </c>
       <c r="J48" t="s">
@@ -4033,14 +4063,14 @@
       <c r="E49" t="s">
         <v>313</v>
       </c>
-      <c r="F49" s="1">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H49">
-        <f>E49*VALUE(LEFT(G49, FIND(":", G49)-1))</f>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I49">
+        <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
         <v>0</v>
       </c>
       <c r="J49" t="s">
@@ -4062,14 +4092,14 @@
       <c r="E50" t="s">
         <v>313</v>
       </c>
-      <c r="F50" s="1">
-        <v>0</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H50">
-        <f>E50*VALUE(LEFT(G50, FIND(":", G50)-1))</f>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I50">
+        <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
         <v>0</v>
       </c>
       <c r="J50" t="s">
@@ -4091,14 +4121,14 @@
       <c r="E51" t="s">
         <v>313</v>
       </c>
-      <c r="F51" s="1">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H51">
-        <f>E51*VALUE(LEFT(G51, FIND(":", G51)-1))</f>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I51">
+        <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
         <v>0</v>
       </c>
       <c r="J51" t="s">
@@ -4122,14 +4152,14 @@
       <c r="E52" t="s">
         <v>316</v>
       </c>
-      <c r="F52" s="1">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H52">
-        <f>E52*VALUE(LEFT(G52, FIND(":", G52)-1))</f>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I52">
+        <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
         <v>0</v>
       </c>
       <c r="J52" t="s">
@@ -4151,14 +4181,14 @@
       <c r="E53" t="s">
         <v>316</v>
       </c>
-      <c r="F53" s="1">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H53">
-        <f>E53*VALUE(LEFT(G53, FIND(":", G53)-1))</f>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I53">
+        <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
         <v>0</v>
       </c>
       <c r="J53" t="s">
@@ -4180,14 +4210,14 @@
       <c r="E54" t="s">
         <v>316</v>
       </c>
-      <c r="F54" s="1">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H54">
-        <f>E54*VALUE(LEFT(G54, FIND(":", G54)-1))</f>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I54">
+        <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
         <v>0</v>
       </c>
       <c r="J54" t="s">
@@ -4209,14 +4239,14 @@
       <c r="E55" t="s">
         <v>316</v>
       </c>
-      <c r="F55" s="1">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H55">
-        <f>E55*VALUE(LEFT(G55, FIND(":", G55)-1))</f>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I55">
+        <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
         <v>0</v>
       </c>
       <c r="J55" t="s">
@@ -4238,14 +4268,14 @@
       <c r="E56" t="s">
         <v>316</v>
       </c>
-      <c r="F56" s="1">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H56">
-        <f>E56*VALUE(LEFT(G56, FIND(":", G56)-1))</f>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I56">
+        <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
         <v>0</v>
       </c>
       <c r="J56" t="s">
@@ -4267,14 +4297,14 @@
       <c r="E57" t="s">
         <v>316</v>
       </c>
-      <c r="F57" s="1">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H57">
-        <f>E57*VALUE(LEFT(G57, FIND(":", G57)-1))</f>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I57">
+        <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
         <v>0</v>
       </c>
       <c r="J57" t="s">
@@ -4298,14 +4328,14 @@
       <c r="E58" t="s">
         <v>314</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58">
         <v>1</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="H58">
-        <f>E58*VALUE(LEFT(G58, FIND(":", G58)-1))</f>
+      <c r="H58" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="I58">
+        <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
         <v>0</v>
       </c>
       <c r="J58" t="s">
@@ -4327,14 +4357,14 @@
       <c r="E59" t="s">
         <v>313</v>
       </c>
-      <c r="F59" s="1">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H59">
-        <f>E59*VALUE(LEFT(G59, FIND(":", G59)-1))</f>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I59">
+        <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
         <v>0</v>
       </c>
       <c r="J59" t="s">
@@ -4356,14 +4386,14 @@
       <c r="E60" t="s">
         <v>313</v>
       </c>
-      <c r="F60" s="1">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H60">
-        <f>E60*VALUE(LEFT(G60, FIND(":", G60)-1))</f>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I60">
+        <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
         <v>0</v>
       </c>
       <c r="J60" t="s">
@@ -4385,14 +4415,14 @@
       <c r="E61" t="s">
         <v>314</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61">
         <v>1</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="H61">
-        <f>E61*VALUE(LEFT(G61, FIND(":", G61)-1))</f>
+      <c r="H61" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="I61">
+        <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
         <v>0</v>
       </c>
       <c r="J61" t="s">
@@ -4414,14 +4444,14 @@
       <c r="E62" t="s">
         <v>313</v>
       </c>
-      <c r="F62" s="1">
-        <v>0</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H62">
-        <f>E62*VALUE(LEFT(G62, FIND(":", G62)-1))</f>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I62">
+        <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
         <v>0</v>
       </c>
       <c r="J62" t="s">
@@ -4443,14 +4473,14 @@
       <c r="E63" t="s">
         <v>313</v>
       </c>
-      <c r="F63" s="1">
-        <v>0</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H63">
-        <f>E63*VALUE(LEFT(G63, FIND(":", G63)-1))</f>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I63">
+        <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
         <v>0</v>
       </c>
       <c r="J63" t="s">
@@ -4474,14 +4504,14 @@
       <c r="E64" t="s">
         <v>314</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64">
         <v>1</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="H64">
-        <f>E64*VALUE(LEFT(G64, FIND(":", G64)-1))</f>
+      <c r="H64" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="I64">
+        <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
         <v>0</v>
       </c>
       <c r="J64" t="s">
@@ -4503,14 +4533,14 @@
       <c r="E65" t="s">
         <v>314</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65">
         <v>1</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="H65">
-        <f>E65*VALUE(LEFT(G65, FIND(":", G65)-1))</f>
+      <c r="H65" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="I65">
+        <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
         <v>0</v>
       </c>
       <c r="J65" t="s">
@@ -4532,14 +4562,14 @@
       <c r="E66" t="s">
         <v>313</v>
       </c>
-      <c r="F66" s="1">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H66">
-        <f>E66*VALUE(LEFT(G66, FIND(":", G66)-1))</f>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I66">
+        <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
         <v>0</v>
       </c>
       <c r="J66" t="s">
@@ -4561,14 +4591,14 @@
       <c r="E67" t="s">
         <v>313</v>
       </c>
-      <c r="F67" s="1">
-        <v>0</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H67">
-        <f>E67*VALUE(LEFT(G67, FIND(":", G67)-1))</f>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I67">
+        <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
         <v>0</v>
       </c>
       <c r="J67" t="s">
@@ -4590,14 +4620,14 @@
       <c r="E68" t="s">
         <v>313</v>
       </c>
-      <c r="F68" s="1">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H68">
-        <f>E68*VALUE(LEFT(G68, FIND(":", G68)-1))</f>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I68">
+        <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
         <v>0</v>
       </c>
       <c r="J68" t="s">
@@ -4619,14 +4649,17 @@
       <c r="E69" t="s">
         <v>314</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H69">
-        <f>E69*VALUE(LEFT(G69, FIND(":", G69)-1))</f>
+        <v>328</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I69">
+        <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
         <v>0</v>
       </c>
       <c r="J69" t="s">
@@ -4650,14 +4683,14 @@
       <c r="E70" t="s">
         <v>313</v>
       </c>
-      <c r="F70" s="1">
-        <v>0</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H70">
-        <f>E70*VALUE(LEFT(G70, FIND(":", G70)-1))</f>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I70">
+        <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
         <v>0</v>
       </c>
       <c r="J70" t="s">
@@ -4679,14 +4712,14 @@
       <c r="E71" t="s">
         <v>314</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71">
         <v>1</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="H71">
-        <f>E71*VALUE(LEFT(G71, FIND(":", G71)-1))</f>
+      <c r="H71" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="I71">
+        <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
         <v>0</v>
       </c>
       <c r="J71" t="s">
@@ -4708,14 +4741,14 @@
       <c r="E72" t="s">
         <v>314</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72">
         <v>1</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="H72">
-        <f>E72*VALUE(LEFT(G72, FIND(":", G72)-1))</f>
+      <c r="H72" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="I72">
+        <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
         <v>0</v>
       </c>
       <c r="J72" t="s">
@@ -4737,14 +4770,14 @@
       <c r="E73" t="s">
         <v>313</v>
       </c>
-      <c r="F73" s="1">
-        <v>0</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H73">
-        <f>E73*VALUE(LEFT(G73, FIND(":", G73)-1))</f>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I73">
+        <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
         <v>0</v>
       </c>
       <c r="J73" t="s">
@@ -4766,14 +4799,14 @@
       <c r="E74" t="s">
         <v>313</v>
       </c>
-      <c r="F74" s="1">
-        <v>0</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H74">
-        <f>E74*VALUE(LEFT(G74, FIND(":", G74)-1))</f>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I74">
+        <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
         <v>0</v>
       </c>
       <c r="J74" t="s">
@@ -4795,14 +4828,14 @@
       <c r="E75" t="s">
         <v>313</v>
       </c>
-      <c r="F75" s="1">
-        <v>0</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H75">
-        <f>E75*VALUE(LEFT(G75, FIND(":", G75)-1))</f>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I75">
+        <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
         <v>0</v>
       </c>
       <c r="J75" t="s">
@@ -4828,14 +4861,14 @@
       <c r="E76" t="s">
         <v>313</v>
       </c>
-      <c r="F76" s="1">
-        <v>0</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H76">
-        <f>E76*VALUE(LEFT(G76, FIND(":", G76)-1))</f>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I76">
+        <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
         <v>0</v>
       </c>
       <c r="J76" t="s">
@@ -4857,14 +4890,14 @@
       <c r="E77" t="s">
         <v>313</v>
       </c>
-      <c r="F77" s="1">
-        <v>0</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H77">
-        <f>E77*VALUE(LEFT(G77, FIND(":", G77)-1))</f>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I77">
+        <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
         <v>0</v>
       </c>
       <c r="J77" t="s">
@@ -4886,14 +4919,14 @@
       <c r="E78" t="s">
         <v>313</v>
       </c>
-      <c r="F78" s="1">
-        <v>0</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H78">
-        <f>E78*VALUE(LEFT(G78, FIND(":", G78)-1))</f>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I78">
+        <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
         <v>0</v>
       </c>
       <c r="J78" t="s">
@@ -4915,14 +4948,14 @@
       <c r="E79" t="s">
         <v>313</v>
       </c>
-      <c r="F79" s="1">
-        <v>0</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H79">
-        <f>E79*VALUE(LEFT(G79, FIND(":", G79)-1))</f>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I79">
+        <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
         <v>0</v>
       </c>
       <c r="J79" t="s">
@@ -4944,14 +4977,14 @@
       <c r="E80" t="s">
         <v>314</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80">
         <v>1</v>
       </c>
-      <c r="G80" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="H80">
-        <f>E80*VALUE(LEFT(G80, FIND(":", G80)-1))</f>
+      <c r="H80" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="I80">
+        <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
         <v>0</v>
       </c>
       <c r="J80" t="s">
@@ -4973,14 +5006,14 @@
       <c r="E81" t="s">
         <v>313</v>
       </c>
-      <c r="F81" s="1">
-        <v>0</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H81">
-        <f>E81*VALUE(LEFT(G81, FIND(":", G81)-1))</f>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I81">
+        <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
         <v>0</v>
       </c>
       <c r="J81" t="s">
@@ -5004,14 +5037,14 @@
       <c r="E82" t="s">
         <v>314</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82">
         <v>1</v>
       </c>
-      <c r="G82" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="H82">
-        <f>E82*VALUE(LEFT(G82, FIND(":", G82)-1))</f>
+      <c r="H82" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="I82">
+        <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
         <v>0</v>
       </c>
       <c r="J82" t="s">
@@ -5033,14 +5066,14 @@
       <c r="E83" t="s">
         <v>314</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83">
         <v>1</v>
       </c>
-      <c r="G83" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="H83">
-        <f>E83*VALUE(LEFT(G83, FIND(":", G83)-1))</f>
+      <c r="H83" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="I83">
+        <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
         <v>0</v>
       </c>
       <c r="J83" t="s">
@@ -5062,14 +5095,14 @@
       <c r="E84" t="s">
         <v>313</v>
       </c>
-      <c r="F84" s="1">
-        <v>0</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H84">
-        <f>E84*VALUE(LEFT(G84, FIND(":", G84)-1))</f>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I84">
+        <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
         <v>0</v>
       </c>
       <c r="J84" t="s">
@@ -5091,14 +5124,14 @@
       <c r="E85" t="s">
         <v>313</v>
       </c>
-      <c r="F85" s="1">
-        <v>0</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H85">
-        <f>E85*VALUE(LEFT(G85, FIND(":", G85)-1))</f>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I85">
+        <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
         <v>0</v>
       </c>
       <c r="J85" t="s">
@@ -5120,14 +5153,14 @@
       <c r="E86" t="s">
         <v>313</v>
       </c>
-      <c r="F86" s="1">
-        <v>0</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H86">
-        <f>E86*VALUE(LEFT(G86, FIND(":", G86)-1))</f>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I86">
+        <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
         <v>0</v>
       </c>
       <c r="J86" t="s">
@@ -5149,14 +5182,14 @@
       <c r="E87" t="s">
         <v>313</v>
       </c>
-      <c r="F87" s="1">
-        <v>0</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H87">
-        <f>E87*VALUE(LEFT(G87, FIND(":", G87)-1))</f>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I87">
+        <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
         <v>0</v>
       </c>
       <c r="J87" t="s">
@@ -5180,14 +5213,14 @@
       <c r="E88" t="s">
         <v>313</v>
       </c>
-      <c r="F88" s="1">
-        <v>0</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H88">
-        <f>E88*VALUE(LEFT(G88, FIND(":", G88)-1))</f>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I88">
+        <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
         <v>0</v>
       </c>
       <c r="J88" t="s">
@@ -5209,14 +5242,17 @@
       <c r="E89" t="s">
         <v>314</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89">
         <v>1</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H89">
-        <f>E89*VALUE(LEFT(G89, FIND(":", G89)-1))</f>
+        <v>329</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I89">
+        <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
         <v>0</v>
       </c>
       <c r="J89" t="s">
@@ -5238,14 +5274,14 @@
       <c r="E90" t="s">
         <v>314</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90">
         <v>1</v>
       </c>
-      <c r="G90" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H90">
-        <f>E90*VALUE(LEFT(G90, FIND(":", G90)-1))</f>
+      <c r="H90" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I90">
+        <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
         <v>0</v>
       </c>
       <c r="J90" t="s">
@@ -5267,14 +5303,17 @@
       <c r="E91" t="s">
         <v>314</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91">
         <v>1</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="H91">
-        <f>E91*VALUE(LEFT(G91, FIND(":", G91)-1))</f>
+        <v>330</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="I91">
+        <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
         <v>0</v>
       </c>
       <c r="J91" t="s">
@@ -5296,14 +5335,14 @@
       <c r="E92" t="s">
         <v>314</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92">
         <v>1</v>
       </c>
-      <c r="G92" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="H92">
-        <f>E92*VALUE(LEFT(G92, FIND(":", G92)-1))</f>
+      <c r="H92" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="I92">
+        <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
         <v>0</v>
       </c>
       <c r="J92" t="s">
@@ -5325,14 +5364,17 @@
       <c r="E93" t="s">
         <v>314</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H93">
-        <f>E93*VALUE(LEFT(G93, FIND(":", G93)-1))</f>
+        <v>331</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I93">
+        <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
         <v>0</v>
       </c>
       <c r="J93" t="s">
@@ -5356,14 +5398,17 @@
       <c r="E94" t="s">
         <v>315</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94">
         <v>1</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H94">
-        <f>E94*VALUE(LEFT(G94, FIND(":", G94)-1))</f>
+        <v>332</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I94">
+        <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
         <v>0</v>
       </c>
       <c r="J94" t="s">
@@ -5385,14 +5430,17 @@
       <c r="E95" t="s">
         <v>315</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95">
         <v>1</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H95">
-        <f>E95*VALUE(LEFT(G95, FIND(":", G95)-1))</f>
+        <v>333</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I95">
+        <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
         <v>0</v>
       </c>
       <c r="J95" t="s">
@@ -5414,14 +5462,17 @@
       <c r="E96" t="s">
         <v>315</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96">
         <v>1</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H96">
-        <f>E96*VALUE(LEFT(G96, FIND(":", G96)-1))</f>
+        <v>334</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I96">
+        <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
         <v>0</v>
       </c>
       <c r="J96" t="s">
@@ -5443,14 +5494,17 @@
       <c r="E97" t="s">
         <v>315</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97">
         <v>1</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H97">
-        <f>E97*VALUE(LEFT(G97, FIND(":", G97)-1))</f>
+        <v>335</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I97">
+        <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
         <v>0</v>
       </c>
       <c r="J97" t="s">
@@ -5472,14 +5526,17 @@
       <c r="E98" t="s">
         <v>314</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98">
         <v>1</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H98">
-        <f>E98*VALUE(LEFT(G98, FIND(":", G98)-1))</f>
+        <v>336</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I98">
+        <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
         <v>0</v>
       </c>
       <c r="J98" t="s">
@@ -5501,14 +5558,14 @@
       <c r="E99" t="s">
         <v>314</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99">
         <v>1</v>
       </c>
-      <c r="G99" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="H99">
-        <f>E99*VALUE(LEFT(G99, FIND(":", G99)-1))</f>
+      <c r="H99" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="I99">
+        <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
         <v>0</v>
       </c>
       <c r="J99" t="s">
@@ -5530,14 +5587,17 @@
       <c r="E100" t="s">
         <v>315</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F100">
         <v>1</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H100">
-        <f>E100*VALUE(LEFT(G100, FIND(":", G100)-1))</f>
+        <v>337</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I100">
+        <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
         <v>0</v>
       </c>
       <c r="J100" t="s">
@@ -5561,14 +5621,17 @@
       <c r="E101" t="s">
         <v>314</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F101">
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H101">
-        <f>E101*VALUE(LEFT(G101, FIND(":", G101)-1))</f>
+        <v>338</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I101">
+        <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
         <v>0</v>
       </c>
       <c r="J101" t="s">
@@ -5590,14 +5653,14 @@
       <c r="E102" t="s">
         <v>313</v>
       </c>
-      <c r="F102" s="1">
-        <v>0</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H102">
-        <f>E102*VALUE(LEFT(G102, FIND(":", G102)-1))</f>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I102">
+        <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
         <v>0</v>
       </c>
       <c r="J102" t="s">
@@ -5619,14 +5682,14 @@
       <c r="E103" t="s">
         <v>313</v>
       </c>
-      <c r="F103" s="1">
-        <v>0</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H103">
-        <f>E103*VALUE(LEFT(G103, FIND(":", G103)-1))</f>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I103">
+        <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
         <v>0</v>
       </c>
       <c r="J103" t="s">
@@ -5648,14 +5711,14 @@
       <c r="E104" t="s">
         <v>313</v>
       </c>
-      <c r="F104" s="1">
-        <v>0</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H104">
-        <f>E104*VALUE(LEFT(G104, FIND(":", G104)-1))</f>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I104">
+        <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
         <v>0</v>
       </c>
       <c r="J104" t="s">
@@ -5677,14 +5740,14 @@
       <c r="E105" t="s">
         <v>313</v>
       </c>
-      <c r="F105" s="1">
-        <v>0</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H105">
-        <f>E105*VALUE(LEFT(G105, FIND(":", G105)-1))</f>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I105">
+        <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
         <v>0</v>
       </c>
       <c r="J105" t="s">
@@ -5706,14 +5769,14 @@
       <c r="E106" t="s">
         <v>314</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F106">
         <v>1</v>
       </c>
-      <c r="G106" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H106">
-        <f>E106*VALUE(LEFT(G106, FIND(":", G106)-1))</f>
+      <c r="H106" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I106">
+        <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
         <v>0</v>
       </c>
       <c r="J106" t="s">
@@ -5739,14 +5802,17 @@
       <c r="E107" t="s">
         <v>314</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F107">
         <v>1</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H107">
-        <f>E107*VALUE(LEFT(G107, FIND(":", G107)-1))</f>
+        <v>339</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I107">
+        <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
         <v>0</v>
       </c>
       <c r="J107" t="s">
@@ -5768,14 +5834,17 @@
       <c r="E108" t="s">
         <v>314</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F108">
         <v>1</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="H108">
-        <f>E108*VALUE(LEFT(G108, FIND(":", G108)-1))</f>
+        <v>340</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="I108">
+        <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
         <v>0</v>
       </c>
       <c r="J108" t="s">
@@ -5797,14 +5866,17 @@
       <c r="E109" t="s">
         <v>314</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F109">
         <v>1</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H109">
-        <f>E109*VALUE(LEFT(G109, FIND(":", G109)-1))</f>
+        <v>341</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I109">
+        <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
         <v>0</v>
       </c>
       <c r="J109" t="s">
@@ -5826,14 +5898,17 @@
       <c r="E110" t="s">
         <v>314</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110">
         <v>1</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="H110">
-        <f>E110*VALUE(LEFT(G110, FIND(":", G110)-1))</f>
+        <v>342</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="I110">
+        <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
         <v>0</v>
       </c>
       <c r="J110" t="s">
@@ -5855,14 +5930,17 @@
       <c r="E111" t="s">
         <v>314</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111">
         <v>1</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="H111">
-        <f>E111*VALUE(LEFT(G111, FIND(":", G111)-1))</f>
+        <v>343</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="I111">
+        <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
         <v>0</v>
       </c>
       <c r="J111" t="s">
@@ -5884,14 +5962,17 @@
       <c r="E112" t="s">
         <v>314</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H112">
-        <f>E112*VALUE(LEFT(G112, FIND(":", G112)-1))</f>
+        <v>344</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I112">
+        <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
         <v>0</v>
       </c>
       <c r="J112" t="s">
@@ -5913,14 +5994,14 @@
       <c r="E113" t="s">
         <v>313</v>
       </c>
-      <c r="F113" s="1">
-        <v>0</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H113">
-        <f>E113*VALUE(LEFT(G113, FIND(":", G113)-1))</f>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I113">
+        <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
         <v>0</v>
       </c>
       <c r="J113" t="s">
@@ -5944,14 +6025,17 @@
       <c r="E114" t="s">
         <v>314</v>
       </c>
-      <c r="F114" s="1">
+      <c r="F114">
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H114">
-        <f>E114*VALUE(LEFT(G114, FIND(":", G114)-1))</f>
+        <v>345</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I114">
+        <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
         <v>0</v>
       </c>
       <c r="J114" t="s">
@@ -5973,14 +6057,17 @@
       <c r="E115" t="s">
         <v>314</v>
       </c>
-      <c r="F115" s="1">
+      <c r="F115">
         <v>1</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H115">
-        <f>E115*VALUE(LEFT(G115, FIND(":", G115)-1))</f>
+        <v>346</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I115">
+        <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
         <v>0</v>
       </c>
       <c r="J115" t="s">
@@ -6002,14 +6089,14 @@
       <c r="E116" t="s">
         <v>314</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F116">
         <v>1</v>
       </c>
-      <c r="G116" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="H116">
-        <f>E116*VALUE(LEFT(G116, FIND(":", G116)-1))</f>
+      <c r="H116" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="I116">
+        <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
         <v>0</v>
       </c>
       <c r="J116" t="s">
@@ -6031,14 +6118,14 @@
       <c r="E117" t="s">
         <v>313</v>
       </c>
-      <c r="F117" s="1">
-        <v>0</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H117">
-        <f>E117*VALUE(LEFT(G117, FIND(":", G117)-1))</f>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I117">
+        <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
         <v>0</v>
       </c>
       <c r="J117" t="s">
@@ -6060,14 +6147,14 @@
       <c r="E118" t="s">
         <v>313</v>
       </c>
-      <c r="F118" s="1">
-        <v>0</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H118">
-        <f>E118*VALUE(LEFT(G118, FIND(":", G118)-1))</f>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I118">
+        <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
         <v>0</v>
       </c>
       <c r="J118" t="s">
@@ -6089,14 +6176,17 @@
       <c r="E119" t="s">
         <v>314</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F119">
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H119">
-        <f>E119*VALUE(LEFT(G119, FIND(":", G119)-1))</f>
+        <v>347</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I119">
+        <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
         <v>0</v>
       </c>
       <c r="J119" t="s">
@@ -6118,14 +6208,14 @@
       <c r="E120" t="s">
         <v>313</v>
       </c>
-      <c r="F120" s="1">
-        <v>0</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H120">
-        <f>E120*VALUE(LEFT(G120, FIND(":", G120)-1))</f>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I120">
+        <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
         <v>0</v>
       </c>
       <c r="J120" t="s">
@@ -6147,16 +6237,16 @@
         <v>297</v>
       </c>
       <c r="E121" t="s">
-        <v>313</v>
-      </c>
-      <c r="F121" s="1">
-        <v>0</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H121">
-        <f>E121*VALUE(LEFT(G121, FIND(":", G121)-1))</f>
+        <v>317</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I121">
+        <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
         <v>0</v>
       </c>
       <c r="J121" t="s">
@@ -6178,14 +6268,14 @@
       <c r="E122" t="s">
         <v>313</v>
       </c>
-      <c r="F122" s="1">
-        <v>0</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H122">
-        <f>E122*VALUE(LEFT(G122, FIND(":", G122)-1))</f>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I122">
+        <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
         <v>0</v>
       </c>
       <c r="J122" t="s">
@@ -6207,14 +6297,14 @@
       <c r="E123" t="s">
         <v>313</v>
       </c>
-      <c r="F123" s="1">
-        <v>0</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H123">
-        <f>E123*VALUE(LEFT(G123, FIND(":", G123)-1))</f>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I123">
+        <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
         <v>0</v>
       </c>
       <c r="J123" t="s">
@@ -6236,14 +6326,14 @@
       <c r="E124" t="s">
         <v>314</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F124">
         <v>1</v>
       </c>
-      <c r="G124" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="H124">
-        <f>E124*VALUE(LEFT(G124, FIND(":", G124)-1))</f>
+      <c r="H124" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I124">
+        <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
         <v>0</v>
       </c>
       <c r="J124" t="s">
@@ -6265,14 +6355,14 @@
       <c r="E125" t="s">
         <v>313</v>
       </c>
-      <c r="F125" s="1">
-        <v>0</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H125">
-        <f>E125*VALUE(LEFT(G125, FIND(":", G125)-1))</f>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I125">
+        <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
         <v>0</v>
       </c>
       <c r="J125" t="s">
@@ -6294,14 +6384,17 @@
       <c r="E126" t="s">
         <v>314</v>
       </c>
-      <c r="F126" s="1">
+      <c r="F126">
         <v>1</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H126">
-        <f>E126*VALUE(LEFT(G126, FIND(":", G126)-1))</f>
+        <v>348</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I126">
+        <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
         <v>0</v>
       </c>
       <c r="J126" t="s">
@@ -6323,14 +6416,17 @@
       <c r="E127" t="s">
         <v>314</v>
       </c>
-      <c r="F127" s="1">
+      <c r="F127">
         <v>1</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H127">
-        <f>E127*VALUE(LEFT(G127, FIND(":", G127)-1))</f>
+        <v>349</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I127">
+        <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
         <v>0</v>
       </c>
       <c r="J127" t="s">
@@ -6352,14 +6448,14 @@
       <c r="E128" t="s">
         <v>313</v>
       </c>
-      <c r="F128" s="1">
-        <v>0</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H128">
-        <f>E128*VALUE(LEFT(G128, FIND(":", G128)-1))</f>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I128">
+        <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
         <v>0</v>
       </c>
       <c r="J128" t="s">
@@ -6379,16 +6475,16 @@
         <v>305</v>
       </c>
       <c r="E129" t="s">
-        <v>317</v>
-      </c>
-      <c r="F129" s="1">
+        <v>318</v>
+      </c>
+      <c r="F129">
         <v>1</v>
       </c>
-      <c r="G129" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="H129">
-        <f>E129*VALUE(LEFT(G129, FIND(":", G129)-1))</f>
+      <c r="H129" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I129">
+        <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
         <v>0</v>
       </c>
       <c r="J129" t="s">
@@ -6412,14 +6508,14 @@
       <c r="E130" t="s">
         <v>313</v>
       </c>
-      <c r="F130" s="1">
-        <v>0</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H130">
-        <f>E130*VALUE(LEFT(G130, FIND(":", G130)-1))</f>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I130">
+        <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
         <v>0</v>
       </c>
       <c r="J130" t="s">
@@ -6441,14 +6537,17 @@
       <c r="E131" t="s">
         <v>314</v>
       </c>
-      <c r="F131" s="1">
+      <c r="F131">
         <v>1</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H131">
-        <f>E131*VALUE(LEFT(G131, FIND(":", G131)-1))</f>
+        <v>350</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I131">
+        <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
         <v>0</v>
       </c>
       <c r="J131" t="s">
@@ -6470,14 +6569,17 @@
       <c r="E132" t="s">
         <v>314</v>
       </c>
-      <c r="F132" s="1">
+      <c r="F132">
         <v>1</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H132">
-        <f>E132*VALUE(LEFT(G132, FIND(":", G132)-1))</f>
+        <v>351</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I132">
+        <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
         <v>0</v>
       </c>
       <c r="J132" t="s">
@@ -6499,14 +6601,14 @@
       <c r="E133" t="s">
         <v>313</v>
       </c>
-      <c r="F133" s="1">
-        <v>0</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H133">
-        <f>E133*VALUE(LEFT(G133, FIND(":", G133)-1))</f>
+      <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I133">
+        <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
         <v>0</v>
       </c>
       <c r="J133" t="s">
@@ -6528,14 +6630,14 @@
       <c r="E134" t="s">
         <v>314</v>
       </c>
-      <c r="F134" s="1">
+      <c r="F134">
         <v>1</v>
       </c>
-      <c r="G134" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="H134">
-        <f>E134*VALUE(LEFT(G134, FIND(":", G134)-1))</f>
+      <c r="H134" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I134">
+        <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
         <v>0</v>
       </c>
       <c r="J134" t="s">
@@ -6557,14 +6659,14 @@
       <c r="E135" t="s">
         <v>313</v>
       </c>
-      <c r="F135" s="1">
-        <v>0</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H135">
-        <f>E135*VALUE(LEFT(G135, FIND(":", G135)-1))</f>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I135">
+        <f>F135*VALUE(LEFT(H135, FIND(":", H135)-1))</f>
         <v>0</v>
       </c>
       <c r="J135" t="s">
@@ -6586,14 +6688,14 @@
       <c r="E136" t="s">
         <v>313</v>
       </c>
-      <c r="F136" s="1">
-        <v>0</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H136">
-        <f>E136*VALUE(LEFT(G136, FIND(":", G136)-1))</f>
+      <c r="F136">
+        <v>0</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I136">
+        <f>F136*VALUE(LEFT(H136, FIND(":", H136)-1))</f>
         <v>0</v>
       </c>
       <c r="J136" t="s">
@@ -6632,409 +6734,409 @@
     <mergeCell ref="B130:B136"/>
   </mergeCells>
   <dataValidations count="135">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5">
       <formula1>"0: Not monitored,2: Reported,5: Manual remediation,10: Automated remediation"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7">
       <formula1>"0: 0 items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G10">
-      <formula1>"0: No items completed,3: item 1 completed,5: items 1, and 2 completed,8: items 1, 2, and 3 completed,10: items 1, 2, 3, and 4 completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10">
+      <formula1>"0: No items completed,3: item 1 completed,5: items 1. and 2 completed,8: items 1. 2. and 3 completed,10: items 1. 2. 3. and 4 completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G12">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G13">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G14">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G15">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G16">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G17">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H16">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G18">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G19">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G20">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G21">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G22">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G23">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H24">
       <formula1>"0: No rules established,10: Published policy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G25">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G26">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G27">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G28">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G29">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G30">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G31">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G32">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G33">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G34">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G35">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G36">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
       <formula1>"0: Not done,10: Done and clearly defined"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G37">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G38">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G39">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G40">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G41">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G42">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
       <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G43">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G44">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G45">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G46">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G47">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G48">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G49">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G50">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G51">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G52">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G53">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G54">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G55">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G56">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G57">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G58">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H56">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G59">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G60">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G61">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G62">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G63">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G64">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G66">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G67">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G68">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G69">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G70">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G71">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H70">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H71">
       <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G72">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G73">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G74">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G75">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G76">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G77">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G78">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G79">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G80">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H77">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H78">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
       <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G81">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G82">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H81">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G83">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H83">
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G84">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G85">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G86">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G87">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G88">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G89">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H84">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H85">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H86">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G90">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
       <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G91">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G92">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
       <formula1>"0: No alerting,10: Alerting exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G93">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G94">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G95">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G96">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G97">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
       <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G98">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G99">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G100">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H101">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G102">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G103">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G104">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G105">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G106">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H102">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H104">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H105">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H106">
       <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G107">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H107">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G108">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80% ,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G109">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H109">
       <formula1>"0: No items completed,5: 1 item  completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G110">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H110">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G111">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H111">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G112">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H112">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G113">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G114">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H113">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H114">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G115">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H115">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G116">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H116">
       <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G117">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G118">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G119">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H117">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H118">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H119">
       <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G120">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G121">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G122">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G123">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G124">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H120">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H121">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H122">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H123">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H124">
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G125">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G126">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H125">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H126">
       <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G127">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H127">
       <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G128">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H128">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H129">
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G130">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G131">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H130">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H131">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G132">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H132">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G133">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G134">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H133">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H134">
       <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G135">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G136">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H135">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H136">
       <formula1>"0: None"</formula1>
     </dataValidation>
   </dataValidations>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="424">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -70,6 +70,9 @@
     <t>Data Ingestion</t>
   </si>
   <si>
+    <t>Executive Strategy Alignment</t>
+  </si>
+  <si>
     <t>FinOps Assessment</t>
   </si>
   <si>
@@ -235,7 +238,7 @@
     <t>Share Reporting &amp; Definitions</t>
   </si>
   <si>
-    <t>Provide Cloud Metrics to Teams</t>
+    <t>Provide Technology Metrics to Teams</t>
   </si>
   <si>
     <t>Coordinate Policy Changes Broadly</t>
@@ -262,6 +265,18 @@
     <t>Resolve Variances &amp; Increase Coverage</t>
   </si>
   <si>
+    <t>Establish Executive Sponsorship</t>
+  </si>
+  <si>
+    <t>Define Decision Rights &amp; Guardrails</t>
+  </si>
+  <si>
+    <t>Build Multi-Year Investment Forecast</t>
+  </si>
+  <si>
+    <t>Establish Decision Support Cadence</t>
+  </si>
+  <si>
     <t>Establish Architecture Review Process</t>
   </si>
   <si>
@@ -667,6 +682,18 @@
     <t>112</t>
   </si>
   <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
     <t>061</t>
   </si>
   <si>
@@ -967,10 +994,19 @@
     <t>0.8.0</t>
   </si>
   <si>
+    <t>0.7.1</t>
+  </si>
+  <si>
+    <t>0.9.0</t>
+  </si>
+  <si>
+    <t>0.8.1</t>
+  </si>
+  <si>
+    <t>0.0.1</t>
+  </si>
+  <si>
     <t>0.5.0</t>
-  </si>
-  <si>
-    <t>0.7.1</t>
   </si>
   <si>
     <t>1.5.0</t>
@@ -1021,6 +1057,64 @@
 10*Ceil(x/5)</t>
   </si>
   <si>
+    <t>1. Identify key stakeholder teams and key contacts for each (ITAM, SRE, etc.)
+2. Document initial thoughts on how this other team may help FinOps goals
+3. Document initial thoughts on how the FinOps team may help the other team's goals
+4. Reach out to the other team with the initial summary of goals
+5. Meet with the other team to better understand how they work</t>
+  </si>
+  <si>
+    <t>* Align on new shared goals that will enhance both teams achievements
+* Determine what data is shared across teams to establish a single source of truth
+* Identify and agree on tasks that will lead to accomplishing shared goals
+* Determine which teams have capacity to work on goal tasks periodically
+* Incorporate tasks into team capacity planning and dependency workflows
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Agree on definitions of shared concepts across teams to reduce confusion
+* Adjust reporting so shared metrics are consistent and from the same source, even if multiple dashboards exist
+* Regularly align on interpretation of shared metrics to plan next steps and report those to leadership
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Share relevant data already maintained and tracked by FinOps
+* Share metric reporting and the calculations behind FinOps created metrics
+* Create new metrics from FinOps and other data based on needs of allied teams
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>1. Document new policies as a result of cross-functional collaboration goals
+2. Broad policy changes are accepted by governing and stakeholder teams
+3. Communication is distributed by all governing teams using shared language
+4. Change management procedures are followed for updated policy implementation
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>* Come up with shared responses as allied teams to external conflicts
+* Resolve internal conflicts before deciding on the next steps needed to reach shared goals
+* Communication to external teams or leaders includes the full story of how allied teams achieve goals together
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Document decision rights and approval authority for technology spend
+* Define and publish spend guardrails with named owners
+* Establish escalation path for spend exceptions
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Inventory vendor commitments across technology categories (cloud, SaaS, data center, AI)
+* Create a multi-year forecast incorporating renewal timelines and growth projections
+* Incorporate transition and modernization costs into the investment plan
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Define a regular review cadence for technology investment decisions
+* Deliver cost and outcome comparisons for competing initiatives at reviews
+* Track and report action follow-through from investment decisions
+10*Ceil(x/3)</t>
+  </si>
+  <si>
     <t>* Define process to address notifications from CSPs
 * Define cadence for review
 * Define exception criteria
@@ -1105,6 +1199,40 @@
 * Gather metrics on a cadence
 * Set goals/targets
 * Set up forecasting and anomaly detection on units
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>* Identify key business performance data to select from various operational areas
+* Agree on source of truth for business data with common terminology
+* Clearly define what a unit of value is for each business metric to be tracked
+* Agree on which costs to use in calculations (list, discounted, amortized, etc.)
+* Define formulas to allocate cost per unit of business value over the same time period to create a KPI
+* Changes to data ingestion, metric definitions, or cost allocations are documented and communicated
+10*Ceil(x/6)</t>
+  </si>
+  <si>
+    <t>* Continuously collect data over time for all inputs to unit economic equations
+* Automate unit economic calculations for each corresponding point in time for cost and business data
+* Create plots of unit economic metrics over time to easily report on and track trends
+* Show disaggregated data to compare unit metrics with standalone usage or rate changes
+* Include filters to show data by each relevant operational area of the business (product/segment/region/etc.)
+* Plots and dashboards are easily accessible by key stakeholders across the business
+10*Ceil(x/6)</t>
+  </si>
+  <si>
+    <t>* Collaborate with stakeholders on desired acceptable thresholds or goals for each unit economic value
+* Review data with stakeholders when metrics exceed acceptable thresholds in either direction
+* Incorporate metric reviews into the decision making processes of stakeholder departments
+* The FinOps team should periodically publish an analysis of major changes in the metrics dashboards
+as well as facilitate reviews of metrics, adoption data, modifications, and KPI refreshes
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>* Scenario plan for which metric values will drive the next decisions, behaviors, or outcomes needed
+* Investigate root causes for changes in metric values to determine next steps
+* Add to the backlog which actions are required to get unit metrics to a desired level
+* Unit economics influence the decisions in build vs buy, architecture design,
+ workload placement, migration, sourcing, pricing, etc.
 10*Ceil(x/4)</t>
   </si>
   <si>
@@ -1220,7 +1348,7 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 4, 'Condition': '1 item completed'}, {'Score': 7, 'Condition': '2 items completed'}, {'Score': 10, 'Condition': '3 items completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1, and 2 completed'}, {'Score': 8, 'Condition': 'items 1, 2, and 3 completed'}, {'Score': 10, 'Condition': 'items 1, 2, 3, and 4 completed'}]</t>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1-2 completed'}, {'Score': 8, 'Condition': 'items 1-3 completed'}, {'Score': 10, 'Condition': 'items 1-4 completed'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
@@ -1235,9 +1363,15 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 6, 'Condition': '3 items completed'}, {'Score': 8, 'Condition': '4 items completed'}, {'Score': 10, 'Condition': '5 items completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': 'item 1 completed'}, {'Score': 4, 'Condition': 'items 1-2 completed'}, {'Score': 6, 'Condition': 'items 1-3 completed'}, {'Score': 8, 'Condition': 'items 1-4 completed'}, {'Score': 10, 'Condition': 'items 1-5 completed'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Done and clearly defined'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No executive sponsor identified'}, {'Score': 10, 'Condition': 'Executive sponsor formally identified and actively engaged'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'Does not exist'}, {'Score': 10, 'Condition': 'Exists'}]</t>
   </si>
   <si>
@@ -1265,6 +1399,9 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': 'item 1 completed'}, {'Score': 10, 'Condition': 'item 2 completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 5, 'Condition': '3 items completed'}, {'Score': 7, 'Condition': '4 items completed'}, {'Score': 9, 'Condition': '5 items completed'}, {'Score': 10, 'Condition': '6 items completed'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 10, 'Condition': 'communicates wins in KPI thresholds and unit costs'}]</t>
   </si>
   <si>
@@ -1274,9 +1411,6 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item  completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 5, 'Condition': '3 items completed'}, {'Score': 7, 'Condition': '4 items completed'}, {'Score': 9, 'Condition': '5 items completed'}, {'Score': 10, 'Condition': '6 items completed'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'No alerting to any owners'}, {'Score': 1, 'Condition': 'Alerting in at least one owner'}, {'Score': 3, 'Condition': 'Alerting to some owners [&gt;20%]'}, {'Score': 6, 'Condition': 'Alerting to most owners [&gt;60%]'}, {'Score': 10, 'Condition': 'Alerting to all owners [100%]'}]</t>
   </si>
   <si>
@@ -1308,6 +1442,9 @@
   </si>
   <si>
     <t>0: No rules established</t>
+  </si>
+  <si>
+    <t>0: No executive sponsor identified</t>
   </si>
   <si>
     <t>0: Does not exist</t>
@@ -1608,9 +1745,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Overview!$A$12:$A$32</c:f>
+              <c:f>Overview!$A$12:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>Allocation</c:v>
                 </c:pt>
@@ -1630,48 +1767,51 @@
                   <c:v>Data Ingestion</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>Executive Strategy Alignment</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>FinOps Assessment</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>FinOps Education &amp; Enablement</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>FinOps Practice Operations</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>Forecasting</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>Governance, Policy &amp; Risk</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>Intersecting Disciplines</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>Invoicing &amp; Chargeback</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>KPIs &amp; Benchmarking</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>Licensing &amp; SaaS</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>Planning &amp; Estimating</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>Rate Optimization</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>Reporting &amp; Analytics</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>Sustainability</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>Unit Economics</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>Usage Optimization</c:v>
                 </c:pt>
               </c:strCache>
@@ -1679,10 +1819,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Overview!$U$12:$U$32</c:f>
+              <c:f>Overview!$U$12:$U$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1744,6 +1884,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1915,7 +2058,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A11:B32" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A11:B33" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" name="Capability"/>
     <tableColumn id="2" name="Action Count"/>
@@ -2209,7 +2352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
@@ -2234,14 +2377,14 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2">
-        <f>SUM(Scoring!F2:F136)</f>
+        <f>SUM(Scoring!F2:F140)</f>
         <v>0</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2">
-        <f>SUM(Scoring!I2:I136)/A2</f>
+        <f>SUM(Scoring!I2:I140)/A2</f>
         <v>0</v>
       </c>
       <c r="D2">
@@ -2262,10 +2405,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="U5">
-        <f>SUMIF(Scoring!J2:J136,A5,Scoring!I2:I136)/SUMIF(Scoring!J2:J136,A5,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!J2:J140,A5,Scoring!I2:I140)/SUMIF(Scoring!J2:J140,A5,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2277,7 +2420,7 @@
         <v>36</v>
       </c>
       <c r="U6">
-        <f>SUMIF(Scoring!J2:J136,A6,Scoring!I2:I136)/SUMIF(Scoring!J2:J136,A6,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!J2:J140,A6,Scoring!I2:I140)/SUMIF(Scoring!J2:J140,A6,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2289,7 +2432,7 @@
         <v>31</v>
       </c>
       <c r="U7">
-        <f>SUMIF(Scoring!J2:J136,A7,Scoring!I2:I136)/SUMIF(Scoring!J2:J136,A7,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!J2:J140,A7,Scoring!I2:I140)/SUMIF(Scoring!J2:J140,A7,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2301,7 +2444,7 @@
         <v>30</v>
       </c>
       <c r="U8">
-        <f>SUMIF(Scoring!J2:J136,A8,Scoring!I2:I136)/SUMIF(Scoring!J2:J136,A8,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!J2:J140,A8,Scoring!I2:I140)/SUMIF(Scoring!J2:J140,A8,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2327,7 +2470,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <f>SUMIF(Scoring!K2:K136,A12,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A12,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A12,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A12,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2339,7 +2482,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <f>SUMIF(Scoring!K2:K136,A13,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A13,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A13,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A13,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2351,7 +2494,7 @@
         <v>12</v>
       </c>
       <c r="U14">
-        <f>SUMIF(Scoring!K2:K136,A14,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A14,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A14,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A14,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2363,7 +2506,7 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <f>SUMIF(Scoring!K2:K136,A15,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A15,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A15,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A15,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2375,7 +2518,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <f>SUMIF(Scoring!K2:K136,A16,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A16,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A16,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A16,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2387,7 +2530,7 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <f>SUMIF(Scoring!K2:K136,A17,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A17,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A17,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A17,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2396,10 +2539,10 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <f>SUMIF(Scoring!K2:K136,A18,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A18,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A18,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A18,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2411,7 +2554,7 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <f>SUMIF(Scoring!K2:K136,A19,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A19,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A19,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A19,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2420,10 +2563,10 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <f>SUMIF(Scoring!K2:K136,A20,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A20,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A20,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A20,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2435,7 +2578,7 @@
         <v>6</v>
       </c>
       <c r="U21">
-        <f>SUMIF(Scoring!K2:K136,A21,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A21,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A21,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A21,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2444,10 +2587,10 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <f>SUMIF(Scoring!K2:K136,A22,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A22,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A22,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A22,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2456,10 +2599,10 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <f>SUMIF(Scoring!K2:K136,A23,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A23,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A23,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A23,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2471,7 +2614,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <f>SUMIF(Scoring!K2:K136,A24,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A24,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A24,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A24,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2483,7 +2626,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <f>SUMIF(Scoring!K2:K136,A25,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A25,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A25,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A25,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2495,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="U26">
-        <f>SUMIF(Scoring!K2:K136,A26,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A26,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A26,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A26,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2504,10 +2647,10 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U27">
-        <f>SUMIF(Scoring!K2:K136,A27,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A27,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A27,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A27,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2516,10 +2659,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <f>SUMIF(Scoring!K2:K136,A28,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A28,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A28,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A28,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2528,10 +2671,10 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <f>SUMIF(Scoring!K2:K136,A29,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A29,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A29,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A29,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2540,10 +2683,10 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <f>SUMIF(Scoring!K2:K136,A30,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A30,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A30,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A30,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2555,7 +2698,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <f>SUMIF(Scoring!K2:K136,A31,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A31,Scoring!F2:F136)</f>
+        <f>SUMIF(Scoring!K2:K140,A31,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A31,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2567,13 +2710,25 @@
         <v>6</v>
       </c>
       <c r="U32">
-        <f>SUMIF(Scoring!K2:K136,A32,Scoring!I2:I136)/SUMIF(Scoring!K2:K136,A32,Scoring!F2:F136)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
+        <f>SUMIF(Scoring!K2:K140,A32,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A32,Scoring!F2:F140)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
       <c r="B33">
-        <f>SUM(Overview!$B$12:$B$32)</f>
+        <v>6</v>
+      </c>
+      <c r="U33">
+        <f>SUMIF(Scoring!K2:K140,A33,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A33,Scoring!F2:F140)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
+      <c r="B34">
+        <f>SUM(Overview!$B$12:$B$33)</f>
         <v>0</v>
       </c>
     </row>
@@ -2590,7 +2745,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K136"/>
+  <dimension ref="A1:K140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
@@ -2608,37 +2763,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2646,22 +2801,22 @@
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E2" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2671,26 +2826,26 @@
         <v>6</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E3" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2700,26 +2855,26 @@
         <v>6</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2729,26 +2884,26 @@
         <v>6</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -2758,26 +2913,26 @@
         <v>6</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E6" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -2787,31 +2942,31 @@
         <v>6</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E7" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>383</v>
+        <v>410</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -2821,29 +2976,29 @@
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E8" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -2853,29 +3008,29 @@
         <v>6</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E9" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -2885,29 +3040,29 @@
         <v>6</v>
       </c>
       <c r="K9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E10" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -2917,29 +3072,29 @@
         <v>6</v>
       </c>
       <c r="K10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E11" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -2949,28 +3104,28 @@
         <v>6</v>
       </c>
       <c r="K11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E12" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -2980,26 +3135,26 @@
         <v>6</v>
       </c>
       <c r="K12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E13" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -3009,26 +3164,26 @@
         <v>6</v>
       </c>
       <c r="K13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E14" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -3038,29 +3193,29 @@
         <v>6</v>
       </c>
       <c r="K14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E15" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3070,26 +3225,26 @@
         <v>6</v>
       </c>
       <c r="K15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E16" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3099,28 +3254,28 @@
         <v>6</v>
       </c>
       <c r="K16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E17" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3130,26 +3285,26 @@
         <v>6</v>
       </c>
       <c r="K17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E18" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3159,26 +3314,26 @@
         <v>6</v>
       </c>
       <c r="K18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E19" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3188,26 +3343,26 @@
         <v>6</v>
       </c>
       <c r="K19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3217,26 +3372,26 @@
         <v>6</v>
       </c>
       <c r="K20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E21" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3246,26 +3401,26 @@
         <v>6</v>
       </c>
       <c r="K21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E22" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3275,7 +3430,7 @@
         <v>6</v>
       </c>
       <c r="K22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3284,19 +3439,19 @@
         <v>14</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E23" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3313,19 +3468,19 @@
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E24" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3342,19 +3497,19 @@
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E25" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3371,22 +3526,22 @@
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E26" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3403,19 +3558,19 @@
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E27" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3431,22 +3586,25 @@
     <row r="28" spans="1:11">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E28" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3456,26 +3614,29 @@
         <v>6</v>
       </c>
       <c r="K28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E29" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3485,26 +3646,29 @@
         <v>6</v>
       </c>
       <c r="K29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E30" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3514,26 +3678,29 @@
         <v>6</v>
       </c>
       <c r="K30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E31" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>341</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3543,26 +3710,29 @@
         <v>6</v>
       </c>
       <c r="K31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E32" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -3572,26 +3742,29 @@
         <v>6</v>
       </c>
       <c r="K32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E33" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -3601,28 +3774,28 @@
         <v>6</v>
       </c>
       <c r="K33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E34" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -3632,26 +3805,26 @@
         <v>6</v>
       </c>
       <c r="K34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E35" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -3661,26 +3834,26 @@
         <v>6</v>
       </c>
       <c r="K35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E36" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -3690,26 +3863,26 @@
         <v>6</v>
       </c>
       <c r="K36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E37" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F37">
         <v>0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -3719,26 +3892,26 @@
         <v>6</v>
       </c>
       <c r="K37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E38" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -3748,26 +3921,26 @@
         <v>6</v>
       </c>
       <c r="K38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E39" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -3777,149 +3950,157 @@
         <v>6</v>
       </c>
       <c r="K39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="A40" s="2"/>
       <c r="B40" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E40" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>387</v>
+        <v>414</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E41" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E42" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E43" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
+      <c r="G43" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="H43" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
         <v>0</v>
       </c>
       <c r="J43" t="s">
+        <v>6</v>
+      </c>
+      <c r="K43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K43" t="s">
+      <c r="B44" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E44" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -3936,19 +4117,22 @@
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E45" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -3965,19 +4149,19 @@
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E46" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>381</v>
+        <v>416</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -3994,19 +4178,19 @@
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E47" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4023,22 +4207,19 @@
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E48" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F48">
-        <v>1</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4055,19 +4236,19 @@
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E49" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F49">
         <v>0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4084,19 +4265,19 @@
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E50" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F50">
         <v>0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4113,19 +4294,19 @@
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E51" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4140,23 +4321,24 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="2"/>
-      <c r="B52" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B52" s="2"/>
       <c r="C52" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E52" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>348</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4166,26 +4348,26 @@
         <v>7</v>
       </c>
       <c r="K52" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E53" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4195,26 +4377,26 @@
         <v>7</v>
       </c>
       <c r="K53" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E54" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4224,26 +4406,26 @@
         <v>7</v>
       </c>
       <c r="K54" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E55" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4253,26 +4435,28 @@
         <v>7</v>
       </c>
       <c r="K55" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
+      <c r="B56" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="C56" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E56" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="F56">
         <v>0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4282,26 +4466,26 @@
         <v>7</v>
       </c>
       <c r="K56" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E57" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4311,28 +4495,26 @@
         <v>7</v>
       </c>
       <c r="K57" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="2"/>
-      <c r="B58" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="B58" s="2"/>
       <c r="C58" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E58" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4342,26 +4524,26 @@
         <v>7</v>
       </c>
       <c r="K58" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E59" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4371,26 +4553,26 @@
         <v>7</v>
       </c>
       <c r="K59" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E60" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4400,26 +4582,26 @@
         <v>7</v>
       </c>
       <c r="K60" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E61" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4429,26 +4611,28 @@
         <v>7</v>
       </c>
       <c r="K61" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
+      <c r="B62" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C62" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>381</v>
+        <v>417</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4458,26 +4642,26 @@
         <v>7</v>
       </c>
       <c r="K62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E63" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4487,28 +4671,26 @@
         <v>7</v>
       </c>
       <c r="K63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="2"/>
-      <c r="B64" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="B64" s="2"/>
       <c r="C64" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E64" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -4518,26 +4700,26 @@
         <v>7</v>
       </c>
       <c r="K64" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E65" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -4547,26 +4729,26 @@
         <v>7</v>
       </c>
       <c r="K65" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E66" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -4576,26 +4758,26 @@
         <v>7</v>
       </c>
       <c r="K66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E67" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -4605,26 +4787,28 @@
         <v>7</v>
       </c>
       <c r="K67" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
+      <c r="B68" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C68" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E68" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -4634,29 +4818,26 @@
         <v>7</v>
       </c>
       <c r="K68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E69" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
-      <c r="G69" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="H69" s="1" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -4666,28 +4847,26 @@
         <v>7</v>
       </c>
       <c r="K69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="2"/>
-      <c r="B70" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="B70" s="2"/>
       <c r="C70" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E70" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -4697,26 +4876,26 @@
         <v>7</v>
       </c>
       <c r="K70" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E71" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -4726,26 +4905,26 @@
         <v>7</v>
       </c>
       <c r="K71" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E72" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -4755,26 +4934,29 @@
         <v>7</v>
       </c>
       <c r="K72" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E73" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -4784,26 +4966,28 @@
         <v>7</v>
       </c>
       <c r="K73" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
+      <c r="B74" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C74" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E74" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F74">
         <v>0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -4813,26 +4997,26 @@
         <v>7</v>
       </c>
       <c r="K74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E75" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>381</v>
+        <v>418</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -4842,146 +5026,146 @@
         <v>7</v>
       </c>
       <c r="K75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="76" spans="1:11">
-      <c r="A76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
       <c r="C76" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E76" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>381</v>
+        <v>417</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
         <v>0</v>
       </c>
       <c r="J76" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K76" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E77" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F77">
         <v>0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
         <v>0</v>
       </c>
       <c r="J77" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K77" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E78" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F78">
         <v>0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
         <v>0</v>
       </c>
       <c r="J78" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K78" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E79" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F79">
         <v>0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
         <v>0</v>
       </c>
       <c r="J79" t="s">
+        <v>7</v>
+      </c>
+      <c r="K79" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K79" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
+      <c r="B80" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="C80" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E80" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -4991,26 +5175,26 @@
         <v>8</v>
       </c>
       <c r="K80" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E81" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F81">
         <v>0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5020,28 +5204,26 @@
         <v>8</v>
       </c>
       <c r="K81" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="2"/>
-      <c r="B82" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B82" s="2"/>
       <c r="C82" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E82" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5051,26 +5233,26 @@
         <v>8</v>
       </c>
       <c r="K82" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E83" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5080,26 +5262,26 @@
         <v>8</v>
       </c>
       <c r="K83" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E84" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>381</v>
+        <v>419</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5109,26 +5291,26 @@
         <v>8</v>
       </c>
       <c r="K84" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E85" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F85">
         <v>0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5138,26 +5320,28 @@
         <v>8</v>
       </c>
       <c r="K85" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
+      <c r="B86" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C86" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E86" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5174,19 +5358,19 @@
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E87" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5201,23 +5385,21 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="2"/>
-      <c r="B88" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="B88" s="2"/>
       <c r="C88" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E88" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F88">
         <v>0</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5227,29 +5409,26 @@
         <v>8</v>
       </c>
       <c r="K88" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E89" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F89">
-        <v>1</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -5259,26 +5438,26 @@
         <v>8</v>
       </c>
       <c r="K89" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E90" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -5288,29 +5467,26 @@
         <v>8</v>
       </c>
       <c r="K90" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E91" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F91">
-        <v>1</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -5320,26 +5496,28 @@
         <v>8</v>
       </c>
       <c r="K91" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
+      <c r="B92" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="C92" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E92" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -5349,29 +5527,29 @@
         <v>8</v>
       </c>
       <c r="K92" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E93" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -5381,31 +5559,26 @@
         <v>8</v>
       </c>
       <c r="K93" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="2"/>
-      <c r="B94" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="B94" s="2"/>
       <c r="C94" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E94" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
-      <c r="G94" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="H94" s="1" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -5415,29 +5588,29 @@
         <v>8</v>
       </c>
       <c r="K94" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E95" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
@@ -5447,29 +5620,26 @@
         <v>8</v>
       </c>
       <c r="K95" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E96" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
-      <c r="G96" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="H96" s="1" t="s">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
@@ -5479,29 +5649,29 @@
         <v>8</v>
       </c>
       <c r="K96" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E97" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
@@ -5511,29 +5681,31 @@
         <v>8</v>
       </c>
       <c r="K97" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
+      <c r="B98" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C98" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E98" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
@@ -5543,26 +5715,29 @@
         <v>8</v>
       </c>
       <c r="K98" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E99" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
+      <c r="G99" s="1" t="s">
+        <v>354</v>
+      </c>
       <c r="H99" s="1" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -5572,29 +5747,29 @@
         <v>8</v>
       </c>
       <c r="K99" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E100" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -5604,31 +5779,29 @@
         <v>8</v>
       </c>
       <c r="K100" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="2"/>
-      <c r="B101" s="2" t="s">
-        <v>30</v>
-      </c>
+      <c r="B101" s="2"/>
       <c r="C101" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E101" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -5638,26 +5811,29 @@
         <v>8</v>
       </c>
       <c r="K101" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E102" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -5667,26 +5843,26 @@
         <v>8</v>
       </c>
       <c r="K102" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="E103" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>381</v>
+        <v>417</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -5696,26 +5872,29 @@
         <v>8</v>
       </c>
       <c r="K103" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E104" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
@@ -5725,26 +5904,31 @@
         <v>8</v>
       </c>
       <c r="K104" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="2"/>
-      <c r="B105" s="2"/>
+      <c r="B105" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C105" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E105" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
@@ -5754,26 +5938,29 @@
         <v>8</v>
       </c>
       <c r="K105" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E106" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
+      <c r="G106" s="1" t="s">
+        <v>360</v>
+      </c>
       <c r="H106" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
@@ -5783,161 +5970,158 @@
         <v>8</v>
       </c>
       <c r="K106" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="107" spans="1:11">
-      <c r="A107" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
       <c r="C107" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E107" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
         <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K107" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E108" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
         <v>0</v>
       </c>
       <c r="J108" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K108" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E109" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
         <v>0</v>
       </c>
       <c r="J109" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K109" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E110" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F110">
         <v>1</v>
       </c>
-      <c r="G110" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="H110" s="1" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="I110">
         <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
         <v>0</v>
       </c>
       <c r="J110" t="s">
+        <v>8</v>
+      </c>
+      <c r="K110" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K110" t="s">
+      <c r="B111" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="111" spans="1:11">
-      <c r="A111" s="2"/>
-      <c r="B111" s="2"/>
       <c r="C111" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E111" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="I111">
         <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
@@ -5954,22 +6138,22 @@
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E112" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="I112">
         <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
@@ -5986,19 +6170,22 @@
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E113" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>366</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I113">
         <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
@@ -6013,26 +6200,24 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="2"/>
-      <c r="B114" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B114" s="2"/>
       <c r="C114" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E114" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="I114">
         <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
@@ -6042,29 +6227,29 @@
         <v>9</v>
       </c>
       <c r="K114" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E115" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F115">
         <v>1</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="I115">
         <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
@@ -6074,26 +6259,29 @@
         <v>9</v>
       </c>
       <c r="K115" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E116" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F116">
         <v>1</v>
       </c>
+      <c r="G116" s="1" t="s">
+        <v>369</v>
+      </c>
       <c r="H116" s="1" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="I116">
         <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
@@ -6103,26 +6291,26 @@
         <v>9</v>
       </c>
       <c r="K116" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E117" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F117">
         <v>0</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I117">
         <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
@@ -6132,26 +6320,31 @@
         <v>9</v>
       </c>
       <c r="K117" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="2"/>
-      <c r="B118" s="2"/>
+      <c r="B118" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C118" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E118" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I118">
         <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
@@ -6168,22 +6361,22 @@
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="E119" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F119">
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I119">
         <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
@@ -6200,19 +6393,19 @@
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E120" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>381</v>
+        <v>421</v>
       </c>
       <c r="I120">
         <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
@@ -6227,23 +6420,21 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="2"/>
-      <c r="B121" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="B121" s="2"/>
       <c r="C121" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="E121" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F121">
         <v>0</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I121">
         <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
@@ -6253,26 +6444,26 @@
         <v>9</v>
       </c>
       <c r="K121" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E122" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F122">
         <v>0</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I122">
         <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
@@ -6282,26 +6473,29 @@
         <v>9</v>
       </c>
       <c r="K122" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E123" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>372</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I123">
         <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
@@ -6311,26 +6505,26 @@
         <v>9</v>
       </c>
       <c r="K123" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="E124" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="I124">
         <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
@@ -6340,26 +6534,28 @@
         <v>9</v>
       </c>
       <c r="K124" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="2"/>
-      <c r="B125" s="2"/>
+      <c r="B125" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C125" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E125" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F125">
         <v>0</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I125">
         <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
@@ -6376,22 +6572,19 @@
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E126" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F126">
-        <v>1</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>348</v>
+        <v>0</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="I126">
         <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
@@ -6408,22 +6601,19 @@
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="E127" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F127">
-        <v>1</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>349</v>
+        <v>0</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="I127">
         <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
@@ -6440,19 +6630,19 @@
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E128" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>381</v>
+        <v>422</v>
       </c>
       <c r="I128">
         <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
@@ -6469,19 +6659,19 @@
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E129" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="I129">
         <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
@@ -6496,23 +6686,24 @@
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="2"/>
-      <c r="B130" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="B130" s="2"/>
       <c r="C130" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E130" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I130">
         <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
@@ -6522,29 +6713,29 @@
         <v>9</v>
       </c>
       <c r="K130" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131" spans="1:11">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E131" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="F131">
         <v>1</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="I131">
         <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
@@ -6554,29 +6745,26 @@
         <v>9</v>
       </c>
       <c r="K131" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E132" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F132">
-        <v>1</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="I132">
         <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
@@ -6586,26 +6774,26 @@
         <v>9</v>
       </c>
       <c r="K132" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E133" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>381</v>
+        <v>422</v>
       </c>
       <c r="I133">
         <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
@@ -6615,26 +6803,28 @@
         <v>9</v>
       </c>
       <c r="K133" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="2"/>
-      <c r="B134" s="2"/>
+      <c r="B134" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="C134" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E134" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="I134">
         <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
@@ -6644,26 +6834,29 @@
         <v>9</v>
       </c>
       <c r="K134" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="E135" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I135">
         <f>F135*VALUE(LEFT(H135, FIND(":", H135)-1))</f>
@@ -6673,26 +6866,29 @@
         <v>9</v>
       </c>
       <c r="K135" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E136" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F136">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>376</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I136">
         <f>F136*VALUE(LEFT(H136, FIND(":", H136)-1))</f>
@@ -6702,15 +6898,131 @@
         <v>9</v>
       </c>
       <c r="K136" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11">
+      <c r="A137" s="2"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E137" t="s">
+        <v>322</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="I137">
+        <f>F137*VALUE(LEFT(H137, FIND(":", H137)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J137" t="s">
+        <v>9</v>
+      </c>
+      <c r="K137" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11">
+      <c r="A138" s="2"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E138" t="s">
+        <v>323</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="I138">
+        <f>F138*VALUE(LEFT(H138, FIND(":", H138)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J138" t="s">
+        <v>9</v>
+      </c>
+      <c r="K138" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11">
+      <c r="A139" s="2"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E139" t="s">
+        <v>322</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="I139">
+        <f>F139*VALUE(LEFT(H139, FIND(":", H139)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J139" t="s">
+        <v>9</v>
+      </c>
+      <c r="K139" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11">
+      <c r="A140" s="2"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E140" t="s">
+        <v>322</v>
+      </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="I140">
+        <f>F140*VALUE(LEFT(H140, FIND(":", H140)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J140" t="s">
+        <v>9</v>
+      </c>
+      <c r="K140" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A2:A39"/>
-    <mergeCell ref="A40:A75"/>
-    <mergeCell ref="A76:A106"/>
-    <mergeCell ref="A107:A136"/>
+  <mergeCells count="26">
+    <mergeCell ref="A2:A43"/>
+    <mergeCell ref="A44:A79"/>
+    <mergeCell ref="A80:A110"/>
+    <mergeCell ref="A111:A140"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="B7:B11"/>
     <mergeCell ref="B12:B16"/>
@@ -6718,22 +7030,23 @@
     <mergeCell ref="B23:B27"/>
     <mergeCell ref="B28:B33"/>
     <mergeCell ref="B34:B39"/>
-    <mergeCell ref="B40:B51"/>
-    <mergeCell ref="B52:B57"/>
-    <mergeCell ref="B58:B63"/>
-    <mergeCell ref="B64:B69"/>
-    <mergeCell ref="B70:B75"/>
-    <mergeCell ref="B76:B81"/>
-    <mergeCell ref="B82:B87"/>
-    <mergeCell ref="B88:B93"/>
-    <mergeCell ref="B94:B100"/>
-    <mergeCell ref="B101:B106"/>
-    <mergeCell ref="B107:B113"/>
-    <mergeCell ref="B114:B120"/>
-    <mergeCell ref="B121:B129"/>
-    <mergeCell ref="B130:B136"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="B44:B55"/>
+    <mergeCell ref="B56:B61"/>
+    <mergeCell ref="B62:B67"/>
+    <mergeCell ref="B68:B73"/>
+    <mergeCell ref="B74:B79"/>
+    <mergeCell ref="B80:B85"/>
+    <mergeCell ref="B86:B91"/>
+    <mergeCell ref="B92:B97"/>
+    <mergeCell ref="B98:B104"/>
+    <mergeCell ref="B105:B110"/>
+    <mergeCell ref="B111:B117"/>
+    <mergeCell ref="B118:B124"/>
+    <mergeCell ref="B125:B133"/>
+    <mergeCell ref="B134:B140"/>
   </mergeCells>
-  <dataValidations count="135">
+  <dataValidations count="139">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"0: None"</formula1>
     </dataValidation>
@@ -6759,7 +7072,7 @@
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10">
-      <formula1>"0: No items completed,3: item 1 completed,5: items 1. and 2 completed,8: items 1. 2. and 3 completed,10: items 1. 2. 3. and 4 completed"</formula1>
+      <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
@@ -6813,22 +7126,22 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: item 1 completed,4: items 1-2 completed,6: items 1-3 completed,8: items 1-4 completed,10: items 1-5 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
       <formula1>"0: None"</formula1>
@@ -6849,31 +7162,31 @@
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
+      <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
       <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
-      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
       <formula1>"0: None"</formula1>
@@ -6885,7 +7198,7 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
       <formula1>"0: None"</formula1>
@@ -6903,7 +7216,7 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
       <formula1>"0: None"</formula1>
@@ -6912,16 +7225,16 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
@@ -6933,31 +7246,31 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H70">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H71">
-      <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H77">
       <formula1>"0: None"</formula1>
@@ -6969,127 +7282,127 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
-      <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H81">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H83">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H84">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H85">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H86">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
-      <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
-      <formula1>"0: No alerting,10: Alerting exists"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
+      <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
+      <formula1>"0: No alerting,10: Alerting exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H101">
       <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H102">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H104">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H105">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H102">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H104">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H105">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H106">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H107">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H109">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H110">
       <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H107">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H111">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H112">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80% ,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H109">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H113">
       <formula1>"0: No items completed,5: 1 item  completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H110">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H114">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H111">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H115">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H112">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H116">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H113">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H114">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H115">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H116">
-      <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H117">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H118">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H119">
-      <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H120">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H121">
       <formula1>"0: None"</formula1>
@@ -7098,45 +7411,57 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H123">
+      <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H124">
       <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H124">
-      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H125">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H126">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H127">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H128">
+      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H129">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H130">
       <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H127">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H131">
       <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H128">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H132">
       <formula1>"0: None"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H133">
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H130">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H134">
       <formula1>"0: None"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H131">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H135">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H132">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H136">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H133">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H137">
       <formula1>"0: None"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H134">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H138">
       <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H135">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H139">
       <formula1>"0: None"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H136">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H140">
       <formula1>"0: None"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7276,6 +7601,10 @@
     <hyperlink ref="D134" r:id="rId133"/>
     <hyperlink ref="D135" r:id="rId134"/>
     <hyperlink ref="D136" r:id="rId135"/>
+    <hyperlink ref="D137" r:id="rId136"/>
+    <hyperlink ref="D138" r:id="rId137"/>
+    <hyperlink ref="D139" r:id="rId138"/>
+    <hyperlink ref="D140" r:id="rId139"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="429">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -313,22 +313,22 @@
     <t>Review Outcomes &amp; Adjust Patterns</t>
   </si>
   <si>
-    <t>Aggregate emissions data by region/service/account with lineage.</t>
-  </si>
-  <si>
-    <t>Define sustainability metrics/targets.</t>
-  </si>
-  <si>
-    <t>Include carbon impact in migration/optimization decisions and PRDs.</t>
-  </si>
-  <si>
-    <t>Enable engineering with carbon-aware data and scheduling guidance.</t>
-  </si>
-  <si>
-    <t>Continuously improve data quality and report progress on dashboards.</t>
-  </si>
-  <si>
-    <t>Tie sustainability wins to cost efficiency where possible.</t>
+    <t>Aggregate Emissions Data</t>
+  </si>
+  <si>
+    <t>Define Sustainability Metrics</t>
+  </si>
+  <si>
+    <t>Carbon Impact Workload Decisions</t>
+  </si>
+  <si>
+    <t>Carbon Aware Data Guidance</t>
+  </si>
+  <si>
+    <t>Sustainability Data Continuous Improvement</t>
+  </si>
+  <si>
+    <t>Tie Sustainability to Cost Efficiency</t>
   </si>
   <si>
     <t>Inventory Licenses &amp; Map Resources</t>
@@ -991,22 +991,22 @@
     <t>1.7.0</t>
   </si>
   <si>
+    <t>1.0.0</t>
+  </si>
+  <si>
     <t>0.8.0</t>
   </si>
   <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>0.0.1</t>
+  </si>
+  <si>
+    <t>0.6.0</t>
+  </si>
+  <si>
     <t>0.7.1</t>
-  </si>
-  <si>
-    <t>0.9.0</t>
-  </si>
-  <si>
-    <t>0.8.1</t>
-  </si>
-  <si>
-    <t>0.0.1</t>
-  </si>
-  <si>
-    <t>0.5.0</t>
   </si>
   <si>
     <t>1.5.0</t>
@@ -1047,6 +1047,40 @@
     <t>* Define process for reviewing asking for credits from CSPs
 * Define frequency of review, etc.
 10*Ceil(x/2)</t>
+  </si>
+  <si>
+    <t>* Weighted sum
+	TCO (score ×3),
+	Vendor scoring (score ×3),
+	Decision document (score ×3),
+	Rules established (score ×1).
+  Max Raw Score (29)
+* TCO_Analysis - Total Cost of Ownership analysis performed
+  (0=None, 1=High-level, 2=Detailed, 3=Validated with Finance)
+* Vendor_Scored - Vendor options scored against criteria
+  (0=None, 1=Informal, 2=Structured scorecard, 3=Multi-stakeholder RFP)
+* Decision_Doc - Build vs Buy decision formally documented and approved
+  (0=No, 1=Informal note, 2=Formal doc, 3=Exec-approved+reviewed)
+* Rules_Est - Guiding rules / policy established for future decsions
+  (0=No rules, 1=Draft, 2=Published+Enforced)
+* Output Range (0 - Max Raw)</t>
+  </si>
+  <si>
+    <t>* Weighted sum
+  Env coverage (score x4),
+  Data Integration (score x4),
+  Tag Config (score x2),
+  Config Doc (score x2).
+  Max raw (52)
+* Env_Coverage - % of cloud environments covered by deployed tools
+  (0=0%, 1&lt;50%, 2=50-79%, 3=80-94%, 4=95-99%, 5=100%)
+* Data_Integration - Data sources integrated (billing, usage, tags, business context)
+  (0=None, 1=Billing Only, 2=+Usage, 3=+Tags, 4=+Business context, 5=All+Automated)
+* Tag_Config - Tag/allocation rules configured and enforced tool
+  (0=No, 1=Partial manual, 2=Full manual, 3=Automated enforcement)
+* Config_Doc - Tool configuration documented and version-controlled
+  (0=No rules, 1=Informal, 2=Documented, 3=Version-controlled+Reviewed)
+* Output Range (0-52)</t>
   </si>
   <si>
     <t>* Define communication pathways between FinOps and the business
@@ -1224,15 +1258,15 @@
 * Review data with stakeholders when metrics exceed acceptable thresholds in either direction
 * Incorporate metric reviews into the decision making processes of stakeholder departments
 * The FinOps team should periodically publish an analysis of major changes in the metrics dashboards
-as well as facilitate reviews of metrics, adoption data, modifications, and KPI refreshes
+  as well as facilitate reviews of metrics, adoption data, modifications, and KPI refreshes
 10*Ceil(x/4)</t>
   </si>
   <si>
     <t>* Scenario plan for which metric values will drive the next decisions, behaviors, or outcomes needed
 * Investigate root causes for changes in metric values to determine next steps
 * Add to the backlog which actions are required to get unit metrics to a desired level
-* Unit economics influence the decisions in build vs buy, architecture design,
- workload placement, migration, sourcing, pricing, etc.
+* Unit economics influence the decisions in build vs buy, architecture design, workload placement,
+  migration, sourcing, pricing, etc.
 10*Ceil(x/4)</t>
   </si>
   <si>
@@ -1351,13 +1385,19 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1-2 completed'}, {'Score': 8, 'Condition': 'items 1-3 completed'}, {'Score': 10, 'Condition': 'items 1-4 completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Completed'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Defined'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'No rules established'}, {'Score': 10, 'Condition': 'Published policy'}]</t>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-8)'}, {'Score': 4, 'Condition': 'Developing, Score Range (9-17)'}, {'Score': 7, 'Condition': 'Established, Score Range (18-24)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (25-29)'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-15)'}, {'Score': 4, 'Condition': 'Developing, Score Range (16-31)'}, {'Score': 7, 'Condition': 'Established, Score Range (32-44)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (45-52)'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 6, 'Condition': '3 items completed'}, {'Score': 8, 'Condition': '4 items completed'}, {'Score': 10, 'Condition': '5 items completed'}]</t>
@@ -1441,7 +1481,10 @@
     <t>0: Not done</t>
   </si>
   <si>
-    <t>0: No rules established</t>
+    <t>0: Low Maturity. Score Range (0-8)</t>
+  </si>
+  <si>
+    <t>0: Low Maturity. Score Range (0-15)</t>
   </si>
   <si>
     <t>0: No executive sponsor identified</t>
@@ -2750,7 +2793,7 @@
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="63" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
@@ -2816,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2845,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2874,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2903,7 +2946,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -2932,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -2966,7 +3009,7 @@
         <v>331</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -2998,7 +3041,7 @@
         <v>332</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -3030,7 +3073,7 @@
         <v>333</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -3053,7 +3096,7 @@
         <v>191</v>
       </c>
       <c r="E10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -3062,7 +3105,7 @@
         <v>334</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -3094,7 +3137,7 @@
         <v>335</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -3119,13 +3162,13 @@
         <v>193</v>
       </c>
       <c r="E12" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -3148,13 +3191,13 @@
         <v>194</v>
       </c>
       <c r="E13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -3177,13 +3220,13 @@
         <v>195</v>
       </c>
       <c r="E14" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -3215,7 +3258,7 @@
         <v>336</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3238,13 +3281,13 @@
         <v>197</v>
       </c>
       <c r="E16" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3275,7 +3318,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3298,13 +3341,13 @@
         <v>199</v>
       </c>
       <c r="E18" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3327,13 +3370,13 @@
         <v>200</v>
       </c>
       <c r="E19" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3356,13 +3399,13 @@
         <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3385,13 +3428,13 @@
         <v>202</v>
       </c>
       <c r="E21" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3414,13 +3457,13 @@
         <v>203</v>
       </c>
       <c r="E22" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3451,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3474,13 +3517,16 @@
         <v>205</v>
       </c>
       <c r="E24" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
+      <c r="G24" s="1" t="s">
+        <v>337</v>
+      </c>
       <c r="H24" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3503,13 +3549,16 @@
         <v>206</v>
       </c>
       <c r="E25" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3538,10 +3587,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3570,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3601,10 +3650,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3633,10 +3682,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3665,10 +3714,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3691,16 +3740,16 @@
         <v>212</v>
       </c>
       <c r="E31" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3729,10 +3778,10 @@
         <v>1</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -3755,16 +3804,16 @@
         <v>214</v>
       </c>
       <c r="E33" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -3789,13 +3838,13 @@
         <v>215</v>
       </c>
       <c r="E34" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -3818,13 +3867,13 @@
         <v>216</v>
       </c>
       <c r="E35" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -3853,7 +3902,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -3876,13 +3925,13 @@
         <v>218</v>
       </c>
       <c r="E37" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -3905,13 +3954,13 @@
         <v>219</v>
       </c>
       <c r="E38" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -3940,7 +3989,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -3965,13 +4014,13 @@
         <v>221</v>
       </c>
       <c r="E40" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -3994,16 +4043,16 @@
         <v>222</v>
       </c>
       <c r="E41" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -4026,16 +4075,16 @@
         <v>223</v>
       </c>
       <c r="E42" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -4058,16 +4107,16 @@
         <v>224</v>
       </c>
       <c r="E43" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -4100,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -4129,10 +4178,10 @@
         <v>1</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -4161,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -4190,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4219,7 +4268,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4248,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4271,13 +4320,13 @@
         <v>231</v>
       </c>
       <c r="E50" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4300,13 +4349,13 @@
         <v>232</v>
       </c>
       <c r="E51" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4335,10 +4384,10 @@
         <v>1</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4361,13 +4410,13 @@
         <v>234</v>
       </c>
       <c r="E53" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4390,13 +4439,13 @@
         <v>235</v>
       </c>
       <c r="E54" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4419,13 +4468,13 @@
         <v>236</v>
       </c>
       <c r="E55" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4450,13 +4499,13 @@
         <v>237</v>
       </c>
       <c r="E56" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4479,13 +4528,13 @@
         <v>238</v>
       </c>
       <c r="E57" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4508,13 +4557,13 @@
         <v>239</v>
       </c>
       <c r="E58" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4537,13 +4586,13 @@
         <v>240</v>
       </c>
       <c r="E59" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4566,13 +4615,13 @@
         <v>241</v>
       </c>
       <c r="E60" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4595,13 +4644,13 @@
         <v>242</v>
       </c>
       <c r="E61" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4632,7 +4681,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4655,13 +4704,13 @@
         <v>244</v>
       </c>
       <c r="E63" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4684,13 +4733,13 @@
         <v>245</v>
       </c>
       <c r="E64" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -4719,7 +4768,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -4742,13 +4791,13 @@
         <v>247</v>
       </c>
       <c r="E66" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -4771,13 +4820,13 @@
         <v>248</v>
       </c>
       <c r="E67" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -4808,7 +4857,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -4837,7 +4886,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -4866,7 +4915,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -4895,7 +4944,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -4924,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -4953,10 +5002,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -4981,13 +5030,13 @@
         <v>255</v>
       </c>
       <c r="E74" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -5016,7 +5065,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -5045,7 +5094,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -5068,13 +5117,13 @@
         <v>258</v>
       </c>
       <c r="E77" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -5097,13 +5146,13 @@
         <v>259</v>
       </c>
       <c r="E78" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
@@ -5126,13 +5175,13 @@
         <v>260</v>
       </c>
       <c r="E79" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
@@ -5165,7 +5214,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -5194,7 +5243,7 @@
         <v>0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5223,7 +5272,7 @@
         <v>0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5252,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5281,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5310,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5341,7 +5390,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5370,7 +5419,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5393,13 +5442,13 @@
         <v>269</v>
       </c>
       <c r="E88" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5422,13 +5471,13 @@
         <v>270</v>
       </c>
       <c r="E89" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -5451,13 +5500,13 @@
         <v>271</v>
       </c>
       <c r="E90" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -5480,13 +5529,13 @@
         <v>272</v>
       </c>
       <c r="E91" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -5517,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -5546,10 +5595,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -5578,7 +5627,7 @@
         <v>1</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -5607,10 +5656,10 @@
         <v>1</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
@@ -5639,7 +5688,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
@@ -5668,10 +5717,10 @@
         <v>1</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
@@ -5702,10 +5751,10 @@
         <v>1</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
@@ -5734,10 +5783,10 @@
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -5766,10 +5815,10 @@
         <v>1</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -5798,10 +5847,10 @@
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -5830,10 +5879,10 @@
         <v>1</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -5862,7 +5911,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -5891,10 +5940,10 @@
         <v>1</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
@@ -5925,10 +5974,10 @@
         <v>1</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
@@ -5957,10 +6006,10 @@
         <v>1</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
@@ -5989,10 +6038,10 @@
         <v>1</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
@@ -6021,10 +6070,10 @@
         <v>1</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
@@ -6053,10 +6102,10 @@
         <v>1</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
@@ -6085,7 +6134,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I110">
         <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
@@ -6118,10 +6167,10 @@
         <v>1</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I111">
         <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
@@ -6150,10 +6199,10 @@
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="I112">
         <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
@@ -6182,10 +6231,10 @@
         <v>1</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I113">
         <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
@@ -6214,10 +6263,10 @@
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="I114">
         <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
@@ -6246,10 +6295,10 @@
         <v>1</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="I115">
         <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
@@ -6278,10 +6327,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I116">
         <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
@@ -6310,7 +6359,7 @@
         <v>0</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I117">
         <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
@@ -6341,10 +6390,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I118">
         <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
@@ -6373,10 +6422,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I119">
         <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
@@ -6405,7 +6454,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="I120">
         <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
@@ -6434,7 +6483,7 @@
         <v>0</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I121">
         <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
@@ -6463,7 +6512,7 @@
         <v>0</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I122">
         <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
@@ -6492,10 +6541,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I123">
         <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
@@ -6524,7 +6573,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I124">
         <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
@@ -6549,13 +6598,13 @@
         <v>306</v>
       </c>
       <c r="E125" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F125">
         <v>0</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I125">
         <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
@@ -6584,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I126">
         <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
@@ -6613,7 +6662,7 @@
         <v>0</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I127">
         <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
@@ -6642,7 +6691,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="I128">
         <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
@@ -6671,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I129">
         <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
@@ -6700,10 +6749,10 @@
         <v>1</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I130">
         <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
@@ -6732,10 +6781,10 @@
         <v>1</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I131">
         <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
@@ -6764,7 +6813,7 @@
         <v>0</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I132">
         <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
@@ -6793,7 +6842,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="I133">
         <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
@@ -6818,13 +6867,13 @@
         <v>315</v>
       </c>
       <c r="E134" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I134">
         <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
@@ -6853,10 +6902,10 @@
         <v>1</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I135">
         <f>F135*VALUE(LEFT(H135, FIND(":", H135)-1))</f>
@@ -6885,10 +6934,10 @@
         <v>1</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I136">
         <f>F136*VALUE(LEFT(H136, FIND(":", H136)-1))</f>
@@ -6911,13 +6960,13 @@
         <v>318</v>
       </c>
       <c r="E137" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I137">
         <f>F137*VALUE(LEFT(H137, FIND(":", H137)-1))</f>
@@ -6946,7 +6995,7 @@
         <v>1</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="I138">
         <f>F138*VALUE(LEFT(H138, FIND(":", H138)-1))</f>
@@ -6969,13 +7018,13 @@
         <v>320</v>
       </c>
       <c r="E139" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I139">
         <f>F139*VALUE(LEFT(H139, FIND(":", H139)-1))</f>
@@ -6998,13 +7047,13 @@
         <v>321</v>
       </c>
       <c r="E140" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I140">
         <f>F140*VALUE(LEFT(H140, FIND(":", H140)-1))</f>
@@ -7078,46 +7127,46 @@
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H16">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H24">
-      <formula1>"0: No rules established,10: Published policy"</formula1>
+      <formula1>"0: Low Maturity. Score Range (0-8),4: Developing. Score Range (9-17),7: Established. Score Range (18-24),10: Optimizing. Score Range (25-29)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Low Maturity. Score Range (0-15),4: Developing. Score Range (16-31),7: Established. Score Range (32-44),10: Optimizing. Score Range (45-52)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
@@ -7144,19 +7193,19 @@
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
       <formula1>"0: Not done,10: Done and clearly defined"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
       <formula1>"0: Not done,10: Defined"</formula1>
@@ -7192,58 +7241,58 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H56">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
@@ -7264,7 +7313,7 @@
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
       <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
@@ -7273,13 +7322,13 @@
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H77">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H78">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
       <formula1>"0: None"</formula1>
@@ -7306,16 +7355,16 @@
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
       <formula1>"0: None"</formula1>
@@ -7444,7 +7493,7 @@
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H134">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H135">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
@@ -7453,16 +7502,16 @@
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H137">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H138">
       <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H139">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H140">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="357">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -109,6 +109,9 @@
     <t>Reporting &amp; Analytics</t>
   </si>
   <si>
+    <t>Sustainability</t>
+  </si>
+  <si>
     <t>Unit Economics</t>
   </si>
   <si>
@@ -163,12 +166,39 @@
     <t>Prioritize Actions &amp; Publish Roadmap</t>
   </si>
   <si>
+    <t>Assess Skills &amp; Training Needs</t>
+  </si>
+  <si>
+    <t>Develop Role-Based Learning Content</t>
+  </si>
+  <si>
+    <t>Offer Certifications &amp; Informal Learning</t>
+  </si>
+  <si>
     <t>Leverage Vendor Training Resources</t>
   </si>
   <si>
+    <t>Track Training Impact &amp; Refresh Content</t>
+  </si>
+  <si>
     <t>Define Org Model &amp; Budget</t>
   </si>
   <si>
+    <t>Create Implementation Roadmap</t>
+  </si>
+  <si>
+    <t>Integrate Cost Data in Workflows</t>
+  </si>
+  <si>
+    <t>Publish FinOps KPIs</t>
+  </si>
+  <si>
+    <t>Drive Stakeholder Engagement</t>
+  </si>
+  <si>
+    <t>Automate Tasks &amp; Review Maturity</t>
+  </si>
+  <si>
     <t>Evaluate Build vs Buy Options</t>
   </si>
   <si>
@@ -196,9 +226,21 @@
     <t>Drive Adoption &amp; Resolve Conflicts</t>
   </si>
   <si>
+    <t>Map Invoices to Allocation Model</t>
+  </si>
+  <si>
+    <t>Reconcile Rates &amp; Track Completion</t>
+  </si>
+  <si>
     <t>Design Chargeback with Finance</t>
   </si>
   <si>
+    <t>Automate Chargeback Data Flows</t>
+  </si>
+  <si>
+    <t>Distribute Reports &amp; Track Accuracy</t>
+  </si>
+  <si>
     <t>Resolve Variances &amp; Increase Coverage</t>
   </si>
   <si>
@@ -214,15 +256,60 @@
     <t>Estimate Trade-Offs &amp; Document Cases</t>
   </si>
   <si>
+    <t>Create Workload Selection Criteria</t>
+  </si>
+  <si>
+    <t>Define Success Criteria &amp; Scope</t>
+  </si>
+  <si>
     <t>Enforce Tagging at Onboarding</t>
   </si>
   <si>
+    <t>Align Timelines with Budgets</t>
+  </si>
+  <si>
+    <t>Start with Lower Environments</t>
+  </si>
+  <si>
+    <t>Review Outcomes &amp; Adjust Patterns</t>
+  </si>
+  <si>
+    <t>Aggregate Emissions Data</t>
+  </si>
+  <si>
+    <t>Define Sustainability Metrics</t>
+  </si>
+  <si>
+    <t>Carbon Impact Workload Decisions</t>
+  </si>
+  <si>
+    <t>Carbon Aware Data Guidance</t>
+  </si>
+  <si>
+    <t>Sustainability Data Continuous Improvement</t>
+  </si>
+  <si>
+    <t>Tie Sustainability to Cost Efficiency</t>
+  </si>
+  <si>
     <t>Inventory Licenses &amp; Map Resources</t>
   </si>
   <si>
+    <t>Document Licensing Models</t>
+  </si>
+  <si>
+    <t>Integrate Billing with Procurement</t>
+  </si>
+  <si>
     <t>Validate Utilization &amp; Remediate</t>
   </si>
   <si>
+    <t>Influence Workload Design Choices</t>
+  </si>
+  <si>
+    <t>Publish License Spend &amp; Utilization</t>
+  </si>
+  <si>
     <t>Document Commitment Strategy</t>
   </si>
   <si>
@@ -232,12 +319,24 @@
     <t>Leverage Spot &amp; Negotiated Discounts</t>
   </si>
   <si>
+    <t>Define Optimization Strategy</t>
+  </si>
+  <si>
     <t>Inventory &amp; Classify Workloads</t>
   </si>
   <si>
     <t>Collect Metrics &amp; Identify Candidates</t>
   </si>
   <si>
+    <t>Partner on Scheduling Actions</t>
+  </si>
+  <si>
+    <t>Gamify Adoption &amp; Celebrate Wins</t>
+  </si>
+  <si>
+    <t>Track KPIs &amp; Document Playbooks</t>
+  </si>
+  <si>
     <t>Track Trends &amp; Compare Over Time</t>
   </si>
   <si>
@@ -247,6 +346,18 @@
     <t>Integrate Rolling Forecasts</t>
   </si>
   <si>
+    <t>Increase Shared Cost Coverage</t>
+  </si>
+  <si>
+    <t>Publish Budget vs Actual Reports</t>
+  </si>
+  <si>
+    <t>Automate Budget Threshold Alerts</t>
+  </si>
+  <si>
+    <t>Review &amp; Adapt Budget Strategy</t>
+  </si>
+  <si>
     <t>Collect Business Drivers Regularly</t>
   </si>
   <si>
@@ -343,15 +454,27 @@
     <t>Define ingestion frequency; include mandatory metadata.</t>
   </si>
   <si>
+    <t>Gather Requirements &amp; Define KPIs</t>
+  </si>
+  <si>
     <t>Enrich Billing with Business Logic</t>
   </si>
   <si>
     <t>Build Dashboards for All Views</t>
   </si>
   <si>
+    <t>Publish Documentation &amp; Support</t>
+  </si>
+  <si>
     <t>Embed Reports in Workflows</t>
   </si>
   <si>
+    <t>Track Adoption &amp; Manage Changes</t>
+  </si>
+  <si>
+    <t>Iterate Based on Feedback</t>
+  </si>
+  <si>
     <t>105</t>
   </si>
   <si>
@@ -367,12 +490,39 @@
     <t>116</t>
   </si>
   <si>
+    <t>097</t>
+  </si>
+  <si>
+    <t>098</t>
+  </si>
+  <si>
+    <t>099</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
+    <t>101</t>
+  </si>
+  <si>
     <t>091</t>
   </si>
   <si>
+    <t>092</t>
+  </si>
+  <si>
+    <t>093</t>
+  </si>
+  <si>
+    <t>094</t>
+  </si>
+  <si>
+    <t>095</t>
+  </si>
+  <si>
+    <t>096</t>
+  </si>
+  <si>
     <t>125</t>
   </si>
   <si>
@@ -400,9 +550,21 @@
     <t>134</t>
   </si>
   <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
     <t>109</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
@@ -418,15 +580,60 @@
     <t>063</t>
   </si>
   <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>085</t>
+  </si>
+  <si>
+    <t>086</t>
+  </si>
+  <si>
+    <t>087</t>
+  </si>
+  <si>
+    <t>088</t>
+  </si>
+  <si>
+    <t>089</t>
+  </si>
+  <si>
+    <t>090</t>
+  </si>
+  <si>
     <t>073</t>
   </si>
   <si>
+    <t>074</t>
+  </si>
+  <si>
+    <t>075</t>
+  </si>
+  <si>
     <t>076</t>
   </si>
   <si>
+    <t>077</t>
+  </si>
+  <si>
+    <t>078</t>
+  </si>
+  <si>
     <t>079</t>
   </si>
   <si>
@@ -436,12 +643,24 @@
     <t>084</t>
   </si>
   <si>
+    <t>067</t>
+  </si>
+  <si>
     <t>068</t>
   </si>
   <si>
     <t>069</t>
   </si>
   <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>071</t>
+  </si>
+  <si>
+    <t>072</t>
+  </si>
+  <si>
     <t>053</t>
   </si>
   <si>
@@ -451,6 +670,18 @@
     <t>044</t>
   </si>
   <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
     <t>038</t>
   </si>
   <si>
@@ -547,13 +778,25 @@
     <t>135</t>
   </si>
   <si>
+    <t>016</t>
+  </si>
+  <si>
     <t>017</t>
   </si>
   <si>
     <t>018</t>
   </si>
   <si>
+    <t>019</t>
+  </si>
+  <si>
     <t>020</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>022</t>
   </si>
   <si>
     <t>1.7.0</t>
@@ -913,6 +1156,9 @@
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1-2 completed'}, {'Score': 8, 'Condition': 'items 1-3 completed'}, {'Score': 10, 'Condition': 'items 1-4 completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Completed'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
@@ -1315,9 +1561,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Overview!$A$12:$A$32</c:f>
+              <c:f>Overview!$A$12:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>Allocation</c:v>
                 </c:pt>
@@ -1376,9 +1622,12 @@
                   <c:v>Reporting &amp; Analytics</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>Sustainability</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>Unit Economics</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>Usage Optimization</c:v>
                 </c:pt>
               </c:strCache>
@@ -1386,10 +1635,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Overview!$U$12:$U$32</c:f>
+              <c:f>Overview!$U$12:$U$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1451,6 +1700,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1622,7 +1874,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A11:B32" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A11:B33" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" name="Capability"/>
     <tableColumn id="2" name="Action Count"/>
@@ -1916,7 +2168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
@@ -1941,14 +2193,14 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2">
-        <f>SUM(Scoring!F2:F69)</f>
+        <f>SUM(Scoring!F2:F109)</f>
         <v>0</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2">
-        <f>SUM(Scoring!I2:I69)/A2</f>
+        <f>SUM(Scoring!I2:I109)/A2</f>
         <v>0</v>
       </c>
       <c r="D2">
@@ -1969,10 +2221,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="U5">
-        <f>SUMIF(Scoring!J2:J69,A5,Scoring!I2:I69)/SUMIF(Scoring!J2:J69,A5,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!J2:J109,A5,Scoring!I2:I109)/SUMIF(Scoring!J2:J109,A5,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -1981,10 +2233,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="U6">
-        <f>SUMIF(Scoring!J2:J69,A6,Scoring!I2:I69)/SUMIF(Scoring!J2:J69,A6,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!J2:J109,A6,Scoring!I2:I109)/SUMIF(Scoring!J2:J109,A6,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -1993,10 +2245,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="U7">
-        <f>SUMIF(Scoring!J2:J69,A7,Scoring!I2:I69)/SUMIF(Scoring!J2:J69,A7,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!J2:J109,A7,Scoring!I2:I109)/SUMIF(Scoring!J2:J109,A7,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2005,10 +2257,10 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="U8">
-        <f>SUMIF(Scoring!J2:J69,A8,Scoring!I2:I69)/SUMIF(Scoring!J2:J69,A8,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!J2:J109,A8,Scoring!I2:I109)/SUMIF(Scoring!J2:J109,A8,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2034,7 +2286,7 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <f>SUMIF(Scoring!K2:K69,A12,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A12,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A12,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A12,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2046,7 +2298,7 @@
         <v>4</v>
       </c>
       <c r="U13">
-        <f>SUMIF(Scoring!K2:K69,A13,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A13,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A13,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A13,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2055,10 +2307,10 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <f>SUMIF(Scoring!K2:K69,A14,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A14,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A14,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A14,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2070,7 +2322,7 @@
         <v>3</v>
       </c>
       <c r="U15">
-        <f>SUMIF(Scoring!K2:K69,A15,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A15,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A15,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A15,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2079,10 +2331,10 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <f>SUMIF(Scoring!K2:K69,A16,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A16,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A16,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A16,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2094,7 +2346,7 @@
         <v>4</v>
       </c>
       <c r="U17">
-        <f>SUMIF(Scoring!K2:K69,A17,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A17,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A17,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A17,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2106,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="U18">
-        <f>SUMIF(Scoring!K2:K69,A18,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A18,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A18,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A18,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2118,7 +2370,7 @@
         <v>4</v>
       </c>
       <c r="U19">
-        <f>SUMIF(Scoring!K2:K69,A19,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A19,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A19,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A19,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2127,10 +2379,10 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <f>SUMIF(Scoring!K2:K69,A20,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A20,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A20,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A20,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2139,10 +2391,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <f>SUMIF(Scoring!K2:K69,A21,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A21,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A21,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A21,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2154,7 +2406,7 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <f>SUMIF(Scoring!K2:K69,A22,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A22,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A22,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A22,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2166,7 +2418,7 @@
         <v>1</v>
       </c>
       <c r="U23">
-        <f>SUMIF(Scoring!K2:K69,A23,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A23,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A23,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A23,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2178,7 +2430,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <f>SUMIF(Scoring!K2:K69,A24,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A24,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A24,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A24,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2187,10 +2439,10 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <f>SUMIF(Scoring!K2:K69,A25,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A25,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A25,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A25,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2202,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="U26">
-        <f>SUMIF(Scoring!K2:K69,A26,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A26,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A26,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A26,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2211,10 +2463,10 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U27">
-        <f>SUMIF(Scoring!K2:K69,A27,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A27,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A27,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A27,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2226,7 +2478,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <f>SUMIF(Scoring!K2:K69,A28,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A28,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A28,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A28,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2238,7 +2490,7 @@
         <v>3</v>
       </c>
       <c r="U29">
-        <f>SUMIF(Scoring!K2:K69,A29,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A29,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A29,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A29,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2247,10 +2499,10 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <f>SUMIF(Scoring!K2:K69,A30,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A30,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A30,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A30,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2262,7 +2514,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <f>SUMIF(Scoring!K2:K69,A31,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A31,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K109,A31,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A31,Scoring!F2:F109)</f>
         <v>0</v>
       </c>
     </row>
@@ -2271,16 +2523,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U32">
-        <f>SUMIF(Scoring!K2:K69,A32,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A32,Scoring!F2:F69)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
+        <f>SUMIF(Scoring!K2:K109,A32,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A32,Scoring!F2:F109)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
       <c r="B33">
-        <f>SUM(Overview!$B$12:$B$32)</f>
+        <v>6</v>
+      </c>
+      <c r="U33">
+        <f>SUMIF(Scoring!K2:K109,A33,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A33,Scoring!F2:F109)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
+      <c r="B34">
+        <f>SUM(Overview!$B$12:$B$33)</f>
         <v>0</v>
       </c>
     </row>
@@ -2297,7 +2561,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
@@ -2315,37 +2579,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2356,19 +2620,19 @@
         <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>258</v>
+        <v>340</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2387,22 +2651,22 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="E3" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>259</v>
+        <v>341</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2419,22 +2683,22 @@
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="E4" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>184</v>
+        <v>265</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>260</v>
+        <v>342</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2451,22 +2715,22 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="E5" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>185</v>
+        <v>266</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>260</v>
+        <v>342</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -2483,22 +2747,22 @@
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="E6" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>186</v>
+        <v>267</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>260</v>
+        <v>342</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -2517,22 +2781,19 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="H7" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -2547,23 +2808,21 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="E8" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>261</v>
+        <v>343</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -2573,31 +2832,26 @@
         <v>6</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="E9" t="s">
-        <v>181</v>
+        <v>261</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="H9" s="1" t="s">
-        <v>262</v>
+        <v>343</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -2607,29 +2861,29 @@
         <v>6</v>
       </c>
       <c r="K9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>189</v>
+        <v>268</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>263</v>
+        <v>342</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -2639,29 +2893,26 @@
         <v>6</v>
       </c>
       <c r="K10" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="E11" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="H11" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -2671,31 +2922,28 @@
         <v>6</v>
       </c>
       <c r="K11" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="E12" t="s">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="H12" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -2705,29 +2953,26 @@
         <v>6</v>
       </c>
       <c r="K12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="E13" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="H13" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -2737,29 +2982,26 @@
         <v>6</v>
       </c>
       <c r="K13" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="E14" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="H14" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -2769,29 +3011,26 @@
         <v>6</v>
       </c>
       <c r="K14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="E15" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="H15" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -2801,29 +3040,26 @@
         <v>6</v>
       </c>
       <c r="K15" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="E16" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="H16" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -2833,29 +3069,26 @@
         <v>6</v>
       </c>
       <c r="K16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="E17" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="H17" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -2865,28 +3098,31 @@
         <v>6</v>
       </c>
       <c r="K17" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="E18" t="s">
-        <v>179</v>
+        <v>262</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
+      <c r="G18" s="1" t="s">
+        <v>269</v>
+      </c>
       <c r="H18" s="1" t="s">
-        <v>261</v>
+        <v>344</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -2896,26 +3132,29 @@
         <v>6</v>
       </c>
       <c r="K18" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="E19" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
+      <c r="G19" s="1" t="s">
+        <v>270</v>
+      </c>
       <c r="H19" s="1" t="s">
-        <v>261</v>
+        <v>345</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -2925,28 +3164,29 @@
         <v>6</v>
       </c>
       <c r="K19" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="E20" t="s">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
+      <c r="G20" s="1" t="s">
+        <v>271</v>
+      </c>
       <c r="H20" s="1" t="s">
-        <v>264</v>
+        <v>342</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -2956,848 +3196,823 @@
         <v>6</v>
       </c>
       <c r="K20" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="E21" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
+      <c r="G21" s="1" t="s">
+        <v>272</v>
+      </c>
       <c r="H21" s="1" t="s">
-        <v>265</v>
+        <v>342</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K21" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="E22" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>197</v>
+        <v>273</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>260</v>
+        <v>342</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K22" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="E23" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
+      <c r="G23" s="1" t="s">
+        <v>274</v>
+      </c>
       <c r="H23" s="1" t="s">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K23" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="E24" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>198</v>
+        <v>275</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>260</v>
+        <v>342</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K24" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="2"/>
-      <c r="B25" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="E25" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
+      <c r="G25" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="H25" s="1" t="s">
-        <v>267</v>
+        <v>342</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K25" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="E26" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
+      <c r="G26" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="H26" s="1" t="s">
-        <v>261</v>
+        <v>342</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K26" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="E27" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>261</v>
+        <v>343</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K27" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="E28" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>261</v>
+        <v>343</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K28" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="E29" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="H29" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K29" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2"/>
-      <c r="B30" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="E30" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>268</v>
+        <v>343</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K30" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>140</v>
+        <v>181</v>
       </c>
       <c r="E31" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K31" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="E32" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>269</v>
+        <v>343</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="E33" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>265</v>
+        <v>346</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K33" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
+      <c r="A34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C34" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="E34" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>265</v>
+        <v>347</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2"/>
-      <c r="B35" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="E35" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>200</v>
+        <v>278</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>260</v>
+        <v>342</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K35" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="E36" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>270</v>
+        <v>348</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K36" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="E37" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="H37" s="1" t="s">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K37" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="E38" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>271</v>
+        <v>343</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K38" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="E39" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>202</v>
+        <v>279</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>260</v>
+        <v>342</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K39" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="2"/>
-      <c r="B40" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="B40" s="2"/>
       <c r="C40" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="E40" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="H40" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K40" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="E41" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="H41" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K41" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
       <c r="E42" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="H42" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K42" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
+      <c r="B43" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="C43" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="E43" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="H43" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K43" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="E44" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="H44" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K44" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="E45" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K45" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="E46" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="H46" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K46" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="2"/>
-      <c r="B47" s="2" t="s">
-        <v>30</v>
-      </c>
+      <c r="B47" s="2"/>
       <c r="C47" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="E47" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="H47" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K47" t="s">
         <v>30</v>
@@ -3807,29 +4022,26 @@
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="E48" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="H48" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K48" t="s">
         <v>30</v>
@@ -3837,695 +4049,1912 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C49" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="E49" t="s">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="H49" s="1" t="s">
-        <v>260</v>
+        <v>349</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K49" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="E50" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="H50" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K50" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="E51" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="H51" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K51" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="E52" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>270</v>
+        <v>343</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
         <v>0</v>
       </c>
       <c r="J52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K52" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
       <c r="C53" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="E53" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="H53" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
         <v>0</v>
       </c>
       <c r="J53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K53" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="E54" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="H54" s="1" t="s">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
         <v>0</v>
       </c>
       <c r="J54" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K54" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
+      <c r="B55" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C55" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="E55" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="H55" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
         <v>0</v>
       </c>
       <c r="J55" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K55" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="E56" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="H56" s="1" t="s">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
         <v>0</v>
       </c>
       <c r="J56" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K56" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="E57" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>267</v>
+        <v>342</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
         <v>0</v>
       </c>
       <c r="J57" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K57" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C58" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="E58" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="H58" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
         <v>0</v>
       </c>
       <c r="J58" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K58" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="2"/>
-      <c r="B59" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B59" s="2"/>
       <c r="C59" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="E59" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="H59" s="1" t="s">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
         <v>0</v>
       </c>
       <c r="J59" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K59" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="E60" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="H60" s="1" t="s">
-        <v>260</v>
+        <v>349</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
         <v>0</v>
       </c>
       <c r="J60" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K60" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="E61" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>272</v>
+        <v>343</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
         <v>0</v>
       </c>
       <c r="J61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K61" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="E62" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="H62" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
         <v>0</v>
       </c>
       <c r="J62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K62" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2"/>
-      <c r="B63" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="B63" s="2"/>
       <c r="C63" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="E63" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>273</v>
+        <v>343</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
         <v>0</v>
       </c>
       <c r="J63" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K63" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:11">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
+      <c r="A64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="C64" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="E64" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="H64" s="1" t="s">
-        <v>260</v>
+        <v>351</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
         <v>0</v>
       </c>
       <c r="J64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K64" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
+      <c r="B65" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C65" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="E65" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="H65" s="1" t="s">
-        <v>260</v>
+        <v>347</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
         <v>0</v>
       </c>
       <c r="J65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="E66" t="s">
-        <v>182</v>
+        <v>260</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>273</v>
+        <v>347</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
         <v>0</v>
       </c>
       <c r="J66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="2"/>
-      <c r="B67" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B67" s="2"/>
       <c r="C67" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="E67" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="H67" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
         <v>0</v>
       </c>
       <c r="J67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K67" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="E68" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="H68" s="1" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
         <v>0</v>
       </c>
       <c r="J68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K68" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E69" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>274</v>
+        <v>343</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
         <v>0</v>
       </c>
       <c r="J69" t="s">
+        <v>8</v>
+      </c>
+      <c r="K69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E70" t="s">
+        <v>261</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I70">
+        <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J70" t="s">
+        <v>8</v>
+      </c>
+      <c r="K70" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E71" t="s">
+        <v>260</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I71">
+        <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J71" t="s">
+        <v>8</v>
+      </c>
+      <c r="K71" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E72" t="s">
+        <v>260</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="I72">
+        <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J72" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E73" t="s">
+        <v>260</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="I73">
+        <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J73" t="s">
+        <v>8</v>
+      </c>
+      <c r="K73" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E74" t="s">
+        <v>260</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="I74">
+        <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J74" t="s">
+        <v>8</v>
+      </c>
+      <c r="K74" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E75" t="s">
+        <v>260</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I75">
+        <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J75" t="s">
+        <v>8</v>
+      </c>
+      <c r="K75" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E76" t="s">
+        <v>261</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I76">
+        <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J76" t="s">
+        <v>8</v>
+      </c>
+      <c r="K76" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E77" t="s">
+        <v>261</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I77">
+        <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J77" t="s">
+        <v>8</v>
+      </c>
+      <c r="K77" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E78" t="s">
+        <v>261</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I78">
+        <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J78" t="s">
+        <v>8</v>
+      </c>
+      <c r="K78" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E79" t="s">
+        <v>261</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I79">
+        <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J79" t="s">
+        <v>8</v>
+      </c>
+      <c r="K79" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E80" t="s">
+        <v>260</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I80">
+        <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J80" t="s">
+        <v>8</v>
+      </c>
+      <c r="K80" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E81" t="s">
+        <v>260</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="I81">
+        <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J81" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E82" t="s">
+        <v>261</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I82">
+        <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J82" t="s">
+        <v>8</v>
+      </c>
+      <c r="K82" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E83" t="s">
+        <v>260</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I83">
+        <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J83" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E84" t="s">
+        <v>261</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I84">
+        <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J84" t="s">
+        <v>8</v>
+      </c>
+      <c r="K84" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E85" t="s">
+        <v>261</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I85">
+        <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J85" t="s">
+        <v>8</v>
+      </c>
+      <c r="K85" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E86" t="s">
+        <v>261</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I86">
+        <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J86" t="s">
+        <v>8</v>
+      </c>
+      <c r="K86" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E87" t="s">
+        <v>261</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I87">
+        <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J87" t="s">
+        <v>8</v>
+      </c>
+      <c r="K87" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E88" t="s">
+        <v>260</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="I88">
+        <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J88" t="s">
+        <v>8</v>
+      </c>
+      <c r="K88" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K69" t="s">
+      <c r="B89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E89" t="s">
+        <v>260</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I89">
+        <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J89" t="s">
+        <v>9</v>
+      </c>
+      <c r="K89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E90" t="s">
+        <v>260</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="I90">
+        <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J90" t="s">
+        <v>9</v>
+      </c>
+      <c r="K90" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E91" t="s">
+        <v>260</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I91">
+        <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J91" t="s">
+        <v>9</v>
+      </c>
+      <c r="K91" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E92" t="s">
+        <v>260</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="I92">
+        <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J92" t="s">
+        <v>9</v>
+      </c>
+      <c r="K92" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E93" t="s">
+        <v>260</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="I93">
+        <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J93" t="s">
+        <v>9</v>
+      </c>
+      <c r="K93" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E94" t="s">
+        <v>260</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I94">
+        <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J94" t="s">
+        <v>9</v>
+      </c>
+      <c r="K94" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E95" t="s">
+        <v>260</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I95">
+        <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J95" t="s">
+        <v>9</v>
+      </c>
+      <c r="K95" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E96" t="s">
+        <v>260</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I96">
+        <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J96" t="s">
+        <v>9</v>
+      </c>
+      <c r="K96" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E97" t="s">
+        <v>260</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="I97">
+        <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J97" t="s">
+        <v>9</v>
+      </c>
+      <c r="K97" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E98" t="s">
+        <v>260</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I98">
+        <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J98" t="s">
+        <v>9</v>
+      </c>
+      <c r="K98" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E99" t="s">
+        <v>260</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="I99">
+        <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J99" t="s">
+        <v>9</v>
+      </c>
+      <c r="K99" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E100" t="s">
+        <v>260</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I100">
+        <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J100" t="s">
+        <v>9</v>
+      </c>
+      <c r="K100" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E101" t="s">
+        <v>260</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I101">
+        <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J101" t="s">
+        <v>9</v>
+      </c>
+      <c r="K101" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E102" t="s">
+        <v>263</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="I102">
+        <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J102" t="s">
+        <v>9</v>
+      </c>
+      <c r="K102" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="C103" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E103" t="s">
+        <v>261</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I103">
+        <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J103" t="s">
+        <v>9</v>
+      </c>
+      <c r="K103" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E104" t="s">
+        <v>260</v>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I104">
+        <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J104" t="s">
+        <v>9</v>
+      </c>
+      <c r="K104" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E105" t="s">
+        <v>260</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I105">
+        <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J105" t="s">
+        <v>9</v>
+      </c>
+      <c r="K105" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E106" t="s">
+        <v>261</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I106">
+        <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J106" t="s">
+        <v>9</v>
+      </c>
+      <c r="K106" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E107" t="s">
+        <v>260</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="I107">
+        <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J107" t="s">
+        <v>9</v>
+      </c>
+      <c r="K107" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E108" t="s">
+        <v>261</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I108">
+        <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J108" t="s">
+        <v>9</v>
+      </c>
+      <c r="K108" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E109" t="s">
+        <v>261</v>
+      </c>
+      <c r="F109">
+        <v>1</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I109">
+        <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J109" t="s">
+        <v>9</v>
+      </c>
+      <c r="K109" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A2:A20"/>
-    <mergeCell ref="A21:A31"/>
-    <mergeCell ref="A32:A52"/>
-    <mergeCell ref="A53:A69"/>
+  <mergeCells count="23">
+    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="A34:A63"/>
+    <mergeCell ref="A64:A88"/>
+    <mergeCell ref="A89:A109"/>
     <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B7:B11"/>
     <mergeCell ref="B12:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B35:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B47:B52"/>
-    <mergeCell ref="B53:B58"/>
-    <mergeCell ref="B59:B62"/>
-    <mergeCell ref="B63:B66"/>
-    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B21:B26"/>
+    <mergeCell ref="B27:B32"/>
+    <mergeCell ref="B34:B42"/>
+    <mergeCell ref="B43:B48"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B63"/>
+    <mergeCell ref="B65:B70"/>
+    <mergeCell ref="B71:B75"/>
+    <mergeCell ref="B76:B82"/>
+    <mergeCell ref="B83:B88"/>
+    <mergeCell ref="B89:B94"/>
+    <mergeCell ref="B95:B98"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="B103:B109"/>
   </mergeCells>
-  <dataValidations count="68">
+  <dataValidations count="108">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"0: Not monitored,2: Reported,5: Manual remediation,10: Automated remediation"</formula1>
     </dataValidation>
@@ -4542,193 +5971,313 @@
       <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H16">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
       <formula1>"0: Low Maturity. Score Range (0-8),4: Developing. Score Range (9-17),7: Established. Score Range (18-24),10: Optimizing. Score Range (25-29)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
       <formula1>"0: Low Maturity. Score Range (0-15),4: Developing. Score Range (16-31),7: Established. Score Range (32-44),10: Optimizing. Score Range (45-52)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
       <formula1>"0: No items completed,2: item 1 completed,4: items 1-2 completed,6: items 1-3 completed,8: items 1-4 completed,10: items 1-5 completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H16">
-      <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
-      <formula1>"0: Not done,10: Done and clearly defined"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
-      <formula1>"0: Not done,10: Defined"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
-      <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
-      <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H24">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+      <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+      <formula1>"0: Not done,10: Done and clearly defined"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
-      <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
-      <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
+      <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
+      <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
+      <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55">
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H56">
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
+      <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
+      <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
+      <formula1>"0: Does not exist,10: Exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
+      <formula1>"0: Does not exist,10: Exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H70">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H71">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
       <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
       <formula1>"0: No alerting,10: Alerting exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H77">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H78">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
       <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H81">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H83">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H84">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H85">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H86">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
       <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80% ,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
       <formula1>"0: No items completed,5: 1 item  completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H56">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
       <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
       <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
       <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H101">
       <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H102">
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H104">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H105">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H106">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H107">
       <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H109">
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -4800,6 +6349,46 @@
     <hyperlink ref="D67" r:id="rId66"/>
     <hyperlink ref="D68" r:id="rId67"/>
     <hyperlink ref="D69" r:id="rId68"/>
+    <hyperlink ref="D70" r:id="rId69"/>
+    <hyperlink ref="D71" r:id="rId70"/>
+    <hyperlink ref="D72" r:id="rId71"/>
+    <hyperlink ref="D73" r:id="rId72"/>
+    <hyperlink ref="D74" r:id="rId73"/>
+    <hyperlink ref="D75" r:id="rId74"/>
+    <hyperlink ref="D76" r:id="rId75"/>
+    <hyperlink ref="D77" r:id="rId76"/>
+    <hyperlink ref="D78" r:id="rId77"/>
+    <hyperlink ref="D79" r:id="rId78"/>
+    <hyperlink ref="D80" r:id="rId79"/>
+    <hyperlink ref="D81" r:id="rId80"/>
+    <hyperlink ref="D82" r:id="rId81"/>
+    <hyperlink ref="D83" r:id="rId82"/>
+    <hyperlink ref="D84" r:id="rId83"/>
+    <hyperlink ref="D85" r:id="rId84"/>
+    <hyperlink ref="D86" r:id="rId85"/>
+    <hyperlink ref="D87" r:id="rId86"/>
+    <hyperlink ref="D88" r:id="rId87"/>
+    <hyperlink ref="D89" r:id="rId88"/>
+    <hyperlink ref="D90" r:id="rId89"/>
+    <hyperlink ref="D91" r:id="rId90"/>
+    <hyperlink ref="D92" r:id="rId91"/>
+    <hyperlink ref="D93" r:id="rId92"/>
+    <hyperlink ref="D94" r:id="rId93"/>
+    <hyperlink ref="D95" r:id="rId94"/>
+    <hyperlink ref="D96" r:id="rId95"/>
+    <hyperlink ref="D97" r:id="rId96"/>
+    <hyperlink ref="D98" r:id="rId97"/>
+    <hyperlink ref="D99" r:id="rId98"/>
+    <hyperlink ref="D100" r:id="rId99"/>
+    <hyperlink ref="D101" r:id="rId100"/>
+    <hyperlink ref="D102" r:id="rId101"/>
+    <hyperlink ref="D103" r:id="rId102"/>
+    <hyperlink ref="D104" r:id="rId103"/>
+    <hyperlink ref="D105" r:id="rId104"/>
+    <hyperlink ref="D106" r:id="rId105"/>
+    <hyperlink ref="D107" r:id="rId106"/>
+    <hyperlink ref="D108" r:id="rId107"/>
+    <hyperlink ref="D109" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="363">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -199,6 +199,9 @@
     <t>Automate Tasks &amp; Review Maturity</t>
   </si>
   <si>
+    <t>Assess Tooling Needs &amp; Criteria</t>
+  </si>
+  <si>
     <t>Evaluate Build vs Buy Options</t>
   </si>
   <si>
@@ -523,6 +526,9 @@
     <t>096</t>
   </si>
   <si>
+    <t>124</t>
+  </si>
+  <si>
     <t>125</t>
   </si>
   <si>
@@ -799,16 +805,19 @@
     <t>022</t>
   </si>
   <si>
-    <t>1.7.0</t>
+    <t>1.8.0</t>
+  </si>
+  <si>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>1.0.0</t>
   </si>
   <si>
-    <t>2.0.1</t>
-  </si>
-  <si>
-    <t>1.5.0</t>
+    <t>2.1.0</t>
+  </si>
+  <si>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>* Select which teams or groups are in scope for the planned assessments
@@ -842,11 +851,24 @@
 10*Ceil(x/2)</t>
   </si>
   <si>
+    <t>* Weighted sum
+  Criteria document (score x3),
+  KPI alignment (score x3),
+  Stakeholder count capped at 5 (score x2),
+  Refresh cadence (score x2).
+  Max Raw Score (31)
+* Criteria formally documented (0=None, 1=Draft, 2=Approved, 3=Versioned+Reviewed)
+* Criteria explicitly mapped to FinOps KPIs (0=None, 1=Partial, 2=Full)
+* of FinOps personas involved in criteria definition (0-5)
+* Criteria review frequency (0=Never, 1=Ad-hoc, 2=Annual, 3=Quarterly+)
+* Output Range (0 - Max Raw)</t>
+  </si>
+  <si>
     <t xml:space="preserve">* Weighted sum
-  TCO (score ×3),
-  Vendor scoring (score ×3),
-  Decision document (score ×3),
-  Rules established (score ×1).
+  TCO (score x3),
+  Vendor scoring (score x3),
+  Decision document (score x3),
+  Rules established (score x1).
   Max Raw Score (29)
 * TCO_Analysis - Total Cost of Ownership analysis performed
   (0=None, 1=High-level, 2=Detailed, 3=Validated with Finance)
@@ -1167,6 +1189,9 @@
     <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Defined'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity (0-9)'}, {'Score': 4, 'Condition': 'Developing (10-18)'}, {'Score': 7, 'Condition': 'Established (19-26)'}, {'Score': 10, 'Condition': 'Optimizing (27-31)'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-8)'}, {'Score': 4, 'Condition': 'Developing, Score Range (9-17)'}, {'Score': 7, 'Condition': 'Established, Score Range (18-24)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (25-29)'}]</t>
   </si>
   <si>
@@ -1249,6 +1274,9 @@
   </si>
   <si>
     <t>0: Not done</t>
+  </si>
+  <si>
+    <t>0: Low Maturity (0-9)</t>
   </si>
   <si>
     <t>0: Low Maturity. Score Range (0-8)</t>
@@ -2193,14 +2221,14 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2">
-        <f>SUM(Scoring!F2:F109)</f>
+        <f>SUM(Scoring!F2:F110)</f>
         <v>0</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2">
-        <f>SUM(Scoring!I2:I109)/A2</f>
+        <f>SUM(Scoring!I2:I110)/A2</f>
         <v>0</v>
       </c>
       <c r="D2">
@@ -2221,10 +2249,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U5">
-        <f>SUMIF(Scoring!J2:J109,A5,Scoring!I2:I109)/SUMIF(Scoring!J2:J109,A5,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!J2:J110,A5,Scoring!I2:I110)/SUMIF(Scoring!J2:J110,A5,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2236,7 +2264,7 @@
         <v>30</v>
       </c>
       <c r="U6">
-        <f>SUMIF(Scoring!J2:J109,A6,Scoring!I2:I109)/SUMIF(Scoring!J2:J109,A6,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!J2:J110,A6,Scoring!I2:I110)/SUMIF(Scoring!J2:J110,A6,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2248,7 +2276,7 @@
         <v>25</v>
       </c>
       <c r="U7">
-        <f>SUMIF(Scoring!J2:J109,A7,Scoring!I2:I109)/SUMIF(Scoring!J2:J109,A7,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!J2:J110,A7,Scoring!I2:I110)/SUMIF(Scoring!J2:J110,A7,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2260,7 +2288,7 @@
         <v>21</v>
       </c>
       <c r="U8">
-        <f>SUMIF(Scoring!J2:J109,A8,Scoring!I2:I109)/SUMIF(Scoring!J2:J109,A8,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!J2:J110,A8,Scoring!I2:I110)/SUMIF(Scoring!J2:J110,A8,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2286,7 +2314,7 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <f>SUMIF(Scoring!K2:K109,A12,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A12,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A12,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A12,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2298,7 +2326,7 @@
         <v>4</v>
       </c>
       <c r="U13">
-        <f>SUMIF(Scoring!K2:K109,A13,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A13,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A13,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A13,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2310,7 +2338,7 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <f>SUMIF(Scoring!K2:K109,A14,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A14,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A14,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A14,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2319,10 +2347,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <f>SUMIF(Scoring!K2:K109,A15,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A15,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A15,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A15,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2334,7 +2362,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <f>SUMIF(Scoring!K2:K109,A16,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A16,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A16,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A16,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2346,7 +2374,7 @@
         <v>4</v>
       </c>
       <c r="U17">
-        <f>SUMIF(Scoring!K2:K109,A17,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A17,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A17,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A17,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2358,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="U18">
-        <f>SUMIF(Scoring!K2:K109,A18,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A18,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A18,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A18,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2370,7 +2398,7 @@
         <v>4</v>
       </c>
       <c r="U19">
-        <f>SUMIF(Scoring!K2:K109,A19,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A19,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A19,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A19,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2382,7 +2410,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <f>SUMIF(Scoring!K2:K109,A20,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A20,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A20,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A20,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2394,7 +2422,7 @@
         <v>6</v>
       </c>
       <c r="U21">
-        <f>SUMIF(Scoring!K2:K109,A21,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A21,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A21,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A21,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2406,7 +2434,7 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <f>SUMIF(Scoring!K2:K109,A22,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A22,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A22,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A22,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2418,7 +2446,7 @@
         <v>1</v>
       </c>
       <c r="U23">
-        <f>SUMIF(Scoring!K2:K109,A23,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A23,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A23,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A23,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2430,7 +2458,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <f>SUMIF(Scoring!K2:K109,A24,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A24,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A24,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A24,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2442,7 +2470,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <f>SUMIF(Scoring!K2:K109,A25,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A25,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A25,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A25,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2454,7 +2482,7 @@
         <v>1</v>
       </c>
       <c r="U26">
-        <f>SUMIF(Scoring!K2:K109,A26,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A26,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A26,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A26,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2466,7 +2494,7 @@
         <v>6</v>
       </c>
       <c r="U27">
-        <f>SUMIF(Scoring!K2:K109,A27,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A27,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A27,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A27,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2478,7 +2506,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <f>SUMIF(Scoring!K2:K109,A28,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A28,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A28,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A28,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2490,7 +2518,7 @@
         <v>3</v>
       </c>
       <c r="U29">
-        <f>SUMIF(Scoring!K2:K109,A29,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A29,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A29,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A29,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2502,7 +2530,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <f>SUMIF(Scoring!K2:K109,A30,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A30,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A30,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A30,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2514,7 +2542,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <f>SUMIF(Scoring!K2:K109,A31,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A31,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A31,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A31,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2526,7 +2554,7 @@
         <v>6</v>
       </c>
       <c r="U32">
-        <f>SUMIF(Scoring!K2:K109,A32,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A32,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A32,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A32,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2538,7 +2566,7 @@
         <v>6</v>
       </c>
       <c r="U33">
-        <f>SUMIF(Scoring!K2:K109,A33,Scoring!I2:I109)/SUMIF(Scoring!K2:K109,A33,Scoring!F2:F109)</f>
+        <f>SUMIF(Scoring!K2:K110,A33,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A33,Scoring!F2:F110)</f>
         <v>0</v>
       </c>
     </row>
@@ -2561,7 +2589,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
@@ -2623,16 +2651,16 @@
         <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2654,19 +2682,19 @@
         <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2686,19 +2714,19 @@
         <v>46</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2718,19 +2746,19 @@
         <v>47</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -2750,19 +2778,19 @@
         <v>48</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -2784,16 +2812,16 @@
         <v>49</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -2813,16 +2841,16 @@
         <v>50</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -2842,16 +2870,16 @@
         <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E9" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -2871,19 +2899,19 @@
         <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -2903,16 +2931,16 @@
         <v>53</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E11" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -2934,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E12" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -2963,16 +2991,16 @@
         <v>55</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -2992,16 +3020,16 @@
         <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -3021,16 +3049,16 @@
         <v>57</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3050,16 +3078,16 @@
         <v>58</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3079,16 +3107,16 @@
         <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3110,19 +3138,19 @@
         <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E18" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3142,19 +3170,19 @@
         <v>61</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E19" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3174,19 +3202,19 @@
         <v>62</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E20" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3201,26 +3229,24 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2"/>
-      <c r="B21" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E21" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3230,29 +3256,31 @@
         <v>6</v>
       </c>
       <c r="K21" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="C22" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E22" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3272,19 +3300,19 @@
         <v>65</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E23" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3304,19 +3332,19 @@
         <v>66</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3336,19 +3364,19 @@
         <v>67</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E25" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3368,19 +3396,19 @@
         <v>68</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E26" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3395,23 +3423,24 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2"/>
-      <c r="B27" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E27" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
+      <c r="G27" s="1" t="s">
+        <v>281</v>
+      </c>
       <c r="H27" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3421,26 +3450,28 @@
         <v>6</v>
       </c>
       <c r="K27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E28" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3460,16 +3491,16 @@
         <v>71</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E29" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3489,16 +3520,16 @@
         <v>72</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E30" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3518,16 +3549,16 @@
         <v>73</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E31" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3547,16 +3578,16 @@
         <v>74</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E32" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -3571,23 +3602,21 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2"/>
-      <c r="B33" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E33" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -3597,62 +3626,61 @@
         <v>6</v>
       </c>
       <c r="K33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E34" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
         <v>0</v>
       </c>
       <c r="J34" t="s">
+        <v>6</v>
+      </c>
+      <c r="K34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K34" t="s">
+      <c r="B35" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E35" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="H35" s="1" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -3672,16 +3700,19 @@
         <v>78</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E36" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
+      <c r="G36" s="1" t="s">
+        <v>282</v>
+      </c>
       <c r="H36" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -3701,16 +3732,16 @@
         <v>79</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E37" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -3730,16 +3761,16 @@
         <v>80</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E38" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -3759,19 +3790,16 @@
         <v>81</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E39" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="H39" s="1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -3791,16 +3819,19 @@
         <v>82</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E40" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
+      <c r="G40" s="1" t="s">
+        <v>283</v>
+      </c>
       <c r="H40" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -3820,16 +3851,16 @@
         <v>83</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E41" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -3849,16 +3880,16 @@
         <v>84</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E42" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -3873,23 +3904,21 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="2"/>
-      <c r="B43" s="2" t="s">
-        <v>30</v>
-      </c>
+      <c r="B43" s="2"/>
       <c r="C43" s="2" t="s">
         <v>85</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E43" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -3899,26 +3928,28 @@
         <v>7</v>
       </c>
       <c r="K43" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
+      <c r="B44" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="C44" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E44" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -3938,16 +3969,16 @@
         <v>87</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E45" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -3967,16 +3998,16 @@
         <v>88</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E46" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -3996,16 +4027,16 @@
         <v>89</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E47" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4025,16 +4056,16 @@
         <v>90</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E48" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4049,23 +4080,21 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="2"/>
-      <c r="B49" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="B49" s="2"/>
       <c r="C49" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E49" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4075,26 +4104,28 @@
         <v>7</v>
       </c>
       <c r="K49" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
+      <c r="B50" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C50" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4114,16 +4145,16 @@
         <v>93</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E51" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4143,16 +4174,16 @@
         <v>94</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E52" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4172,16 +4203,16 @@
         <v>95</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E53" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4201,16 +4232,16 @@
         <v>96</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E54" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4225,23 +4256,21 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="2"/>
-      <c r="B55" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="B55" s="2"/>
       <c r="C55" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E55" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4251,26 +4280,28 @@
         <v>7</v>
       </c>
       <c r="K55" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
+      <c r="B56" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C56" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E56" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4290,19 +4321,16 @@
         <v>99</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E57" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="H57" s="1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4317,23 +4345,24 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="2"/>
-      <c r="B58" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="B58" s="2"/>
       <c r="C58" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E58" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
+      <c r="G58" s="1" t="s">
+        <v>284</v>
+      </c>
       <c r="H58" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4343,26 +4372,28 @@
         <v>7</v>
       </c>
       <c r="K58" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
+      <c r="B59" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C59" s="2" t="s">
         <v>101</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E59" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4382,16 +4413,16 @@
         <v>102</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E60" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4411,16 +4442,16 @@
         <v>103</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E61" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4440,16 +4471,16 @@
         <v>104</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E62" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4469,16 +4500,16 @@
         <v>105</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E63" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4492,57 +4523,55 @@
       </c>
     </row>
     <row r="64" spans="1:11">
-      <c r="A64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
       <c r="C64" s="2" t="s">
         <v>106</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E64" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
         <v>0</v>
       </c>
       <c r="J64" t="s">
+        <v>7</v>
+      </c>
+      <c r="K64" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K64" t="s">
+      <c r="B65" s="2" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>107</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E65" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -4552,26 +4581,28 @@
         <v>8</v>
       </c>
       <c r="K65" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
+      <c r="B66" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C66" s="2" t="s">
         <v>108</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E66" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -4591,16 +4622,16 @@
         <v>109</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E67" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -4620,16 +4651,16 @@
         <v>110</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E68" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -4649,16 +4680,16 @@
         <v>111</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E69" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -4678,16 +4709,16 @@
         <v>112</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E70" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -4702,26 +4733,21 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="2"/>
-      <c r="B71" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="B71" s="2"/>
       <c r="C71" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E71" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="H71" s="1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -4731,26 +4757,31 @@
         <v>8</v>
       </c>
       <c r="K71" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="C72" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E72" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
+      <c r="G72" s="1" t="s">
+        <v>285</v>
+      </c>
       <c r="H72" s="1" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -4770,19 +4801,16 @@
         <v>115</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E73" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
-      <c r="G73" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="H73" s="1" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -4802,16 +4830,19 @@
         <v>116</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E74" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
+      <c r="G74" s="1" t="s">
+        <v>286</v>
+      </c>
       <c r="H74" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -4831,19 +4862,16 @@
         <v>117</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E75" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="H75" s="1" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -4858,26 +4886,24 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="2"/>
-      <c r="B76" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="B76" s="2"/>
       <c r="C76" s="2" t="s">
         <v>118</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E76" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -4887,29 +4913,31 @@
         <v>8</v>
       </c>
       <c r="K76" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
+      <c r="B77" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C77" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E77" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -4929,19 +4957,19 @@
         <v>120</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E78" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
@@ -4961,19 +4989,19 @@
         <v>121</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E79" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
@@ -4993,19 +5021,19 @@
         <v>122</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E80" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -5025,16 +5053,19 @@
         <v>123</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E81" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
+      <c r="G81" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="H81" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5054,19 +5085,16 @@
         <v>124</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E82" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
-      <c r="G82" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="H82" s="1" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5081,26 +5109,24 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="2"/>
-      <c r="B83" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="B83" s="2"/>
       <c r="C83" s="2" t="s">
         <v>125</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E83" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5110,29 +5136,31 @@
         <v>8</v>
       </c>
       <c r="K83" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
+      <c r="B84" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C84" s="2" t="s">
         <v>126</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E84" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5152,19 +5180,19 @@
         <v>127</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5184,19 +5212,19 @@
         <v>128</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5216,19 +5244,19 @@
         <v>129</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E87" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5248,16 +5276,19 @@
         <v>130</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E88" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
+      <c r="G88" s="1" t="s">
+        <v>298</v>
+      </c>
       <c r="H88" s="1" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5271,61 +5302,58 @@
       </c>
     </row>
     <row r="89" spans="1:11">
-      <c r="A89" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
       <c r="C89" s="2" t="s">
         <v>131</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E89" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
-      <c r="G89" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="H89" s="1" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
         <v>0</v>
       </c>
       <c r="J89" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K89" t="s">
+      <c r="B90" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
       <c r="C90" s="2" t="s">
         <v>132</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E90" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -5345,19 +5373,19 @@
         <v>133</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E91" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -5377,19 +5405,19 @@
         <v>134</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E92" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -5409,19 +5437,19 @@
         <v>135</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E93" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -5441,19 +5469,19 @@
         <v>136</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E94" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -5468,26 +5496,24 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="2"/>
-      <c r="B95" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B95" s="2"/>
       <c r="C95" s="2" t="s">
         <v>137</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E95" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
@@ -5497,29 +5523,31 @@
         <v>9</v>
       </c>
       <c r="K95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
+      <c r="B96" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C96" s="2" t="s">
         <v>138</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E96" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
@@ -5539,16 +5567,19 @@
         <v>139</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E97" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
+      <c r="G97" s="1" t="s">
+        <v>306</v>
+      </c>
       <c r="H97" s="1" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
@@ -5568,19 +5599,16 @@
         <v>140</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E98" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
-      <c r="G98" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="H98" s="1" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
@@ -5595,23 +5623,24 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="2"/>
-      <c r="B99" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="B99" s="2"/>
       <c r="C99" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E99" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
+      <c r="G99" s="1" t="s">
+        <v>307</v>
+      </c>
       <c r="H99" s="1" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -5621,29 +5650,28 @@
         <v>9</v>
       </c>
       <c r="K99" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
+      <c r="B100" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C100" s="2" t="s">
         <v>142</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E100" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
-      <c r="G100" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="H100" s="1" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -5663,19 +5691,19 @@
         <v>143</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E101" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -5695,16 +5723,19 @@
         <v>144</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E102" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
+      <c r="G102" s="1" t="s">
+        <v>309</v>
+      </c>
       <c r="H102" s="1" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -5719,23 +5750,21 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="2"/>
-      <c r="B103" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B103" s="2"/>
       <c r="C103" s="2" t="s">
         <v>145</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E103" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -5745,29 +5774,28 @@
         <v>9</v>
       </c>
       <c r="K103" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="2"/>
-      <c r="B104" s="2"/>
+      <c r="B104" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="C104" s="2" t="s">
         <v>146</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E104" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
-      <c r="G104" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="H104" s="1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
@@ -5787,19 +5815,19 @@
         <v>147</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
@@ -5819,16 +5847,19 @@
         <v>148</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E106" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
+      <c r="G106" s="1" t="s">
+        <v>311</v>
+      </c>
       <c r="H106" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
@@ -5848,16 +5879,16 @@
         <v>149</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E107" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
@@ -5877,16 +5908,16 @@
         <v>150</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E108" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
@@ -5906,16 +5937,16 @@
         <v>151</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E109" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
@@ -5928,33 +5959,62 @@
         <v>29</v>
       </c>
     </row>
+    <row r="110" spans="1:11">
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E110" t="s">
+        <v>264</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I110">
+        <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J110" t="s">
+        <v>9</v>
+      </c>
+      <c r="K110" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A2:A33"/>
-    <mergeCell ref="A34:A63"/>
-    <mergeCell ref="A64:A88"/>
-    <mergeCell ref="A89:A109"/>
+    <mergeCell ref="A2:A34"/>
+    <mergeCell ref="A35:A64"/>
+    <mergeCell ref="A65:A89"/>
+    <mergeCell ref="A90:A110"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="B7:B11"/>
     <mergeCell ref="B12:B17"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="B21:B26"/>
-    <mergeCell ref="B27:B32"/>
-    <mergeCell ref="B34:B42"/>
-    <mergeCell ref="B43:B48"/>
-    <mergeCell ref="B49:B54"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B63"/>
-    <mergeCell ref="B65:B70"/>
-    <mergeCell ref="B71:B75"/>
-    <mergeCell ref="B76:B82"/>
-    <mergeCell ref="B83:B88"/>
-    <mergeCell ref="B89:B94"/>
-    <mergeCell ref="B95:B98"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B109"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="B28:B33"/>
+    <mergeCell ref="B35:B43"/>
+    <mergeCell ref="B44:B49"/>
+    <mergeCell ref="B50:B55"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="B59:B64"/>
+    <mergeCell ref="B66:B71"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="B77:B83"/>
+    <mergeCell ref="B84:B89"/>
+    <mergeCell ref="B90:B95"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="B104:B110"/>
   </mergeCells>
-  <dataValidations count="108">
+  <dataValidations count="109">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"0: Not monitored,2: Reported,5: Manual remediation,10: Automated remediation"</formula1>
     </dataValidation>
@@ -6004,73 +6064,73 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
+      <formula1>"0: Low Maturity (0-9),4: Developing (10-18),7: Established (19-26),10: Optimizing (27-31)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
       <formula1>"0: Low Maturity. Score Range (0-8),4: Developing. Score Range (9-17),7: Established. Score Range (18-24),10: Optimizing. Score Range (25-29)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
       <formula1>"0: Low Maturity. Score Range (0-15),4: Developing. Score Range (16-31),7: Established. Score Range (32-44),10: Optimizing. Score Range (45-52)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
       <formula1>"0: No items completed,2: item 1 completed,4: items 1-2 completed,6: items 1-3 completed,8: items 1-4 completed,10: items 1-5 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H24">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
       <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
       <formula1>"0: Not done,10: Done and clearly defined"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
       <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
       <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -6097,43 +6157,43 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H56">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
       <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -6142,16 +6202,16 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
       <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -6163,22 +6223,22 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H71">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
       <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
       <formula1>"0: No alerting,10: Alerting exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H77">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
@@ -6187,96 +6247,99 @@
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
       <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H81">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H81">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H83">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H84">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H85">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H86">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
       <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80% ,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
       <formula1>"0: No items completed,5: 1 item  completed,10: 2 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
       <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
       <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
-      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H101">
       <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H102">
+      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H104">
       <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H104">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H105">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H106">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H107">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H107">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108">
       <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H109">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H109">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H110">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6389,6 +6452,7 @@
     <hyperlink ref="D107" r:id="rId106"/>
     <hyperlink ref="D108" r:id="rId107"/>
     <hyperlink ref="D109" r:id="rId108"/>
+    <hyperlink ref="D110" r:id="rId109"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -1481,7 +1481,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
-  <c:style val="37"/>
+  <c:style val="29"/>
   <c:chart>
     <c:plotArea>
       <c:layout/>
@@ -1567,7 +1567,6 @@
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
-    <c:plotVisOnly val="1"/>
   </c:chart>
 </c:chartSpace>
 </file>
@@ -1575,7 +1574,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
-  <c:style val="37"/>
+  <c:style val="29"/>
   <c:chart>
     <c:plotArea>
       <c:layout/>
@@ -1769,7 +1768,6 @@
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
-    <c:plotVisOnly val="1"/>
   </c:chart>
 </c:chartSpace>
 </file>
@@ -2197,12 +2195,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:U34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -2590,7 +2589,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -2201,7 +2201,7 @@
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="0" hidden="1" customWidth="1"/>
+    <col min="6" max="16384" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -2235,6 +2235,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3" spans="1:21"/>
     <row r="4" spans="1:21">
       <c r="A4" t="s">
         <v>4</v>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -1556,11 +1556,12 @@
         <c:axId val="50020002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="10"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
@@ -1757,11 +1758,12 @@
         <c:axId val="50030002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="10"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030001"/>
         <c:crosses val="autoZero"/>
@@ -2298,6 +2300,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10" spans="1:21"/>
     <row r="11" spans="1:21">
       <c r="A11" t="s">
         <v>10</v>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="427">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -151,9 +151,21 @@
     <t>action</t>
   </si>
   <si>
+    <t>Draft Cloud Financial Policies</t>
+  </si>
+  <si>
+    <t>Publish Guidelines &amp; Guardrails</t>
+  </si>
+  <si>
+    <t>Educate Stakeholders on Policy</t>
+  </si>
+  <si>
     <t>Monitor Compliance &amp; Report Breaches</t>
   </si>
   <si>
+    <t>Iterate Policies Based on Feedback</t>
+  </si>
+  <si>
     <t>Define Assessment Scope &amp; Goals</t>
   </si>
   <si>
@@ -166,6 +178,9 @@
     <t>Prioritize Actions &amp; Publish Roadmap</t>
   </si>
   <si>
+    <t>Reassess Progress &amp; Update Priorities</t>
+  </si>
+  <si>
     <t>Assess Skills &amp; Training Needs</t>
   </si>
   <si>
@@ -211,6 +226,9 @@
     <t>Train Users &amp; Integrate Data</t>
   </si>
   <si>
+    <t>Monitor Adoption &amp; Iterate Tools</t>
+  </si>
+  <si>
     <t>Establish Cross-Team Collab</t>
   </si>
   <si>
@@ -250,6 +268,15 @@
     <t>Establish Executive Sponsorship</t>
   </si>
   <si>
+    <t>Define Decision Rights &amp; Guardrails</t>
+  </si>
+  <si>
+    <t>Build Multi-Year Investment Forecast</t>
+  </si>
+  <si>
+    <t>Establish Decision Support Cadence</t>
+  </si>
+  <si>
     <t>Establish Architecture Review Process</t>
   </si>
   <si>
@@ -259,6 +286,15 @@
     <t>Estimate Trade-Offs &amp; Document Cases</t>
   </si>
   <si>
+    <t>Implement Iteratively &amp; Measure Results</t>
+  </si>
+  <si>
+    <t>Publish Benefits &amp; Update References</t>
+  </si>
+  <si>
+    <t>Strengthen Architecture Collaboration</t>
+  </si>
+  <si>
     <t>Create Workload Selection Criteria</t>
   </si>
   <si>
@@ -319,6 +355,15 @@
     <t>Build Commitment Analysis Process</t>
   </si>
   <si>
+    <t>Purchase Commitments Regularly</t>
+  </si>
+  <si>
+    <t>Track ROI &amp; Notify Owners</t>
+  </si>
+  <si>
+    <t>Allocate Upfront Costs Transparently</t>
+  </si>
+  <si>
     <t>Leverage Spot &amp; Negotiated Discounts</t>
   </si>
   <si>
@@ -340,9 +385,24 @@
     <t>Track KPIs &amp; Document Playbooks</t>
   </si>
   <si>
+    <t>Select KPIs &amp; Measurement Scope</t>
+  </si>
+  <si>
+    <t>Validate Tagging for Comparability</t>
+  </si>
+  <si>
+    <t>Choose Internal vs External Benchmarks</t>
+  </si>
+  <si>
+    <t>Stand Up Internal Benchmarking</t>
+  </si>
+  <si>
     <t>Track Trends &amp; Compare Over Time</t>
   </si>
   <si>
+    <t>Translate Gaps to Initiatives</t>
+  </si>
+  <si>
     <t>Define Budgeting Strategy</t>
   </si>
   <si>
@@ -361,6 +421,9 @@
     <t>Review &amp; Adapt Budget Strategy</t>
   </si>
   <si>
+    <t>Establish Forecasting Approach</t>
+  </si>
+  <si>
     <t>Collect Business Drivers Regularly</t>
   </si>
   <si>
@@ -433,6 +496,9 @@
     <t>Automate Tagging &amp; Enforcement</t>
   </si>
   <si>
+    <t>Iterate Strategies &amp; Communicate</t>
+  </si>
+  <si>
     <t>Configure Cost Spike Detection</t>
   </si>
   <si>
@@ -442,18 +508,42 @@
     <t>Automate Alert Routing</t>
   </si>
   <si>
+    <t>Record Anomaly Context &amp; Timeline</t>
+  </si>
+  <si>
+    <t>Analyze Root Causes &amp; Fix Issues</t>
+  </si>
+  <si>
     <t>Track Metrics &amp; Avoidance Rates</t>
   </si>
   <si>
+    <t>Tune Thresholds to Reduce Noise</t>
+  </si>
+  <si>
+    <t>Inventory All Data Sources</t>
+  </si>
+  <si>
+    <t>Choose Data Landing Tooling</t>
+  </si>
+  <si>
+    <t>Create Landing Zones &amp; Controls</t>
+  </si>
+  <si>
     <t>Define Data Granularity &amp; Frequency</t>
   </si>
   <si>
+    <t>Document Normalization Rules</t>
+  </si>
+  <si>
     <t>Implement Data Quality Checks</t>
   </si>
   <si>
     <t>Build Ingestion Anomaly Dashboards</t>
   </si>
   <si>
+    <t>Optimize Pipelines for Timeliness</t>
+  </si>
+  <si>
     <t>Define ingestion frequency; include mandatory metadata.</t>
   </si>
   <si>
@@ -478,9 +568,21 @@
     <t>Iterate Based on Feedback</t>
   </si>
   <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
     <t>105</t>
   </si>
   <si>
+    <t>106</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
@@ -493,6 +595,9 @@
     <t>116</t>
   </si>
   <si>
+    <t>117</t>
+  </si>
+  <si>
     <t>097</t>
   </si>
   <si>
@@ -538,6 +643,9 @@
     <t>127</t>
   </si>
   <si>
+    <t>128</t>
+  </si>
+  <si>
     <t>129</t>
   </si>
   <si>
@@ -577,6 +685,15 @@
     <t>136</t>
   </si>
   <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
     <t>061</t>
   </si>
   <si>
@@ -586,6 +703,15 @@
     <t>063</t>
   </si>
   <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>066</t>
+  </si>
+  <si>
     <t>118</t>
   </si>
   <si>
@@ -646,6 +772,15 @@
     <t>080</t>
   </si>
   <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>082</t>
+  </si>
+  <si>
+    <t>083</t>
+  </si>
+  <si>
     <t>084</t>
   </si>
   <si>
@@ -667,9 +802,24 @@
     <t>072</t>
   </si>
   <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
     <t>053</t>
   </si>
   <si>
+    <t>054</t>
+  </si>
+  <si>
     <t>043</t>
   </si>
   <si>
@@ -688,6 +838,9 @@
     <t>048</t>
   </si>
   <si>
+    <t>037</t>
+  </si>
+  <si>
     <t>038</t>
   </si>
   <si>
@@ -760,6 +913,9 @@
     <t>014</t>
   </si>
   <si>
+    <t>015</t>
+  </si>
+  <si>
     <t>023</t>
   </si>
   <si>
@@ -769,18 +925,42 @@
     <t>025</t>
   </si>
   <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
     <t>028</t>
   </si>
   <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
     <t>004</t>
   </si>
   <si>
+    <t>005</t>
+  </si>
+  <si>
     <t>006</t>
   </si>
   <si>
     <t>007</t>
   </si>
   <si>
+    <t>008</t>
+  </si>
+  <si>
     <t>135</t>
   </si>
   <si>
@@ -805,13 +985,13 @@
     <t>022</t>
   </si>
   <si>
+    <t>1.0.0</t>
+  </si>
+  <si>
     <t>1.8.0</t>
   </si>
   <si>
     <t>1.1.0</t>
-  </si>
-  <si>
-    <t>1.0.0</t>
   </si>
   <si>
     <t>2.1.0</t>
@@ -844,6 +1024,12 @@
 2. Determine owners for addressing each of the prioritized gaps
 3. Owners will work with relevant teams to scope out how to meet the target score for each gap
 4. Work is then scheduled in a roadmap with deadlines that can be tracked at the leadership level</t>
+  </si>
+  <si>
+    <t>* Schedule a cadence to report progress outcomes to key stakeholders.
+* Create reporting to show progress on key outcomes across all maturity initiatives.
+* After successful outcomes are achieved, move on to the next prioritized item in the roadmap.
+* Periodically reevaluate the gap analysis and priority list based on lessons learned and new business goals.</t>
   </si>
   <si>
     <t>* Define process for reviewing asking for credits from CSPs
@@ -947,6 +1133,24 @@
 10*Ceil(x/3)</t>
   </si>
   <si>
+    <t>* Document decision rights and approval authority for technology spend
+* Define and publish spend guardrails with named owners
+* Establish escalation path for spend exceptions
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Inventory vendor commitments across technology categories (cloud, SaaS, data center, AI)
+* Create a multi-year forecast incorporating renewal timelines and growth projections
+* Incorporate transition and modernization costs into the investment plan
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Define a regular review cadence for technology investment decisions
+* Deliver cost and outcome comparisons for competing initiatives at reviews
+* Track and report action follow-through from investment decisions
+10*Ceil(x/3)</t>
+  </si>
+  <si>
     <t>* Define process to address notifications from CSPs
 * Define cadence for review
 * Define exception criteria
@@ -1165,6 +1369,9 @@
 10*Ceil(x/4)</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Completed'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'Not monitored'}, {'Score': 2, 'Condition': 'Reported'}, {'Score': 5, 'Condition': 'Manual remediation'}, {'Score': 10, 'Condition': 'Automated remediation'}]</t>
   </si>
   <si>
@@ -1180,9 +1387,6 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1-2 completed'}, {'Score': 8, 'Condition': 'items 1-3 completed'}, {'Score': 10, 'Condition': 'items 1-4 completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Completed'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
   </si>
   <si>
@@ -1264,6 +1468,9 @@
     <t>[{'Score': 0, 'Condition': 'No alerting in workflow tools'}, {'Score': 1, 'Condition': 'Alerting in at least one tool'}, {'Score': 3, 'Condition': 'Alerting in some tooling [&gt;20%]'}, {'Score': 6, 'Condition': 'Alerting in most tooling [&gt;60%]'}, {'Score': 10, 'Condition': 'Alerting in all workflow tools [100%]'}]</t>
   </si>
   <si>
+    <t>0: Not done</t>
+  </si>
+  <si>
     <t>0: Not monitored</t>
   </si>
   <si>
@@ -1271,9 +1478,6 @@
   </si>
   <si>
     <t>0: No items completed</t>
-  </si>
-  <si>
-    <t>0: Not done</t>
   </si>
   <si>
     <t>0: Low Maturity (0-9)</t>
@@ -2222,14 +2426,14 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2">
-        <f>SUM(Scoring!F2:F110)</f>
+        <f>SUM(Scoring!F2:F140)</f>
         <v>0</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2">
-        <f>SUM(Scoring!I2:I110)/A2</f>
+        <f>SUM(Scoring!I2:I140)/A2</f>
         <v>0</v>
       </c>
       <c r="D2">
@@ -2251,10 +2455,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="U5">
-        <f>SUMIF(Scoring!J2:J110,A5,Scoring!I2:I110)/SUMIF(Scoring!J2:J110,A5,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!J2:J140,A5,Scoring!I2:I140)/SUMIF(Scoring!J2:J140,A5,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2263,10 +2467,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="U6">
-        <f>SUMIF(Scoring!J2:J110,A6,Scoring!I2:I110)/SUMIF(Scoring!J2:J110,A6,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!J2:J140,A6,Scoring!I2:I140)/SUMIF(Scoring!J2:J140,A6,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2275,10 +2479,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="U7">
-        <f>SUMIF(Scoring!J2:J110,A7,Scoring!I2:I110)/SUMIF(Scoring!J2:J110,A7,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!J2:J140,A7,Scoring!I2:I140)/SUMIF(Scoring!J2:J140,A7,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2287,10 +2491,10 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="U8">
-        <f>SUMIF(Scoring!J2:J110,A8,Scoring!I2:I110)/SUMIF(Scoring!J2:J110,A8,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!J2:J140,A8,Scoring!I2:I140)/SUMIF(Scoring!J2:J140,A8,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2314,10 +2518,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <f>SUMIF(Scoring!K2:K110,A12,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A12,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A12,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A12,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2326,10 +2530,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <f>SUMIF(Scoring!K2:K110,A13,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A13,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A13,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A13,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2338,10 +2542,10 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="U14">
-        <f>SUMIF(Scoring!K2:K110,A14,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A14,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A14,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A14,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2350,10 +2554,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <f>SUMIF(Scoring!K2:K110,A15,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A15,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A15,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A15,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2365,7 +2569,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <f>SUMIF(Scoring!K2:K110,A16,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A16,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A16,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A16,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2374,10 +2578,10 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <f>SUMIF(Scoring!K2:K110,A17,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A17,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A17,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A17,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2386,10 +2590,10 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <f>SUMIF(Scoring!K2:K110,A18,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A18,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A18,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A18,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2398,10 +2602,10 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <f>SUMIF(Scoring!K2:K110,A19,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A19,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A19,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A19,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2413,7 +2617,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <f>SUMIF(Scoring!K2:K110,A20,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A20,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A20,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A20,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2425,7 +2629,7 @@
         <v>6</v>
       </c>
       <c r="U21">
-        <f>SUMIF(Scoring!K2:K110,A21,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A21,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A21,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A21,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2434,10 +2638,10 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <f>SUMIF(Scoring!K2:K110,A22,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A22,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A22,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A22,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2446,10 +2650,10 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <f>SUMIF(Scoring!K2:K110,A23,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A23,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A23,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A23,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2461,7 +2665,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <f>SUMIF(Scoring!K2:K110,A24,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A24,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A24,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A24,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2473,7 +2677,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <f>SUMIF(Scoring!K2:K110,A25,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A25,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A25,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A25,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2482,10 +2686,10 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <f>SUMIF(Scoring!K2:K110,A26,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A26,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A26,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A26,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2497,7 +2701,7 @@
         <v>6</v>
       </c>
       <c r="U27">
-        <f>SUMIF(Scoring!K2:K110,A27,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A27,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A27,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A27,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2509,7 +2713,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <f>SUMIF(Scoring!K2:K110,A28,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A28,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A28,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A28,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2518,10 +2722,10 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <f>SUMIF(Scoring!K2:K110,A29,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A29,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A29,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A29,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2533,7 +2737,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <f>SUMIF(Scoring!K2:K110,A30,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A30,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A30,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A30,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2545,7 +2749,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <f>SUMIF(Scoring!K2:K110,A31,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A31,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A31,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A31,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2557,7 +2761,7 @@
         <v>6</v>
       </c>
       <c r="U32">
-        <f>SUMIF(Scoring!K2:K110,A32,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A32,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A32,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A32,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2569,7 +2773,7 @@
         <v>6</v>
       </c>
       <c r="U33">
-        <f>SUMIF(Scoring!K2:K110,A33,Scoring!I2:I110)/SUMIF(Scoring!K2:K110,A33,Scoring!F2:F110)</f>
+        <f>SUMIF(Scoring!K2:K140,A33,Scoring!I2:I140)/SUMIF(Scoring!K2:K140,A33,Scoring!F2:F140)</f>
         <v>0</v>
       </c>
     </row>
@@ -2592,7 +2796,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K140"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
@@ -2654,16 +2858,16 @@
         <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="E2" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>345</v>
+        <v>409</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2678,26 +2882,21 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="E3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>346</v>
+        <v>409</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2707,7 +2906,7 @@
         <v>6</v>
       </c>
       <c r="K3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2717,19 +2916,16 @@
         <v>46</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2739,7 +2935,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2749,19 +2945,16 @@
         <v>47</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="H5" s="1" t="s">
-        <v>347</v>
+        <v>410</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -2771,7 +2964,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2781,19 +2974,16 @@
         <v>48</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="E6" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -2803,28 +2993,31 @@
         <v>6</v>
       </c>
       <c r="K6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="E7" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
+      <c r="G7" s="1" t="s">
+        <v>327</v>
+      </c>
       <c r="H7" s="1" t="s">
-        <v>348</v>
+        <v>411</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -2834,7 +3027,7 @@
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2844,16 +3037,19 @@
         <v>50</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="E8" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
+      <c r="G8" s="1" t="s">
+        <v>328</v>
+      </c>
       <c r="H8" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -2863,7 +3059,7 @@
         <v>6</v>
       </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2873,16 +3069,19 @@
         <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="E9" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
+      <c r="G9" s="1" t="s">
+        <v>329</v>
+      </c>
       <c r="H9" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -2892,7 +3091,7 @@
         <v>6</v>
       </c>
       <c r="K9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2902,19 +3101,19 @@
         <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="E10" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>271</v>
+        <v>330</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>347</v>
+        <v>412</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -2924,7 +3123,7 @@
         <v>6</v>
       </c>
       <c r="K10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2934,16 +3133,19 @@
         <v>53</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="E11" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
+      <c r="G11" s="1" t="s">
+        <v>331</v>
+      </c>
       <c r="H11" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -2953,28 +3155,28 @@
         <v>6</v>
       </c>
       <c r="K11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="E12" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -2984,7 +3186,7 @@
         <v>6</v>
       </c>
       <c r="K12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2994,16 +3196,16 @@
         <v>55</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="E13" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -3013,7 +3215,7 @@
         <v>6</v>
       </c>
       <c r="K13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3023,16 +3225,16 @@
         <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="E14" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -3042,7 +3244,7 @@
         <v>6</v>
       </c>
       <c r="K14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -3052,16 +3254,19 @@
         <v>57</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="E15" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
+      <c r="G15" s="1" t="s">
+        <v>332</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3071,7 +3276,7 @@
         <v>6</v>
       </c>
       <c r="K15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3081,16 +3286,16 @@
         <v>58</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="E16" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3100,26 +3305,28 @@
         <v>6</v>
       </c>
       <c r="K16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="C17" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="E17" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3134,26 +3341,21 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2"/>
-      <c r="B18" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="E18" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="H18" s="1" t="s">
-        <v>349</v>
+        <v>409</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3163,7 +3365,7 @@
         <v>6</v>
       </c>
       <c r="K18" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3173,19 +3375,16 @@
         <v>61</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="E19" t="s">
-        <v>265</v>
+        <v>322</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="H19" s="1" t="s">
-        <v>350</v>
+        <v>409</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3195,7 +3394,7 @@
         <v>6</v>
       </c>
       <c r="K19" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3205,19 +3404,16 @@
         <v>62</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="H20" s="1" t="s">
-        <v>351</v>
+        <v>409</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3227,7 +3423,7 @@
         <v>6</v>
       </c>
       <c r="K20" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3237,19 +3433,16 @@
         <v>63</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="E21" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="H21" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3259,31 +3452,26 @@
         <v>6</v>
       </c>
       <c r="K21" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2"/>
-      <c r="B22" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="B22" s="2"/>
       <c r="C22" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="E22" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="H22" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3293,29 +3481,31 @@
         <v>6</v>
       </c>
       <c r="K22" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="C23" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="E23" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>277</v>
+        <v>333</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>347</v>
+        <v>413</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3325,7 +3515,7 @@
         <v>6</v>
       </c>
       <c r="K23" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -3335,19 +3525,19 @@
         <v>66</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="E24" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>347</v>
+        <v>414</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3357,7 +3547,7 @@
         <v>6</v>
       </c>
       <c r="K24" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3367,19 +3557,19 @@
         <v>67</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="E25" t="s">
-        <v>263</v>
+        <v>324</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>279</v>
+        <v>335</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>347</v>
+        <v>415</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3389,7 +3579,7 @@
         <v>6</v>
       </c>
       <c r="K25" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -3399,19 +3589,19 @@
         <v>68</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="E26" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>347</v>
+        <v>412</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3421,7 +3611,7 @@
         <v>6</v>
       </c>
       <c r="K26" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3431,19 +3621,16 @@
         <v>69</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="E27" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="H27" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3453,28 +3640,31 @@
         <v>6</v>
       </c>
       <c r="K27" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="E28" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
+      <c r="G28" s="1" t="s">
+        <v>337</v>
+      </c>
       <c r="H28" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3484,7 +3674,7 @@
         <v>6</v>
       </c>
       <c r="K28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3494,16 +3684,19 @@
         <v>71</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="E29" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
+      <c r="G29" s="1" t="s">
+        <v>338</v>
+      </c>
       <c r="H29" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3513,7 +3706,7 @@
         <v>6</v>
       </c>
       <c r="K29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3523,16 +3716,19 @@
         <v>72</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="E30" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
+      <c r="G30" s="1" t="s">
+        <v>339</v>
+      </c>
       <c r="H30" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3542,7 +3738,7 @@
         <v>6</v>
       </c>
       <c r="K30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3552,16 +3748,19 @@
         <v>73</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="E31" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
+      <c r="G31" s="1" t="s">
+        <v>340</v>
+      </c>
       <c r="H31" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3571,7 +3770,7 @@
         <v>6</v>
       </c>
       <c r="K31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3581,16 +3780,19 @@
         <v>74</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="E32" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
+      <c r="G32" s="1" t="s">
+        <v>341</v>
+      </c>
       <c r="H32" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -3600,7 +3802,7 @@
         <v>6</v>
       </c>
       <c r="K32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3610,16 +3812,19 @@
         <v>75</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="E33" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
+      <c r="G33" s="1" t="s">
+        <v>342</v>
+      </c>
       <c r="H33" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -3629,28 +3834,28 @@
         <v>6</v>
       </c>
       <c r="K33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="E34" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>352</v>
+        <v>409</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -3660,40 +3865,36 @@
         <v>6</v>
       </c>
       <c r="K34" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="E35" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>353</v>
+        <v>409</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K35" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3703,29 +3904,26 @@
         <v>78</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="E36" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="H36" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K36" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3735,26 +3933,26 @@
         <v>79</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="E37" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>354</v>
+        <v>409</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K37" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3764,26 +3962,26 @@
         <v>80</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="E38" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K38" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3793,58 +3991,57 @@
         <v>81</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="E39" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K39" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
+      <c r="B40" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="C40" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="E40" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="H40" s="1" t="s">
-        <v>347</v>
+        <v>416</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -3854,26 +4051,29 @@
         <v>83</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="E41" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
+      <c r="G41" s="1" t="s">
+        <v>343</v>
+      </c>
       <c r="H41" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -3883,26 +4083,29 @@
         <v>84</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="E42" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
+      <c r="G42" s="1" t="s">
+        <v>344</v>
+      </c>
       <c r="H42" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -3912,47 +4115,52 @@
         <v>85</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="E43" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
+      <c r="G43" s="1" t="s">
+        <v>345</v>
+      </c>
       <c r="H43" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
         <v>0</v>
       </c>
       <c r="J43" t="s">
+        <v>6</v>
+      </c>
+      <c r="K43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K43" t="s">
+      <c r="B44" s="2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="E44" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>348</v>
+        <v>417</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -3962,7 +4170,7 @@
         <v>7</v>
       </c>
       <c r="K44" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3972,16 +4180,19 @@
         <v>87</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="E45" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
+      <c r="G45" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="H45" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -3991,7 +4202,7 @@
         <v>7</v>
       </c>
       <c r="K45" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -4001,16 +4212,16 @@
         <v>88</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="E46" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>348</v>
+        <v>418</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -4020,7 +4231,7 @@
         <v>7</v>
       </c>
       <c r="K46" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -4030,16 +4241,16 @@
         <v>89</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="E47" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4049,7 +4260,7 @@
         <v>7</v>
       </c>
       <c r="K47" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -4059,16 +4270,16 @@
         <v>90</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="E48" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4078,7 +4289,7 @@
         <v>7</v>
       </c>
       <c r="K48" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -4088,16 +4299,16 @@
         <v>91</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="E49" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4107,28 +4318,26 @@
         <v>7</v>
       </c>
       <c r="K49" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="2"/>
-      <c r="B50" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="B50" s="2"/>
       <c r="C50" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="E50" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>355</v>
+        <v>409</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4138,7 +4347,7 @@
         <v>7</v>
       </c>
       <c r="K50" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -4148,16 +4357,16 @@
         <v>93</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="E51" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4167,7 +4376,7 @@
         <v>7</v>
       </c>
       <c r="K51" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -4177,16 +4386,19 @@
         <v>94</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="E52" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
+      <c r="G52" s="1" t="s">
+        <v>347</v>
+      </c>
       <c r="H52" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4196,7 +4408,7 @@
         <v>7</v>
       </c>
       <c r="K52" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -4206,16 +4418,16 @@
         <v>95</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E53" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4225,7 +4437,7 @@
         <v>7</v>
       </c>
       <c r="K53" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -4235,16 +4447,16 @@
         <v>96</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="E54" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4254,7 +4466,7 @@
         <v>7</v>
       </c>
       <c r="K54" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -4264,16 +4476,16 @@
         <v>97</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="E55" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4283,28 +4495,28 @@
         <v>7</v>
       </c>
       <c r="K55" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="E56" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4314,7 +4526,7 @@
         <v>7</v>
       </c>
       <c r="K56" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -4324,16 +4536,16 @@
         <v>99</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="E57" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4343,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="K57" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -4353,19 +4565,16 @@
         <v>100</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="E58" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="H58" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4375,28 +4584,26 @@
         <v>7</v>
       </c>
       <c r="K58" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="2"/>
-      <c r="B59" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="B59" s="2"/>
       <c r="C59" s="2" t="s">
         <v>101</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="E59" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4406,7 +4613,7 @@
         <v>7</v>
       </c>
       <c r="K59" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -4416,16 +4623,16 @@
         <v>102</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="E60" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>356</v>
+        <v>409</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4435,7 +4642,7 @@
         <v>7</v>
       </c>
       <c r="K60" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -4445,16 +4652,16 @@
         <v>103</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="E61" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>355</v>
+        <v>409</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4464,26 +4671,28 @@
         <v>7</v>
       </c>
       <c r="K61" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
+      <c r="B62" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C62" s="2" t="s">
         <v>104</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>348</v>
+        <v>419</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4493,7 +4702,7 @@
         <v>7</v>
       </c>
       <c r="K62" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -4503,16 +4712,16 @@
         <v>105</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="E63" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4522,7 +4731,7 @@
         <v>7</v>
       </c>
       <c r="K63" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -4532,16 +4741,16 @@
         <v>106</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="E64" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -4551,71 +4760,65 @@
         <v>7</v>
       </c>
       <c r="K64" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:11">
-      <c r="A65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
       <c r="C65" s="2" t="s">
         <v>107</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="E65" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>357</v>
+        <v>409</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
         <v>0</v>
       </c>
       <c r="J65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="2"/>
-      <c r="B66" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
         <v>108</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="E66" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>353</v>
+        <v>409</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
         <v>0</v>
       </c>
       <c r="J66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K66" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -4625,55 +4828,57 @@
         <v>109</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="E67" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>353</v>
+        <v>409</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
         <v>0</v>
       </c>
       <c r="J67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K67" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
+      <c r="B68" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C68" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="E68" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
         <v>0</v>
       </c>
       <c r="J68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K68" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -4683,26 +4888,26 @@
         <v>111</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="E69" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
         <v>0</v>
       </c>
       <c r="J69" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K69" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -4712,26 +4917,26 @@
         <v>112</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="E70" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
         <v>0</v>
       </c>
       <c r="J70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K70" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -4741,60 +4946,55 @@
         <v>113</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="E71" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
         <v>0</v>
       </c>
       <c r="J71" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K71" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="2"/>
-      <c r="B72" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="B72" s="2"/>
       <c r="C72" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="E72" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="H72" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
         <v>0</v>
       </c>
       <c r="J72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K72" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -4804,58 +5004,60 @@
         <v>115</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="E73" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
+      <c r="G73" s="1" t="s">
+        <v>348</v>
+      </c>
       <c r="H73" s="1" t="s">
-        <v>358</v>
+        <v>412</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
         <v>0</v>
       </c>
       <c r="J73" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K73" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
+      <c r="B74" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C74" s="2" t="s">
         <v>116</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="E74" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
-      <c r="G74" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="H74" s="1" t="s">
-        <v>355</v>
+        <v>409</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
         <v>0</v>
       </c>
       <c r="J74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K74" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -4865,26 +5067,26 @@
         <v>117</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="E75" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>359</v>
+        <v>420</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
         <v>0</v>
       </c>
       <c r="J75" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K75" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -4894,63 +5096,55 @@
         <v>118</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="E76" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="H76" s="1" t="s">
-        <v>347</v>
+        <v>419</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
         <v>0</v>
       </c>
       <c r="J76" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K76" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="2"/>
-      <c r="B77" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="B77" s="2"/>
       <c r="C77" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="E77" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
-      <c r="G77" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="H77" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
         <v>0</v>
       </c>
       <c r="J77" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K77" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -4960,29 +5154,26 @@
         <v>120</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="E78" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
-      <c r="G78" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="H78" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
         <v>0</v>
       </c>
       <c r="J78" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K78" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -4992,51 +5183,49 @@
         <v>121</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="E79" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
-      <c r="G79" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="H79" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
         <v>0</v>
       </c>
       <c r="J79" t="s">
+        <v>7</v>
+      </c>
+      <c r="K79" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K79" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
+      <c r="B80" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="C80" s="2" t="s">
         <v>122</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="E80" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
-      <c r="G80" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="H80" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -5046,7 +5235,7 @@
         <v>8</v>
       </c>
       <c r="K80" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -5056,19 +5245,16 @@
         <v>123</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="E81" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
-      <c r="G81" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="H81" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5078,7 +5264,7 @@
         <v>8</v>
       </c>
       <c r="K81" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -5088,16 +5274,16 @@
         <v>124</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="E82" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>355</v>
+        <v>409</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5107,7 +5293,7 @@
         <v>8</v>
       </c>
       <c r="K82" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -5117,19 +5303,16 @@
         <v>125</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="E83" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
-      <c r="G83" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="H83" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5139,31 +5322,26 @@
         <v>8</v>
       </c>
       <c r="K83" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="2"/>
-      <c r="B84" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="B84" s="2"/>
       <c r="C84" s="2" t="s">
         <v>126</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="E84" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
-      <c r="G84" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="H84" s="1" t="s">
-        <v>347</v>
+        <v>421</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5173,7 +5351,7 @@
         <v>8</v>
       </c>
       <c r="K84" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -5183,19 +5361,16 @@
         <v>127</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="E85" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
-      <c r="G85" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="H85" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5205,29 +5380,28 @@
         <v>8</v>
       </c>
       <c r="K85" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
+      <c r="B86" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C86" s="2" t="s">
         <v>128</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="E86" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
-      <c r="G86" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="H86" s="1" t="s">
-        <v>347</v>
+        <v>417</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5237,7 +5411,7 @@
         <v>8</v>
       </c>
       <c r="K86" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -5247,19 +5421,16 @@
         <v>129</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="E87" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
-      <c r="G87" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="H87" s="1" t="s">
-        <v>347</v>
+        <v>417</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5269,7 +5440,7 @@
         <v>8</v>
       </c>
       <c r="K87" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -5279,19 +5450,16 @@
         <v>130</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="E88" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
-      <c r="G88" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="H88" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5301,7 +5469,7 @@
         <v>8</v>
       </c>
       <c r="K88" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -5311,16 +5479,16 @@
         <v>131</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="E89" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>358</v>
+        <v>409</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -5330,43 +5498,36 @@
         <v>8</v>
       </c>
       <c r="K89" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:11">
-      <c r="A90" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
       <c r="C90" s="2" t="s">
         <v>132</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="E90" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
-      <c r="G90" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="H90" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
         <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K90" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -5376,61 +5537,57 @@
         <v>133</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="E91" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
-      <c r="G91" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="H91" s="1" t="s">
-        <v>355</v>
+        <v>409</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
         <v>0</v>
       </c>
       <c r="J91" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K91" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
+      <c r="B92" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="C92" s="2" t="s">
         <v>134</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="E92" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
-      <c r="G92" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="H92" s="1" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K92" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -5440,29 +5597,29 @@
         <v>135</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="E93" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>302</v>
+        <v>349</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
         <v>0</v>
       </c>
       <c r="J93" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K93" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -5472,29 +5629,26 @@
         <v>136</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="E94" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
-      <c r="G94" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="H94" s="1" t="s">
-        <v>355</v>
+        <v>422</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K94" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -5504,63 +5658,58 @@
         <v>137</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="E95" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>347</v>
+        <v>419</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
         <v>0</v>
       </c>
       <c r="J95" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K95" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="2"/>
-      <c r="B96" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B96" s="2"/>
       <c r="C96" s="2" t="s">
         <v>138</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="E96" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
-      <c r="G96" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="H96" s="1" t="s">
-        <v>347</v>
+        <v>423</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
         <v>0</v>
       </c>
       <c r="J96" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K96" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -5570,58 +5719,63 @@
         <v>139</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="E97" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>306</v>
+        <v>351</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>347</v>
+        <v>412</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
         <v>0</v>
       </c>
       <c r="J97" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K97" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
+      <c r="B98" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C98" s="2" t="s">
         <v>140</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="E98" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
+      <c r="G98" s="1" t="s">
+        <v>352</v>
+      </c>
       <c r="H98" s="1" t="s">
-        <v>360</v>
+        <v>412</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
         <v>0</v>
       </c>
       <c r="J98" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K98" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -5631,60 +5785,61 @@
         <v>141</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="E99" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>307</v>
+        <v>353</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>347</v>
+        <v>412</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
         <v>0</v>
       </c>
       <c r="J99" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K99" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="2"/>
-      <c r="B100" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="B100" s="2"/>
       <c r="C100" s="2" t="s">
         <v>142</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="E100" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
+      <c r="G100" s="1" t="s">
+        <v>354</v>
+      </c>
       <c r="H100" s="1" t="s">
-        <v>361</v>
+        <v>412</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
         <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K100" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -5694,29 +5849,29 @@
         <v>143</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="E101" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>308</v>
+        <v>355</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>347</v>
+        <v>412</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
         <v>0</v>
       </c>
       <c r="J101" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K101" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -5726,29 +5881,29 @@
         <v>144</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="E102" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>309</v>
+        <v>356</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>347</v>
+        <v>412</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
         <v>0</v>
       </c>
       <c r="J102" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K102" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -5758,89 +5913,92 @@
         <v>145</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="E103" t="s">
-        <v>266</v>
+        <v>323</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>361</v>
+        <v>419</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
         <v>0</v>
       </c>
       <c r="J103" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K103" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="2"/>
-      <c r="B104" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B104" s="2"/>
       <c r="C104" s="2" t="s">
         <v>146</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="E104" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
+      <c r="G104" s="1" t="s">
+        <v>357</v>
+      </c>
       <c r="H104" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
         <v>0</v>
       </c>
       <c r="J104" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K104" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="2"/>
-      <c r="B105" s="2"/>
+      <c r="B105" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C105" s="2" t="s">
         <v>147</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="E105" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>310</v>
+        <v>358</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>347</v>
+        <v>412</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
         <v>0</v>
       </c>
       <c r="J105" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K105" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -5850,29 +6008,29 @@
         <v>148</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="E106" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>311</v>
+        <v>359</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>347</v>
+        <v>412</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
         <v>0</v>
       </c>
       <c r="J106" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K106" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -5882,26 +6040,29 @@
         <v>149</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="E107" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
+      <c r="G107" s="1" t="s">
+        <v>360</v>
+      </c>
       <c r="H107" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
         <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K107" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -5911,26 +6072,29 @@
         <v>150</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="E108" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
+      <c r="G108" s="1" t="s">
+        <v>361</v>
+      </c>
       <c r="H108" s="1" t="s">
-        <v>362</v>
+        <v>412</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
         <v>0</v>
       </c>
       <c r="J108" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K108" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -5940,26 +6104,29 @@
         <v>151</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="E109" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
+      <c r="G109" s="1" t="s">
+        <v>362</v>
+      </c>
       <c r="H109" s="1" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
         <v>0</v>
       </c>
       <c r="J109" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K109" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -5969,87 +6136,1009 @@
         <v>152</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="E110" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="F110">
         <v>1</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>348</v>
+        <v>422</v>
       </c>
       <c r="I110">
         <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
         <v>0</v>
       </c>
       <c r="J110" t="s">
+        <v>8</v>
+      </c>
+      <c r="K110" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K110" t="s">
+      <c r="B111" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E111" t="s">
+        <v>323</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I111">
+        <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J111" t="s">
+        <v>9</v>
+      </c>
+      <c r="K111" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E112" t="s">
+        <v>323</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="I112">
+        <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J112" t="s">
+        <v>9</v>
+      </c>
+      <c r="K112" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E113" t="s">
+        <v>323</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I113">
+        <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J113" t="s">
+        <v>9</v>
+      </c>
+      <c r="K113" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E114" t="s">
+        <v>323</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="I114">
+        <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J114" t="s">
+        <v>9</v>
+      </c>
+      <c r="K114" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E115" t="s">
+        <v>323</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="I115">
+        <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J115" t="s">
+        <v>9</v>
+      </c>
+      <c r="K115" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E116" t="s">
+        <v>323</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I116">
+        <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J116" t="s">
+        <v>9</v>
+      </c>
+      <c r="K116" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E117" t="s">
+        <v>322</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I117">
+        <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J117" t="s">
+        <v>9</v>
+      </c>
+      <c r="K117" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118" s="2"/>
+      <c r="B118" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E118" t="s">
+        <v>323</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I118">
+        <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J118" t="s">
+        <v>9</v>
+      </c>
+      <c r="K118" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E119" t="s">
+        <v>323</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I119">
+        <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J119" t="s">
+        <v>9</v>
+      </c>
+      <c r="K119" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E120" t="s">
+        <v>323</v>
+      </c>
+      <c r="F120">
+        <v>1</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="I120">
+        <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J120" t="s">
+        <v>9</v>
+      </c>
+      <c r="K120" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E121" t="s">
+        <v>322</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I121">
+        <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K121" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122" s="2"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E122" t="s">
+        <v>322</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I122">
+        <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J122" t="s">
+        <v>9</v>
+      </c>
+      <c r="K122" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E123" t="s">
+        <v>323</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I123">
+        <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J123" t="s">
+        <v>9</v>
+      </c>
+      <c r="K123" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E124" t="s">
+        <v>322</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I124">
+        <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J124" t="s">
+        <v>9</v>
+      </c>
+      <c r="K124" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125" s="2"/>
+      <c r="B125" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E125" t="s">
+        <v>322</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I125">
+        <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J125" t="s">
+        <v>9</v>
+      </c>
+      <c r="K125" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E126" t="s">
+        <v>322</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I126">
+        <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J126" t="s">
+        <v>9</v>
+      </c>
+      <c r="K126" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="A127" s="2"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E127" t="s">
+        <v>322</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I127">
+        <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J127" t="s">
+        <v>9</v>
+      </c>
+      <c r="K127" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
+      <c r="A128" s="2"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E128" t="s">
+        <v>323</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="I128">
+        <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J128" t="s">
+        <v>9</v>
+      </c>
+      <c r="K128" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="A129" s="2"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E129" t="s">
+        <v>322</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I129">
+        <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J129" t="s">
+        <v>9</v>
+      </c>
+      <c r="K129" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="2"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E130" t="s">
+        <v>323</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I130">
+        <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J130" t="s">
+        <v>9</v>
+      </c>
+      <c r="K130" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="2"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E131" t="s">
+        <v>323</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I131">
+        <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J131" t="s">
+        <v>9</v>
+      </c>
+      <c r="K131" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132" s="2"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E132" t="s">
+        <v>322</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I132">
+        <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J132" t="s">
+        <v>9</v>
+      </c>
+      <c r="K132" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="A133" s="2"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E133" t="s">
+        <v>326</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="I133">
+        <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J133" t="s">
+        <v>9</v>
+      </c>
+      <c r="K133" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
+      <c r="A134" s="2"/>
+      <c r="B134" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="C134" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="E134" t="s">
+        <v>322</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I134">
+        <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J134" t="s">
+        <v>9</v>
+      </c>
+      <c r="K134" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11">
+      <c r="A135" s="2"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E135" t="s">
+        <v>323</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I135">
+        <f>F135*VALUE(LEFT(H135, FIND(":", H135)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J135" t="s">
+        <v>9</v>
+      </c>
+      <c r="K135" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11">
+      <c r="A136" s="2"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E136" t="s">
+        <v>323</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I136">
+        <f>F136*VALUE(LEFT(H136, FIND(":", H136)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J136" t="s">
+        <v>9</v>
+      </c>
+      <c r="K136" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11">
+      <c r="A137" s="2"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E137" t="s">
+        <v>322</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I137">
+        <f>F137*VALUE(LEFT(H137, FIND(":", H137)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J137" t="s">
+        <v>9</v>
+      </c>
+      <c r="K137" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11">
+      <c r="A138" s="2"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E138" t="s">
+        <v>323</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="I138">
+        <f>F138*VALUE(LEFT(H138, FIND(":", H138)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J138" t="s">
+        <v>9</v>
+      </c>
+      <c r="K138" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11">
+      <c r="A139" s="2"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E139" t="s">
+        <v>322</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I139">
+        <f>F139*VALUE(LEFT(H139, FIND(":", H139)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J139" t="s">
+        <v>9</v>
+      </c>
+      <c r="K139" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11">
+      <c r="A140" s="2"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E140" t="s">
+        <v>322</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I140">
+        <f>F140*VALUE(LEFT(H140, FIND(":", H140)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J140" t="s">
+        <v>9</v>
+      </c>
+      <c r="K140" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A2:A34"/>
-    <mergeCell ref="A35:A64"/>
-    <mergeCell ref="A65:A89"/>
-    <mergeCell ref="A90:A110"/>
-    <mergeCell ref="B3:B6"/>
+  <mergeCells count="26">
+    <mergeCell ref="A2:A43"/>
+    <mergeCell ref="A44:A79"/>
+    <mergeCell ref="A80:A110"/>
+    <mergeCell ref="A111:A140"/>
+    <mergeCell ref="B2:B6"/>
     <mergeCell ref="B7:B11"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="B23:B27"/>
     <mergeCell ref="B28:B33"/>
-    <mergeCell ref="B35:B43"/>
-    <mergeCell ref="B44:B49"/>
-    <mergeCell ref="B50:B55"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B59:B64"/>
-    <mergeCell ref="B66:B71"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="B77:B83"/>
-    <mergeCell ref="B84:B89"/>
-    <mergeCell ref="B90:B95"/>
-    <mergeCell ref="B96:B99"/>
-    <mergeCell ref="B100:B103"/>
-    <mergeCell ref="B104:B110"/>
+    <mergeCell ref="B34:B39"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="B44:B55"/>
+    <mergeCell ref="B56:B61"/>
+    <mergeCell ref="B62:B67"/>
+    <mergeCell ref="B68:B73"/>
+    <mergeCell ref="B74:B79"/>
+    <mergeCell ref="B80:B85"/>
+    <mergeCell ref="B86:B91"/>
+    <mergeCell ref="B92:B97"/>
+    <mergeCell ref="B98:B104"/>
+    <mergeCell ref="B105:B110"/>
+    <mergeCell ref="B111:B117"/>
+    <mergeCell ref="B118:B124"/>
+    <mergeCell ref="B125:B133"/>
+    <mergeCell ref="B134:B140"/>
   </mergeCells>
-  <dataValidations count="109">
+  <dataValidations count="139">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5">
       <formula1>"0: Not monitored,2: Reported,5: Manual remediation,10: Automated remediation"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7">
       <formula1>"0: 0 items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10">
       <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
       <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10">
-      <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
-      <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -6058,100 +7147,100 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H16">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
+      <formula1>"0: Not done,10: Defined"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
       <formula1>"0: Low Maturity (0-9),4: Developing (10-18),7: Established (19-26),10: Optimizing (27-31)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H24">
       <formula1>"0: Low Maturity. Score Range (0-8),4: Developing. Score Range (9-17),7: Established. Score Range (18-24),10: Optimizing. Score Range (25-29)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
       <formula1>"0: Low Maturity. Score Range (0-15),4: Developing. Score Range (16-31),7: Established. Score Range (32-44),10: Optimizing. Score Range (45-52)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
       <formula1>"0: No items completed,2: item 1 completed,4: items 1-2 completed,6: items 1-3 completed,8: items 1-4 completed,10: items 1-5 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
       <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
       <formula1>"0: Not done,10: Done and clearly defined"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
       <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
-      <formula1>"0: Not done,10: Defined"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
-      <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
-      <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
+      <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -6163,16 +7252,16 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
       <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -6181,25 +7270,25 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H56">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
-      <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -6208,19 +7297,19 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
-      <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H70">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -6229,120 +7318,210 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
+      <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H77">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H78">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H81">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H83">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H84">
+      <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H85">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H86">
+      <formula1>"0: Does not exist,10: Exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
+      <formula1>"0: Does not exist,10: Exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
       <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
       <formula1>"0: No alerting,10: Alerting exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H78">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H101">
       <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H81">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H102">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H83">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H104">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H84">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H85">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H86">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
-      <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
-      <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80% ,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
-      <formula1>"0: No items completed,5: 1 item  completed,10: 2 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
-      <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
-      <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
-      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H101">
-      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H102">
-      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
-      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H104">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H105">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H106">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H107">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H107">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H109">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H110">
+      <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H111">
+      <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H112">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80% ,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H113">
+      <formula1>"0: No items completed,5: 1 item  completed,10: 2 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H114">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H115">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H116">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H117">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H118">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H119">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H120">
+      <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H121">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H122">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H123">
+      <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H124">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H125">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H126">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H127">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H128">
+      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H129">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H130">
+      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H131">
+      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H132">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H133">
+      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H134">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H135">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H136">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H137">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H138">
       <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H109">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H139">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H110">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H140">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6456,6 +7635,36 @@
     <hyperlink ref="D108" r:id="rId107"/>
     <hyperlink ref="D109" r:id="rId108"/>
     <hyperlink ref="D110" r:id="rId109"/>
+    <hyperlink ref="D111" r:id="rId110"/>
+    <hyperlink ref="D112" r:id="rId111"/>
+    <hyperlink ref="D113" r:id="rId112"/>
+    <hyperlink ref="D114" r:id="rId113"/>
+    <hyperlink ref="D115" r:id="rId114"/>
+    <hyperlink ref="D116" r:id="rId115"/>
+    <hyperlink ref="D117" r:id="rId116"/>
+    <hyperlink ref="D118" r:id="rId117"/>
+    <hyperlink ref="D119" r:id="rId118"/>
+    <hyperlink ref="D120" r:id="rId119"/>
+    <hyperlink ref="D121" r:id="rId120"/>
+    <hyperlink ref="D122" r:id="rId121"/>
+    <hyperlink ref="D123" r:id="rId122"/>
+    <hyperlink ref="D124" r:id="rId123"/>
+    <hyperlink ref="D125" r:id="rId124"/>
+    <hyperlink ref="D126" r:id="rId125"/>
+    <hyperlink ref="D127" r:id="rId126"/>
+    <hyperlink ref="D128" r:id="rId127"/>
+    <hyperlink ref="D129" r:id="rId128"/>
+    <hyperlink ref="D130" r:id="rId129"/>
+    <hyperlink ref="D131" r:id="rId130"/>
+    <hyperlink ref="D132" r:id="rId131"/>
+    <hyperlink ref="D133" r:id="rId132"/>
+    <hyperlink ref="D134" r:id="rId133"/>
+    <hyperlink ref="D135" r:id="rId134"/>
+    <hyperlink ref="D136" r:id="rId135"/>
+    <hyperlink ref="D137" r:id="rId136"/>
+    <hyperlink ref="D138" r:id="rId137"/>
+    <hyperlink ref="D139" r:id="rId138"/>
+    <hyperlink ref="D140" r:id="rId139"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -544,7 +544,7 @@
     <t>Optimize Pipelines for Timeliness</t>
   </si>
   <si>
-    <t>Define ingestion frequency; include mandatory metadata.</t>
+    <t>Define Data Ingestion Requirements</t>
   </si>
   <si>
     <t>Gather Requirements &amp; Define KPIs</t>
@@ -997,7 +997,7 @@
     <t>2.1.0</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.6.1</t>
   </si>
   <si>
     <t>* Select which teams or groups are in scope for the planned assessments
@@ -2801,7 +2801,7 @@
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
